--- a/eval/results/statistical_tests_new30.xlsx
+++ b/eval/results/statistical_tests_new30.xlsx
@@ -666,16 +666,16 @@
         <v>0.0318</v>
       </c>
       <c r="F2" t="n">
-        <v>0.738</v>
+        <v>0.74</v>
       </c>
       <c r="G2" t="n">
-        <v>0.777</v>
+        <v>0.779</v>
       </c>
       <c r="H2" t="n">
-        <v>0.168</v>
+        <v>0.165</v>
       </c>
       <c r="I2" t="n">
-        <v>0.163</v>
+        <v>0.159</v>
       </c>
       <c r="J2" t="n">
         <v>0.8</v>
@@ -690,7 +690,7 @@
         <v>0.667</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="O2" t="n">
         <v>0.767</v>
@@ -738,7 +738,7 @@
         <v>0.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="AE2" t="n">
         <v>0.767</v>
@@ -802,16 +802,16 @@
         <v>0.031</v>
       </c>
       <c r="F3" t="n">
-        <v>0.738</v>
+        <v>0.74</v>
       </c>
       <c r="G3" t="n">
-        <v>0.777</v>
+        <v>0.779</v>
       </c>
       <c r="H3" t="n">
-        <v>0.168</v>
+        <v>0.165</v>
       </c>
       <c r="I3" t="n">
-        <v>0.163</v>
+        <v>0.159</v>
       </c>
       <c r="J3" t="n">
         <v>0.8</v>
@@ -826,7 +826,7 @@
         <v>0.667</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="O3" t="n">
         <v>0.767</v>
@@ -874,7 +874,7 @@
         <v>0.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="AE3" t="n">
         <v>0.767</v>
@@ -938,16 +938,16 @@
         <v>0.143</v>
       </c>
       <c r="F4" t="n">
-        <v>0.738</v>
+        <v>0.74</v>
       </c>
       <c r="G4" t="n">
-        <v>0.779</v>
+        <v>0.781</v>
       </c>
       <c r="H4" t="n">
-        <v>0.168</v>
+        <v>0.165</v>
       </c>
       <c r="I4" t="n">
-        <v>0.142</v>
+        <v>0.139</v>
       </c>
       <c r="J4" t="n">
         <v>0.8</v>
@@ -962,7 +962,7 @@
         <v>0.667</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="O4" t="n">
         <v>0.767</v>
@@ -1010,7 +1010,7 @@
         <v>0.967</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.6</v>
+        <v>0.633</v>
       </c>
       <c r="AE4" t="n">
         <v>0.9</v>
@@ -1074,16 +1074,16 @@
         <v>0.217</v>
       </c>
       <c r="F5" t="n">
-        <v>0.738</v>
+        <v>0.74</v>
       </c>
       <c r="G5" t="n">
-        <v>0.779</v>
+        <v>0.781</v>
       </c>
       <c r="H5" t="n">
-        <v>0.168</v>
+        <v>0.165</v>
       </c>
       <c r="I5" t="n">
-        <v>0.142</v>
+        <v>0.139</v>
       </c>
       <c r="J5" t="n">
         <v>0.8</v>
@@ -1098,7 +1098,7 @@
         <v>0.667</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="O5" t="n">
         <v>0.767</v>
@@ -1146,7 +1146,7 @@
         <v>0.967</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.6</v>
+        <v>0.633</v>
       </c>
       <c r="AE5" t="n">
         <v>0.9</v>
@@ -1207,19 +1207,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.0203</v>
+        <v>0.0319</v>
       </c>
       <c r="F6" t="n">
         <v>0.804</v>
       </c>
       <c r="G6" t="n">
-        <v>0.76</v>
+        <v>0.762</v>
       </c>
       <c r="H6" t="n">
         <v>0.119</v>
       </c>
       <c r="I6" t="n">
-        <v>0.114</v>
+        <v>0.113</v>
       </c>
       <c r="J6" t="n">
         <v>0.767</v>
@@ -1282,7 +1282,7 @@
         <v>0.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.7</v>
+        <v>0.733</v>
       </c>
       <c r="AE6" t="n">
         <v>0.833</v>
@@ -1343,19 +1343,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.0201</v>
+        <v>0.0311</v>
       </c>
       <c r="F7" t="n">
         <v>0.804</v>
       </c>
       <c r="G7" t="n">
-        <v>0.76</v>
+        <v>0.762</v>
       </c>
       <c r="H7" t="n">
         <v>0.119</v>
       </c>
       <c r="I7" t="n">
-        <v>0.114</v>
+        <v>0.113</v>
       </c>
       <c r="J7" t="n">
         <v>0.767</v>
@@ -1418,7 +1418,7 @@
         <v>0.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.7</v>
+        <v>0.733</v>
       </c>
       <c r="AE7" t="n">
         <v>0.833</v>
@@ -1479,19 +1479,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.339</v>
+        <v>0.283</v>
       </c>
       <c r="F8" t="n">
         <v>0.804</v>
       </c>
       <c r="G8" t="n">
-        <v>0.823</v>
+        <v>0.825</v>
       </c>
       <c r="H8" t="n">
         <v>0.119</v>
       </c>
       <c r="I8" t="n">
-        <v>0.113</v>
+        <v>0.11</v>
       </c>
       <c r="J8" t="n">
         <v>0.767</v>
@@ -1554,7 +1554,7 @@
         <v>0.967</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.633</v>
+        <v>0.667</v>
       </c>
       <c r="AE8" t="n">
         <v>0.9330000000000001</v>
@@ -1590,7 +1590,7 @@
         <v>0.6</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.407</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="9">
@@ -1615,19 +1615,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.192</v>
+        <v>0.18</v>
       </c>
       <c r="F9" t="n">
         <v>0.804</v>
       </c>
       <c r="G9" t="n">
-        <v>0.823</v>
+        <v>0.825</v>
       </c>
       <c r="H9" t="n">
         <v>0.119</v>
       </c>
       <c r="I9" t="n">
-        <v>0.113</v>
+        <v>0.11</v>
       </c>
       <c r="J9" t="n">
         <v>0.767</v>
@@ -1690,7 +1690,7 @@
         <v>0.967</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.633</v>
+        <v>0.667</v>
       </c>
       <c r="AE9" t="n">
         <v>0.9330000000000001</v>
@@ -1751,19 +1751,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.484</v>
+        <v>0.528</v>
       </c>
       <c r="F10" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>0.669</v>
+        <v>0.671</v>
       </c>
       <c r="H10" t="n">
         <v>0.17</v>
       </c>
       <c r="I10" t="n">
-        <v>0.177</v>
+        <v>0.174</v>
       </c>
       <c r="J10" t="n">
         <v>0.7</v>
@@ -1826,7 +1826,7 @@
         <v>0.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="AE10" t="n">
         <v>0.767</v>
@@ -1862,7 +1862,7 @@
         <v>0.667</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.484</v>
+        <v>0.528</v>
       </c>
     </row>
     <row r="11">
@@ -1887,19 +1887,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.715</v>
+        <v>0.775</v>
       </c>
       <c r="F11" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>0.669</v>
+        <v>0.671</v>
       </c>
       <c r="H11" t="n">
         <v>0.17</v>
       </c>
       <c r="I11" t="n">
-        <v>0.177</v>
+        <v>0.174</v>
       </c>
       <c r="J11" t="n">
         <v>0.7</v>
@@ -1962,7 +1962,7 @@
         <v>0.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="AE11" t="n">
         <v>0.767</v>
@@ -1998,7 +1998,7 @@
         <v>0.667</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.715</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="12">
@@ -2295,13 +2295,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.0235</v>
+        <v>0.0236</v>
       </c>
       <c r="F14" t="n">
-        <v>0.737</v>
+        <v>0.738</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="H14" t="n">
         <v>0.216</v>
@@ -2322,7 +2322,7 @@
         <v>0.4</v>
       </c>
       <c r="N14" t="n">
-        <v>0.737</v>
+        <v>0.75</v>
       </c>
       <c r="O14" t="n">
         <v>0.792</v>
@@ -2370,7 +2370,7 @@
         <v>0.556</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.8</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="AE14" t="n">
         <v>0.792</v>
@@ -2406,7 +2406,7 @@
         <v>0.5</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.0708</v>
       </c>
     </row>
     <row r="15">
@@ -2434,10 +2434,10 @@
         <v>0.00765</v>
       </c>
       <c r="F15" t="n">
-        <v>0.737</v>
+        <v>0.738</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="H15" t="n">
         <v>0.216</v>
@@ -2458,7 +2458,7 @@
         <v>0.4</v>
       </c>
       <c r="N15" t="n">
-        <v>0.737</v>
+        <v>0.75</v>
       </c>
       <c r="O15" t="n">
         <v>0.792</v>
@@ -2506,7 +2506,7 @@
         <v>0.556</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.8</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="AE15" t="n">
         <v>0.792</v>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.015</v>
+        <v>0.0153</v>
       </c>
       <c r="F16" t="n">
-        <v>0.737</v>
+        <v>0.738</v>
       </c>
       <c r="G16" t="n">
         <v>0.839</v>
@@ -2594,7 +2594,7 @@
         <v>0.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0.737</v>
+        <v>0.75</v>
       </c>
       <c r="O16" t="n">
         <v>0.792</v>
@@ -2642,7 +2642,7 @@
         <v>1</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.833</v>
+        <v>0.842</v>
       </c>
       <c r="AE16" t="n">
         <v>0.875</v>
@@ -2678,7 +2678,7 @@
         <v>0.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.0708</v>
       </c>
     </row>
     <row r="17">
@@ -2706,7 +2706,7 @@
         <v>0.00287</v>
       </c>
       <c r="F17" t="n">
-        <v>0.737</v>
+        <v>0.738</v>
       </c>
       <c r="G17" t="n">
         <v>0.839</v>
@@ -2730,7 +2730,7 @@
         <v>0.4</v>
       </c>
       <c r="N17" t="n">
-        <v>0.737</v>
+        <v>0.75</v>
       </c>
       <c r="O17" t="n">
         <v>0.792</v>
@@ -2778,7 +2778,7 @@
         <v>1</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.833</v>
+        <v>0.842</v>
       </c>
       <c r="AE17" t="n">
         <v>0.875</v>
@@ -3111,13 +3111,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.541</v>
+        <v>0.534</v>
       </c>
       <c r="F20" t="n">
         <v>0.853</v>
       </c>
       <c r="G20" t="n">
-        <v>0.876</v>
+        <v>0.877</v>
       </c>
       <c r="H20" t="n">
         <v>0.13</v>
@@ -3186,7 +3186,7 @@
         <v>1</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.882</v>
+        <v>0.889</v>
       </c>
       <c r="AE20" t="n">
         <v>0.952</v>
@@ -3222,7 +3222,7 @@
         <v>0.667</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.649</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="21">
@@ -3253,7 +3253,7 @@
         <v>0.853</v>
       </c>
       <c r="G21" t="n">
-        <v>0.876</v>
+        <v>0.877</v>
       </c>
       <c r="H21" t="n">
         <v>0.13</v>
@@ -3322,7 +3322,7 @@
         <v>1</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.882</v>
+        <v>0.889</v>
       </c>
       <c r="AE21" t="n">
         <v>0.952</v>
@@ -3383,13 +3383,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.227</v>
+        <v>0.217</v>
       </c>
       <c r="F22" t="n">
         <v>0.8080000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>0.859</v>
+        <v>0.86</v>
       </c>
       <c r="H22" t="n">
         <v>0.156</v>
@@ -3458,7 +3458,7 @@
         <v>1</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.8</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -3494,7 +3494,7 @@
         <v>0.632</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.454</v>
+        <v>0.434</v>
       </c>
     </row>
     <row r="23">
@@ -3525,7 +3525,7 @@
         <v>0.8080000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>0.859</v>
+        <v>0.86</v>
       </c>
       <c r="H23" t="n">
         <v>0.156</v>
@@ -3594,7 +3594,7 @@
         <v>1</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.8</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -3930,16 +3930,16 @@
         <v>0.396</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>0.788</v>
+        <v>0.791</v>
       </c>
       <c r="H26" t="n">
-        <v>0.174</v>
+        <v>0.171</v>
       </c>
       <c r="I26" t="n">
-        <v>0.177</v>
+        <v>0.173</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3954,7 +3954,7 @@
         <v>0.857</v>
       </c>
       <c r="N26" t="n">
-        <v>0.583</v>
+        <v>0.625</v>
       </c>
       <c r="O26" t="n">
         <v>0.905</v>
@@ -4002,7 +4002,7 @@
         <v>0.714</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.5</v>
+        <v>0.542</v>
       </c>
       <c r="AE26" t="n">
         <v>0.905</v>
@@ -4038,7 +4038,7 @@
         <v>0.6</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.45</v>
+        <v>0.475</v>
       </c>
     </row>
     <row r="27">
@@ -4066,16 +4066,16 @@
         <v>0.289</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>0.788</v>
+        <v>0.791</v>
       </c>
       <c r="H27" t="n">
-        <v>0.174</v>
+        <v>0.171</v>
       </c>
       <c r="I27" t="n">
-        <v>0.177</v>
+        <v>0.173</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -4090,7 +4090,7 @@
         <v>0.857</v>
       </c>
       <c r="N27" t="n">
-        <v>0.583</v>
+        <v>0.625</v>
       </c>
       <c r="O27" t="n">
         <v>0.905</v>
@@ -4138,7 +4138,7 @@
         <v>0.714</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.5</v>
+        <v>0.542</v>
       </c>
       <c r="AE27" t="n">
         <v>0.905</v>
@@ -4202,16 +4202,16 @@
         <v>0.07770000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>0.739</v>
+        <v>0.742</v>
       </c>
       <c r="H28" t="n">
-        <v>0.174</v>
+        <v>0.171</v>
       </c>
       <c r="I28" t="n">
-        <v>0.252</v>
+        <v>0.251</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -4226,7 +4226,7 @@
         <v>0.857</v>
       </c>
       <c r="N28" t="n">
-        <v>0.583</v>
+        <v>0.625</v>
       </c>
       <c r="O28" t="n">
         <v>0.905</v>
@@ -4274,7 +4274,7 @@
         <v>0.857</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.625</v>
+        <v>0.667</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -4338,16 +4338,16 @@
         <v>0.0805</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>0.739</v>
+        <v>0.742</v>
       </c>
       <c r="H29" t="n">
-        <v>0.174</v>
+        <v>0.171</v>
       </c>
       <c r="I29" t="n">
-        <v>0.252</v>
+        <v>0.251</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -4362,7 +4362,7 @@
         <v>0.857</v>
       </c>
       <c r="N29" t="n">
-        <v>0.583</v>
+        <v>0.625</v>
       </c>
       <c r="O29" t="n">
         <v>0.905</v>
@@ -4410,7 +4410,7 @@
         <v>0.857</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.625</v>
+        <v>0.667</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -4471,13 +4471,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.00396</v>
+        <v>0.00468</v>
       </c>
       <c r="F30" t="n">
         <v>0.8120000000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>0.632</v>
+        <v>0.634</v>
       </c>
       <c r="H30" t="n">
         <v>0.205</v>
@@ -4546,7 +4546,7 @@
         <v>0.571</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.625</v>
+        <v>0.667</v>
       </c>
       <c r="AE30" t="n">
         <v>0.857</v>
@@ -4582,7 +4582,7 @@
         <v>0.733</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.0238</v>
+        <v>0.0281</v>
       </c>
     </row>
     <row r="31">
@@ -4607,13 +4607,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.0009790000000000001</v>
+        <v>0.00147</v>
       </c>
       <c r="F31" t="n">
         <v>0.8120000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>0.632</v>
+        <v>0.634</v>
       </c>
       <c r="H31" t="n">
         <v>0.205</v>
@@ -4682,7 +4682,7 @@
         <v>0.571</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.625</v>
+        <v>0.667</v>
       </c>
       <c r="AE31" t="n">
         <v>0.857</v>
@@ -4718,7 +4718,7 @@
         <v>0.733</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.00587</v>
+        <v>0.00882</v>
       </c>
     </row>
     <row r="32">
@@ -4743,19 +4743,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.45</v>
+        <v>0.489</v>
       </c>
       <c r="F32" t="n">
         <v>0.8120000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>0.781</v>
+        <v>0.784</v>
       </c>
       <c r="H32" t="n">
         <v>0.205</v>
       </c>
       <c r="I32" t="n">
-        <v>0.203</v>
+        <v>0.202</v>
       </c>
       <c r="J32" t="n">
         <v>0.958</v>
@@ -4818,7 +4818,7 @@
         <v>0.857</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.625</v>
+        <v>0.667</v>
       </c>
       <c r="AE32" t="n">
         <v>0.952</v>
@@ -4854,7 +4854,7 @@
         <v>0.4</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.45</v>
+        <v>0.489</v>
       </c>
     </row>
     <row r="33">
@@ -4879,19 +4879,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.859</v>
+        <v>0.878</v>
       </c>
       <c r="F33" t="n">
         <v>0.8120000000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>0.781</v>
+        <v>0.784</v>
       </c>
       <c r="H33" t="n">
         <v>0.205</v>
       </c>
       <c r="I33" t="n">
-        <v>0.203</v>
+        <v>0.202</v>
       </c>
       <c r="J33" t="n">
         <v>0.958</v>
@@ -4954,7 +4954,7 @@
         <v>0.857</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.625</v>
+        <v>0.667</v>
       </c>
       <c r="AE33" t="n">
         <v>0.952</v>
@@ -4990,7 +4990,7 @@
         <v>0.4</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.859</v>
+        <v>0.878</v>
       </c>
     </row>
     <row r="34">
@@ -5015,19 +5015,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.0174</v>
+        <v>0.0199</v>
       </c>
       <c r="F34" t="n">
         <v>0.641</v>
       </c>
       <c r="G34" t="n">
-        <v>0.512</v>
+        <v>0.515</v>
       </c>
       <c r="H34" t="n">
         <v>0.219</v>
       </c>
       <c r="I34" t="n">
-        <v>0.187</v>
+        <v>0.185</v>
       </c>
       <c r="J34" t="n">
         <v>0.792</v>
@@ -5090,7 +5090,7 @@
         <v>0.571</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.333</v>
+        <v>0.375</v>
       </c>
       <c r="AE34" t="n">
         <v>0.667</v>
@@ -5151,19 +5151,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.0219</v>
+        <v>0.0303</v>
       </c>
       <c r="F35" t="n">
         <v>0.641</v>
       </c>
       <c r="G35" t="n">
-        <v>0.512</v>
+        <v>0.515</v>
       </c>
       <c r="H35" t="n">
         <v>0.219</v>
       </c>
       <c r="I35" t="n">
-        <v>0.187</v>
+        <v>0.185</v>
       </c>
       <c r="J35" t="n">
         <v>0.792</v>
@@ -5226,7 +5226,7 @@
         <v>0.571</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.333</v>
+        <v>0.375</v>
       </c>
       <c r="AE35" t="n">
         <v>0.667</v>
@@ -5262,7 +5262,7 @@
         <v>0.8</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.0458</v>
+        <v>0.0606</v>
       </c>
     </row>
     <row r="36">
@@ -5534,7 +5534,7 @@
         <v>0.4</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.0458</v>
+        <v>0.0606</v>
       </c>
     </row>
   </sheetData>
@@ -5963,10 +5963,10 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
@@ -6177,13 +6177,13 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.737</v>
+        <v>0.75</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>0.709</v>
       </c>
       <c r="X3" t="n">
         <v>1</v>
@@ -6391,13 +6391,13 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.583</v>
+        <v>0.625</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.542</v>
       </c>
       <c r="W4" t="n">
-        <v>0.772</v>
+        <v>0.77</v>
       </c>
       <c r="X4" t="n">
         <v>1</v>
@@ -6605,13 +6605,13 @@
         <v>0.0893</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6</v>
+        <v>0.633</v>
       </c>
       <c r="W5" t="n">
-        <v>0.604</v>
+        <v>0.601</v>
       </c>
       <c r="X5" t="n">
         <v>1</v>
@@ -6819,13 +6819,13 @@
         <v>0.297</v>
       </c>
       <c r="U6" t="n">
-        <v>0.737</v>
+        <v>0.75</v>
       </c>
       <c r="V6" t="n">
-        <v>0.833</v>
+        <v>0.842</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.695</v>
       </c>
       <c r="X6" t="n">
         <v>1</v>
@@ -7033,10 +7033,10 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.583</v>
+        <v>0.625</v>
       </c>
       <c r="V7" t="n">
-        <v>0.625</v>
+        <v>0.667</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
@@ -7250,10 +7250,10 @@
         <v>0.667</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7</v>
+        <v>0.733</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>0.779</v>
       </c>
       <c r="X8" t="n">
         <v>1</v>
@@ -7467,7 +7467,7 @@
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0.489</v>
+        <v>0.487</v>
       </c>
       <c r="X9" t="n">
         <v>1</v>
@@ -7678,7 +7678,7 @@
         <v>0.667</v>
       </c>
       <c r="V10" t="n">
-        <v>0.625</v>
+        <v>0.667</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
@@ -7892,7 +7892,7 @@
         <v>0.667</v>
       </c>
       <c r="V11" t="n">
-        <v>0.633</v>
+        <v>0.667</v>
       </c>
       <c r="W11" t="n">
         <v>1</v>
@@ -8106,7 +8106,7 @@
         <v>0.889</v>
       </c>
       <c r="V12" t="n">
-        <v>0.882</v>
+        <v>0.889</v>
       </c>
       <c r="W12" t="n">
         <v>1</v>
@@ -8320,7 +8320,7 @@
         <v>0.667</v>
       </c>
       <c r="V13" t="n">
-        <v>0.625</v>
+        <v>0.667</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
@@ -8534,7 +8534,7 @@
         <v>0.433</v>
       </c>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="W14" t="n">
         <v>1</v>
@@ -8748,7 +8748,7 @@
         <v>0.769</v>
       </c>
       <c r="V15" t="n">
-        <v>0.8</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="W15" t="n">
         <v>1</v>
@@ -8962,10 +8962,10 @@
         <v>0.417</v>
       </c>
       <c r="V16" t="n">
-        <v>0.333</v>
+        <v>0.375</v>
       </c>
       <c r="W16" t="n">
-        <v>0.766</v>
+        <v>1</v>
       </c>
       <c r="X16" t="n">
         <v>1</v>

--- a/eval/results/statistical_tests_new30.xlsx
+++ b/eval/results/statistical_tests_new30.xlsx
@@ -503,22 +503,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.0318</v>
+        <v>0.0626</v>
       </c>
       <c r="F2" t="n">
-        <v>0.74</v>
+        <v>0.767</v>
       </c>
       <c r="G2" t="n">
-        <v>0.779</v>
+        <v>0.802</v>
       </c>
       <c r="H2" t="n">
-        <v>0.165</v>
+        <v>0.158</v>
       </c>
       <c r="I2" t="n">
-        <v>0.159</v>
+        <v>0.145</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0646</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="3">
@@ -543,22 +543,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.031</v>
+        <v>0.0698</v>
       </c>
       <c r="F3" t="n">
-        <v>0.74</v>
+        <v>0.767</v>
       </c>
       <c r="G3" t="n">
-        <v>0.779</v>
+        <v>0.802</v>
       </c>
       <c r="H3" t="n">
-        <v>0.165</v>
+        <v>0.158</v>
       </c>
       <c r="I3" t="n">
-        <v>0.159</v>
+        <v>0.145</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0742</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="4">
@@ -583,22 +583,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.143</v>
+        <v>0.504</v>
       </c>
       <c r="F4" t="n">
-        <v>0.74</v>
+        <v>0.767</v>
       </c>
       <c r="G4" t="n">
-        <v>0.781</v>
+        <v>0.783</v>
       </c>
       <c r="H4" t="n">
-        <v>0.165</v>
+        <v>0.158</v>
       </c>
       <c r="I4" t="n">
-        <v>0.139</v>
+        <v>0.137</v>
       </c>
       <c r="J4" t="n">
-        <v>0.214</v>
+        <v>0.504</v>
       </c>
     </row>
     <row r="5">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.217</v>
+        <v>0.849</v>
       </c>
       <c r="F5" t="n">
-        <v>0.74</v>
+        <v>0.767</v>
       </c>
       <c r="G5" t="n">
-        <v>0.781</v>
+        <v>0.783</v>
       </c>
       <c r="H5" t="n">
-        <v>0.165</v>
+        <v>0.158</v>
       </c>
       <c r="I5" t="n">
-        <v>0.139</v>
+        <v>0.137</v>
       </c>
       <c r="J5" t="n">
-        <v>0.26</v>
+        <v>0.849</v>
       </c>
     </row>
     <row r="6">
@@ -666,19 +666,19 @@
         <v>0.0319</v>
       </c>
       <c r="F6" t="n">
-        <v>0.804</v>
+        <v>0.806</v>
       </c>
       <c r="G6" t="n">
-        <v>0.762</v>
+        <v>0.765</v>
       </c>
       <c r="H6" t="n">
-        <v>0.119</v>
+        <v>0.117</v>
       </c>
       <c r="I6" t="n">
-        <v>0.113</v>
+        <v>0.11</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0646</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="7">
@@ -706,19 +706,19 @@
         <v>0.0311</v>
       </c>
       <c r="F7" t="n">
-        <v>0.804</v>
+        <v>0.806</v>
       </c>
       <c r="G7" t="n">
-        <v>0.762</v>
+        <v>0.765</v>
       </c>
       <c r="H7" t="n">
-        <v>0.119</v>
+        <v>0.117</v>
       </c>
       <c r="I7" t="n">
-        <v>0.113</v>
+        <v>0.11</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0742</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="8">
@@ -746,19 +746,19 @@
         <v>0.283</v>
       </c>
       <c r="F8" t="n">
-        <v>0.804</v>
+        <v>0.806</v>
       </c>
       <c r="G8" t="n">
-        <v>0.825</v>
+        <v>0.827</v>
       </c>
       <c r="H8" t="n">
-        <v>0.119</v>
+        <v>0.117</v>
       </c>
       <c r="I8" t="n">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="J8" t="n">
-        <v>0.34</v>
+        <v>0.424</v>
       </c>
     </row>
     <row r="9">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.18</v>
+        <v>0.166</v>
       </c>
       <c r="F9" t="n">
-        <v>0.804</v>
+        <v>0.806</v>
       </c>
       <c r="G9" t="n">
-        <v>0.825</v>
+        <v>0.827</v>
       </c>
       <c r="H9" t="n">
-        <v>0.119</v>
+        <v>0.117</v>
       </c>
       <c r="I9" t="n">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="J9" t="n">
-        <v>0.26</v>
+        <v>0.249</v>
       </c>
     </row>
     <row r="10">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.528</v>
+        <v>0.488</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.694</v>
       </c>
       <c r="G10" t="n">
-        <v>0.671</v>
+        <v>0.673</v>
       </c>
       <c r="H10" t="n">
-        <v>0.17</v>
+        <v>0.165</v>
       </c>
       <c r="I10" t="n">
-        <v>0.174</v>
+        <v>0.171</v>
       </c>
       <c r="J10" t="n">
-        <v>0.528</v>
+        <v>0.504</v>
       </c>
     </row>
     <row r="11">
@@ -863,22 +863,22 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.775</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.694</v>
       </c>
       <c r="G11" t="n">
-        <v>0.671</v>
+        <v>0.673</v>
       </c>
       <c r="H11" t="n">
-        <v>0.17</v>
+        <v>0.165</v>
       </c>
       <c r="I11" t="n">
-        <v>0.174</v>
+        <v>0.171</v>
       </c>
       <c r="J11" t="n">
-        <v>0.775</v>
+        <v>0.827</v>
       </c>
     </row>
     <row r="12">
@@ -903,22 +903,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.0323</v>
+        <v>0.0374</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.694</v>
       </c>
       <c r="G12" t="n">
-        <v>0.762</v>
+        <v>0.765</v>
       </c>
       <c r="H12" t="n">
-        <v>0.17</v>
+        <v>0.165</v>
       </c>
       <c r="I12" t="n">
-        <v>0.139</v>
+        <v>0.136</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0646</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="13">
@@ -943,22 +943,22 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.0371</v>
+        <v>0.0449</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.694</v>
       </c>
       <c r="G13" t="n">
-        <v>0.762</v>
+        <v>0.765</v>
       </c>
       <c r="H13" t="n">
-        <v>0.17</v>
+        <v>0.165</v>
       </c>
       <c r="I13" t="n">
-        <v>0.139</v>
+        <v>0.136</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0742</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="14">
@@ -983,22 +983,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.0236</v>
+        <v>0.0375</v>
       </c>
       <c r="F14" t="n">
-        <v>0.738</v>
+        <v>0.761</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.828</v>
       </c>
       <c r="H14" t="n">
-        <v>0.216</v>
+        <v>0.21</v>
       </c>
       <c r="I14" t="n">
-        <v>0.158</v>
+        <v>0.152</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0708</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="15">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.00765</v>
+        <v>0.0229</v>
       </c>
       <c r="F15" t="n">
-        <v>0.738</v>
+        <v>0.761</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.828</v>
       </c>
       <c r="H15" t="n">
-        <v>0.216</v>
+        <v>0.21</v>
       </c>
       <c r="I15" t="n">
-        <v>0.158</v>
+        <v>0.152</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0229</v>
+        <v>0.0562</v>
       </c>
     </row>
     <row r="16">
@@ -1063,22 +1063,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.0153</v>
+        <v>0.037</v>
       </c>
       <c r="F16" t="n">
-        <v>0.738</v>
+        <v>0.761</v>
       </c>
       <c r="G16" t="n">
-        <v>0.839</v>
+        <v>0.84</v>
       </c>
       <c r="H16" t="n">
-        <v>0.216</v>
+        <v>0.21</v>
       </c>
       <c r="I16" t="n">
         <v>0.192</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0708</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="17">
@@ -1103,22 +1103,22 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.00287</v>
+        <v>0.00604</v>
       </c>
       <c r="F17" t="n">
-        <v>0.738</v>
+        <v>0.761</v>
       </c>
       <c r="G17" t="n">
-        <v>0.839</v>
+        <v>0.84</v>
       </c>
       <c r="H17" t="n">
-        <v>0.216</v>
+        <v>0.21</v>
       </c>
       <c r="I17" t="n">
         <v>0.192</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0172</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="18">
@@ -1143,7 +1143,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.65</v>
+        <v>0.652</v>
       </c>
       <c r="F18" t="n">
         <v>0.853</v>
@@ -1158,7 +1158,7 @@
         <v>0.186</v>
       </c>
       <c r="J18" t="n">
-        <v>0.65</v>
+        <v>0.652</v>
       </c>
     </row>
     <row r="19">
@@ -1303,13 +1303,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.217</v>
+        <v>0.222</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>0.86</v>
+        <v>0.861</v>
       </c>
       <c r="H22" t="n">
         <v>0.156</v>
@@ -1318,7 +1318,7 @@
         <v>0.175</v>
       </c>
       <c r="J22" t="n">
-        <v>0.434</v>
+        <v>0.444</v>
       </c>
     </row>
     <row r="23">
@@ -1346,10 +1346,10 @@
         <v>0.0281</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>0.86</v>
+        <v>0.861</v>
       </c>
       <c r="H23" t="n">
         <v>0.156</v>
@@ -1383,13 +1383,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.31</v>
+        <v>0.299</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>0.779</v>
+        <v>0.78</v>
       </c>
       <c r="H24" t="n">
         <v>0.156</v>
@@ -1398,7 +1398,7 @@
         <v>0.188</v>
       </c>
       <c r="J24" t="n">
-        <v>0.465</v>
+        <v>0.449</v>
       </c>
     </row>
     <row r="25">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.308</v>
+        <v>0.272</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>0.779</v>
+        <v>0.78</v>
       </c>
       <c r="H25" t="n">
         <v>0.156</v>
@@ -1438,7 +1438,7 @@
         <v>0.188</v>
       </c>
       <c r="J25" t="n">
-        <v>0.308</v>
+        <v>0.272</v>
       </c>
     </row>
     <row r="26">
@@ -1463,22 +1463,22 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.396</v>
+        <v>0.61</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="G26" t="n">
-        <v>0.791</v>
+        <v>0.806</v>
       </c>
       <c r="H26" t="n">
         <v>0.171</v>
       </c>
       <c r="I26" t="n">
-        <v>0.173</v>
+        <v>0.167</v>
       </c>
       <c r="J26" t="n">
-        <v>0.475</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="27">
@@ -1503,22 +1503,22 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.289</v>
+        <v>0.35</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="G27" t="n">
-        <v>0.791</v>
+        <v>0.806</v>
       </c>
       <c r="H27" t="n">
         <v>0.171</v>
       </c>
       <c r="I27" t="n">
-        <v>0.173</v>
+        <v>0.167</v>
       </c>
       <c r="J27" t="n">
-        <v>0.347</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="28">
@@ -1543,22 +1543,22 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.0538</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="G28" t="n">
-        <v>0.742</v>
+        <v>0.744</v>
       </c>
       <c r="H28" t="n">
         <v>0.171</v>
       </c>
       <c r="I28" t="n">
-        <v>0.251</v>
+        <v>0.25</v>
       </c>
       <c r="J28" t="n">
-        <v>0.117</v>
+        <v>0.08069999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -1583,22 +1583,22 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.0805</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="G29" t="n">
-        <v>0.742</v>
+        <v>0.744</v>
       </c>
       <c r="H29" t="n">
         <v>0.171</v>
       </c>
       <c r="I29" t="n">
-        <v>0.251</v>
+        <v>0.25</v>
       </c>
       <c r="J29" t="n">
-        <v>0.121</v>
+        <v>0.104</v>
       </c>
     </row>
     <row r="30">
@@ -1626,16 +1626,16 @@
         <v>0.00468</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>0.634</v>
+        <v>0.637</v>
       </c>
       <c r="H30" t="n">
-        <v>0.205</v>
+        <v>0.203</v>
       </c>
       <c r="I30" t="n">
-        <v>0.223</v>
+        <v>0.222</v>
       </c>
       <c r="J30" t="n">
         <v>0.0281</v>
@@ -1666,16 +1666,16 @@
         <v>0.00147</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>0.634</v>
+        <v>0.637</v>
       </c>
       <c r="H31" t="n">
-        <v>0.205</v>
+        <v>0.203</v>
       </c>
       <c r="I31" t="n">
-        <v>0.223</v>
+        <v>0.222</v>
       </c>
       <c r="J31" t="n">
         <v>0.00882</v>
@@ -1706,19 +1706,19 @@
         <v>0.489</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>0.784</v>
+        <v>0.787</v>
       </c>
       <c r="H32" t="n">
-        <v>0.205</v>
+        <v>0.203</v>
       </c>
       <c r="I32" t="n">
         <v>0.202</v>
       </c>
       <c r="J32" t="n">
-        <v>0.489</v>
+        <v>0.587</v>
       </c>
     </row>
     <row r="33">
@@ -1746,13 +1746,13 @@
         <v>0.878</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>0.784</v>
+        <v>0.787</v>
       </c>
       <c r="H33" t="n">
-        <v>0.205</v>
+        <v>0.203</v>
       </c>
       <c r="I33" t="n">
         <v>0.202</v>
@@ -1783,22 +1783,22 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.0199</v>
+        <v>0.018</v>
       </c>
       <c r="F34" t="n">
-        <v>0.641</v>
+        <v>0.646</v>
       </c>
       <c r="G34" t="n">
-        <v>0.515</v>
+        <v>0.518</v>
       </c>
       <c r="H34" t="n">
-        <v>0.219</v>
+        <v>0.214</v>
       </c>
       <c r="I34" t="n">
-        <v>0.185</v>
+        <v>0.182</v>
       </c>
       <c r="J34" t="n">
-        <v>0.0464</v>
+        <v>0.0508</v>
       </c>
     </row>
     <row r="35">
@@ -1826,16 +1826,16 @@
         <v>0.0303</v>
       </c>
       <c r="F35" t="n">
-        <v>0.641</v>
+        <v>0.646</v>
       </c>
       <c r="G35" t="n">
-        <v>0.515</v>
+        <v>0.518</v>
       </c>
       <c r="H35" t="n">
-        <v>0.219</v>
+        <v>0.214</v>
       </c>
       <c r="I35" t="n">
-        <v>0.185</v>
+        <v>0.182</v>
       </c>
       <c r="J35" t="n">
         <v>0.0606</v>
@@ -1863,22 +1863,22 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.0232</v>
+        <v>0.0254</v>
       </c>
       <c r="F36" t="n">
-        <v>0.641</v>
+        <v>0.646</v>
       </c>
       <c r="G36" t="n">
-        <v>0.787</v>
+        <v>0.79</v>
       </c>
       <c r="H36" t="n">
-        <v>0.219</v>
+        <v>0.214</v>
       </c>
       <c r="I36" t="n">
-        <v>0.201</v>
+        <v>0.199</v>
       </c>
       <c r="J36" t="n">
-        <v>0.0464</v>
+        <v>0.0508</v>
       </c>
     </row>
     <row r="37">
@@ -1903,19 +1903,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.0229</v>
+        <v>0.0281</v>
       </c>
       <c r="F37" t="n">
-        <v>0.641</v>
+        <v>0.646</v>
       </c>
       <c r="G37" t="n">
-        <v>0.787</v>
+        <v>0.79</v>
       </c>
       <c r="H37" t="n">
-        <v>0.219</v>
+        <v>0.214</v>
       </c>
       <c r="I37" t="n">
-        <v>0.201</v>
+        <v>0.199</v>
       </c>
       <c r="J37" t="n">
         <v>0.0606</v>
@@ -2118,13 +2118,13 @@
         <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>0.667</v>
+        <v>0.733</v>
       </c>
       <c r="G5" t="n">
         <v>0.8</v>
       </c>
       <c r="H5" t="n">
-        <v>0.382</v>
+        <v>0.761</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -2158,7 +2158,7 @@
         <v>0.533</v>
       </c>
       <c r="G6" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
@@ -2192,10 +2192,10 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>0.767</v>
+        <v>0.9</v>
       </c>
       <c r="G7" t="n">
-        <v>0.767</v>
+        <v>0.867</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
@@ -2229,10 +2229,10 @@
         <v>7</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G8" t="n">
-        <v>0.733</v>
+        <v>0.767</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
@@ -2377,13 +2377,13 @@
         <v>11</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.633</v>
       </c>
       <c r="G12" t="n">
-        <v>0.667</v>
+        <v>0.767</v>
       </c>
       <c r="H12" t="n">
-        <v>0.596</v>
+        <v>0.399</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
@@ -2525,13 +2525,13 @@
         <v>15</v>
       </c>
       <c r="F16" t="n">
-        <v>0.633</v>
+        <v>0.667</v>
       </c>
       <c r="G16" t="n">
-        <v>0.733</v>
+        <v>0.767</v>
       </c>
       <c r="H16" t="n">
-        <v>0.58</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
@@ -2562,13 +2562,13 @@
         <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>0.433</v>
+        <v>0.467</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>0.796</v>
+        <v>0.606</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
@@ -2710,13 +2710,13 @@
         <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4</v>
+        <v>0.462</v>
       </c>
       <c r="G21" t="n">
         <v>0.556</v>
       </c>
       <c r="H21" t="n">
-        <v>0.675</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
@@ -2750,10 +2750,10 @@
         <v>0.75</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.867</v>
       </c>
       <c r="H22" t="n">
-        <v>0.709</v>
+        <v>0.672</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
@@ -2784,10 +2784,10 @@
         <v>6</v>
       </c>
       <c r="F23" t="n">
-        <v>0.792</v>
+        <v>0.909</v>
       </c>
       <c r="G23" t="n">
-        <v>0.792</v>
+        <v>0.87</v>
       </c>
       <c r="H23" t="n">
         <v>1</v>
@@ -2821,13 +2821,13 @@
         <v>7</v>
       </c>
       <c r="F24" t="n">
-        <v>0.708</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>0.762</v>
+        <v>0.8</v>
       </c>
       <c r="H24" t="n">
-        <v>0.746</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
@@ -2969,13 +2969,13 @@
         <v>11</v>
       </c>
       <c r="F28" t="n">
-        <v>0.739</v>
+        <v>0.76</v>
       </c>
       <c r="G28" t="n">
-        <v>0.889</v>
+        <v>0.905</v>
       </c>
       <c r="H28" t="n">
-        <v>0.429</v>
+        <v>0.26</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
@@ -3117,13 +3117,13 @@
         <v>15</v>
       </c>
       <c r="F32" t="n">
-        <v>0.696</v>
+        <v>0.727</v>
       </c>
       <c r="G32" t="n">
-        <v>0.773</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>0.738</v>
+        <v>0.721</v>
       </c>
       <c r="I32" t="n">
         <v>1</v>
@@ -3154,13 +3154,13 @@
         <v>16</v>
       </c>
       <c r="F33" t="n">
-        <v>0.429</v>
+        <v>0.462</v>
       </c>
       <c r="G33" t="n">
-        <v>0.5</v>
+        <v>0.556</v>
       </c>
       <c r="H33" t="n">
-        <v>0.735</v>
+        <v>0.722</v>
       </c>
       <c r="I33" t="n">
         <v>1</v>
@@ -3376,10 +3376,10 @@
         <v>6</v>
       </c>
       <c r="F39" t="n">
-        <v>0.905</v>
+        <v>0.952</v>
       </c>
       <c r="G39" t="n">
-        <v>0.905</v>
+        <v>0.952</v>
       </c>
       <c r="H39" t="n">
         <v>1</v>
@@ -3561,10 +3561,10 @@
         <v>11</v>
       </c>
       <c r="F44" t="n">
-        <v>0.708</v>
+        <v>0.792</v>
       </c>
       <c r="G44" t="n">
-        <v>0.667</v>
+        <v>0.792</v>
       </c>
       <c r="H44" t="n">
         <v>1</v>
@@ -3749,10 +3749,10 @@
         <v>0.4</v>
       </c>
       <c r="G49" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="H49" t="n">
-        <v>0.466</v>
+        <v>0.272</v>
       </c>
       <c r="I49" t="n">
         <v>1</v>
@@ -3894,16 +3894,16 @@
         <v>4</v>
       </c>
       <c r="F53" t="n">
-        <v>0.667</v>
+        <v>0.733</v>
       </c>
       <c r="G53" t="n">
         <v>0.967</v>
       </c>
       <c r="H53" t="n">
-        <v>0.00558</v>
+        <v>0.0257</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0893</v>
+        <v>0.411</v>
       </c>
     </row>
     <row r="54">
@@ -3968,13 +3968,13 @@
         <v>6</v>
       </c>
       <c r="F55" t="n">
-        <v>0.767</v>
+        <v>0.9</v>
       </c>
       <c r="G55" t="n">
         <v>0.9</v>
       </c>
       <c r="H55" t="n">
-        <v>0.299</v>
+        <v>1</v>
       </c>
       <c r="I55" t="n">
         <v>1</v>
@@ -4005,13 +4005,13 @@
         <v>7</v>
       </c>
       <c r="F56" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G56" t="n">
         <v>0.733</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>0.761</v>
       </c>
       <c r="I56" t="n">
         <v>1</v>
@@ -4153,13 +4153,13 @@
         <v>11</v>
       </c>
       <c r="F60" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.633</v>
       </c>
       <c r="G60" t="n">
-        <v>0.633</v>
+        <v>0.667</v>
       </c>
       <c r="H60" t="n">
-        <v>0.792</v>
+        <v>1</v>
       </c>
       <c r="I60" t="n">
         <v>1</v>
@@ -4301,7 +4301,7 @@
         <v>15</v>
       </c>
       <c r="F64" t="n">
-        <v>0.633</v>
+        <v>0.667</v>
       </c>
       <c r="G64" t="n">
         <v>0.633</v>
@@ -4338,13 +4338,13 @@
         <v>16</v>
       </c>
       <c r="F65" t="n">
-        <v>0.433</v>
+        <v>0.467</v>
       </c>
       <c r="G65" t="n">
         <v>0.5</v>
       </c>
       <c r="H65" t="n">
-        <v>0.796</v>
+        <v>1</v>
       </c>
       <c r="I65" t="n">
         <v>1</v>
@@ -4486,16 +4486,16 @@
         <v>4</v>
       </c>
       <c r="F69" t="n">
-        <v>0.4</v>
+        <v>0.462</v>
       </c>
       <c r="G69" t="n">
         <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>0.0186</v>
+        <v>0.0436</v>
       </c>
       <c r="I69" t="n">
-        <v>0.297</v>
+        <v>0.698</v>
       </c>
     </row>
     <row r="70">
@@ -4560,13 +4560,13 @@
         <v>6</v>
       </c>
       <c r="F71" t="n">
-        <v>0.792</v>
+        <v>0.909</v>
       </c>
       <c r="G71" t="n">
         <v>0.875</v>
       </c>
       <c r="H71" t="n">
-        <v>0.701</v>
+        <v>1</v>
       </c>
       <c r="I71" t="n">
         <v>1</v>
@@ -4597,13 +4597,13 @@
         <v>7</v>
       </c>
       <c r="F72" t="n">
-        <v>0.708</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G72" t="n">
         <v>0.824</v>
       </c>
       <c r="H72" t="n">
-        <v>0.48</v>
+        <v>1</v>
       </c>
       <c r="I72" t="n">
         <v>1</v>
@@ -4745,13 +4745,13 @@
         <v>11</v>
       </c>
       <c r="F76" t="n">
-        <v>0.739</v>
+        <v>0.76</v>
       </c>
       <c r="G76" t="n">
-        <v>0.842</v>
+        <v>0.85</v>
       </c>
       <c r="H76" t="n">
-        <v>0.477</v>
+        <v>0.71</v>
       </c>
       <c r="I76" t="n">
         <v>1</v>
@@ -4893,13 +4893,13 @@
         <v>15</v>
       </c>
       <c r="F80" t="n">
-        <v>0.696</v>
+        <v>0.727</v>
       </c>
       <c r="G80" t="n">
         <v>0.909</v>
       </c>
       <c r="H80" t="n">
-        <v>0.227</v>
+        <v>0.378</v>
       </c>
       <c r="I80" t="n">
         <v>1</v>
@@ -4930,7 +4930,7 @@
         <v>16</v>
       </c>
       <c r="F81" t="n">
-        <v>0.429</v>
+        <v>0.462</v>
       </c>
       <c r="G81" t="n">
         <v>0.5</v>
@@ -5152,13 +5152,13 @@
         <v>6</v>
       </c>
       <c r="F87" t="n">
-        <v>0.905</v>
+        <v>0.952</v>
       </c>
       <c r="G87" t="n">
         <v>1</v>
       </c>
       <c r="H87" t="n">
-        <v>0.488</v>
+        <v>1</v>
       </c>
       <c r="I87" t="n">
         <v>1</v>
@@ -5337,13 +5337,13 @@
         <v>11</v>
       </c>
       <c r="F92" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="G92" t="n">
         <v>0.708</v>
       </c>
-      <c r="G92" t="n">
-        <v>0.667</v>
-      </c>
       <c r="H92" t="n">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="I92" t="n">
         <v>1</v>
@@ -5929,13 +5929,13 @@
         <v>11</v>
       </c>
       <c r="F108" t="n">
-        <v>0.667</v>
+        <v>0.7</v>
       </c>
       <c r="G108" t="n">
-        <v>0.6</v>
+        <v>0.633</v>
       </c>
       <c r="H108" t="n">
-        <v>0.789</v>
+        <v>0.785</v>
       </c>
       <c r="I108" t="n">
         <v>1</v>
@@ -6521,10 +6521,10 @@
         <v>11</v>
       </c>
       <c r="F124" t="n">
-        <v>0.889</v>
+        <v>0.895</v>
       </c>
       <c r="G124" t="n">
-        <v>0.929</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="H124" t="n">
         <v>1</v>
@@ -7113,13 +7113,13 @@
         <v>11</v>
       </c>
       <c r="F140" t="n">
-        <v>0.667</v>
+        <v>0.708</v>
       </c>
       <c r="G140" t="n">
-        <v>0.542</v>
+        <v>0.583</v>
       </c>
       <c r="H140" t="n">
-        <v>0.556</v>
+        <v>0.547</v>
       </c>
       <c r="I140" t="n">
         <v>1</v>
@@ -7705,13 +7705,13 @@
         <v>11</v>
       </c>
       <c r="F156" t="n">
-        <v>0.667</v>
+        <v>0.7</v>
       </c>
       <c r="G156" t="n">
-        <v>0.733</v>
+        <v>0.767</v>
       </c>
       <c r="H156" t="n">
-        <v>0.779</v>
+        <v>0.771</v>
       </c>
       <c r="I156" t="n">
         <v>1</v>
@@ -8297,10 +8297,10 @@
         <v>11</v>
       </c>
       <c r="F172" t="n">
-        <v>0.889</v>
+        <v>0.895</v>
       </c>
       <c r="G172" t="n">
-        <v>0.864</v>
+        <v>0.87</v>
       </c>
       <c r="H172" t="n">
         <v>1</v>
@@ -8889,13 +8889,13 @@
         <v>11</v>
       </c>
       <c r="F188" t="n">
-        <v>0.667</v>
+        <v>0.708</v>
       </c>
       <c r="G188" t="n">
-        <v>0.792</v>
+        <v>0.833</v>
       </c>
       <c r="H188" t="n">
-        <v>0.517</v>
+        <v>0.494</v>
       </c>
       <c r="I188" t="n">
         <v>1</v>
@@ -9481,13 +9481,13 @@
         <v>11</v>
       </c>
       <c r="F204" t="n">
-        <v>0.467</v>
+        <v>0.533</v>
       </c>
       <c r="G204" t="n">
-        <v>0.4</v>
+        <v>0.433</v>
       </c>
       <c r="H204" t="n">
-        <v>0.795</v>
+        <v>0.606</v>
       </c>
       <c r="I204" t="n">
         <v>1</v>
@@ -10073,10 +10073,10 @@
         <v>11</v>
       </c>
       <c r="F220" t="n">
-        <v>0.833</v>
+        <v>0.857</v>
       </c>
       <c r="G220" t="n">
-        <v>0.875</v>
+        <v>0.889</v>
       </c>
       <c r="H220" t="n">
         <v>1</v>
@@ -10665,13 +10665,13 @@
         <v>11</v>
       </c>
       <c r="F236" t="n">
-        <v>0.417</v>
+        <v>0.5</v>
       </c>
       <c r="G236" t="n">
-        <v>0.292</v>
+        <v>0.333</v>
       </c>
       <c r="H236" t="n">
-        <v>0.547</v>
+        <v>0.38</v>
       </c>
       <c r="I236" t="n">
         <v>1</v>
@@ -11257,13 +11257,13 @@
         <v>11</v>
       </c>
       <c r="F252" t="n">
-        <v>0.467</v>
+        <v>0.533</v>
       </c>
       <c r="G252" t="n">
-        <v>0.533</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H252" t="n">
-        <v>0.797</v>
+        <v>1</v>
       </c>
       <c r="I252" t="n">
         <v>1</v>
@@ -11849,10 +11849,10 @@
         <v>11</v>
       </c>
       <c r="F268" t="n">
-        <v>0.833</v>
+        <v>0.857</v>
       </c>
       <c r="G268" t="n">
-        <v>0.778</v>
+        <v>0.789</v>
       </c>
       <c r="H268" t="n">
         <v>1</v>
@@ -12413,7 +12413,7 @@
         <v>0.358</v>
       </c>
       <c r="I283" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.716</v>
       </c>
     </row>
     <row r="284">
@@ -12441,16 +12441,16 @@
         <v>11</v>
       </c>
       <c r="F284" t="n">
-        <v>0.417</v>
+        <v>0.5</v>
       </c>
       <c r="G284" t="n">
-        <v>0.583</v>
+        <v>0.625</v>
       </c>
       <c r="H284" t="n">
-        <v>0.387</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="I284" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.898</v>
       </c>
     </row>
     <row r="285">
@@ -12598,7 +12598,7 @@
         <v>0.451</v>
       </c>
       <c r="I288" t="n">
-        <v>0.721</v>
+        <v>0.801</v>
       </c>
     </row>
     <row r="289">

--- a/eval/results/statistical_tests_new30.xlsx
+++ b/eval/results/statistical_tests_new30.xlsx
@@ -503,22 +503,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.0626</v>
+        <v>0.132</v>
       </c>
       <c r="F2" t="n">
-        <v>0.767</v>
+        <v>0.823</v>
       </c>
       <c r="G2" t="n">
-        <v>0.802</v>
+        <v>0.854</v>
       </c>
       <c r="H2" t="n">
-        <v>0.158</v>
+        <v>0.133</v>
       </c>
       <c r="I2" t="n">
-        <v>0.145</v>
+        <v>0.105</v>
       </c>
       <c r="J2" t="n">
-        <v>0.125</v>
+        <v>0.198</v>
       </c>
     </row>
     <row r="3">
@@ -543,22 +543,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.0698</v>
+        <v>0.213</v>
       </c>
       <c r="F3" t="n">
-        <v>0.767</v>
+        <v>0.823</v>
       </c>
       <c r="G3" t="n">
-        <v>0.802</v>
+        <v>0.854</v>
       </c>
       <c r="H3" t="n">
-        <v>0.158</v>
+        <v>0.133</v>
       </c>
       <c r="I3" t="n">
-        <v>0.145</v>
+        <v>0.105</v>
       </c>
       <c r="J3" t="n">
-        <v>0.14</v>
+        <v>0.256</v>
       </c>
     </row>
     <row r="4">
@@ -583,22 +583,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.504</v>
+        <v>0.0165</v>
       </c>
       <c r="F4" t="n">
-        <v>0.767</v>
+        <v>0.823</v>
       </c>
       <c r="G4" t="n">
         <v>0.783</v>
       </c>
       <c r="H4" t="n">
-        <v>0.158</v>
+        <v>0.133</v>
       </c>
       <c r="I4" t="n">
-        <v>0.137</v>
+        <v>0.153</v>
       </c>
       <c r="J4" t="n">
-        <v>0.504</v>
+        <v>0.099</v>
       </c>
     </row>
     <row r="5">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.849</v>
+        <v>0.016</v>
       </c>
       <c r="F5" t="n">
-        <v>0.767</v>
+        <v>0.823</v>
       </c>
       <c r="G5" t="n">
         <v>0.783</v>
       </c>
       <c r="H5" t="n">
-        <v>0.158</v>
+        <v>0.133</v>
       </c>
       <c r="I5" t="n">
-        <v>0.137</v>
+        <v>0.153</v>
       </c>
       <c r="J5" t="n">
-        <v>0.849</v>
+        <v>0.096</v>
       </c>
     </row>
     <row r="6">
@@ -663,22 +663,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.0319</v>
+        <v>0.0506</v>
       </c>
       <c r="F6" t="n">
-        <v>0.806</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>0.765</v>
+        <v>0.771</v>
       </c>
       <c r="H6" t="n">
-        <v>0.117</v>
+        <v>0.125</v>
       </c>
       <c r="I6" t="n">
-        <v>0.11</v>
+        <v>0.111</v>
       </c>
       <c r="J6" t="n">
-        <v>0.112</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="7">
@@ -703,22 +703,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.0311</v>
+        <v>0.047</v>
       </c>
       <c r="F7" t="n">
-        <v>0.806</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>0.765</v>
+        <v>0.771</v>
       </c>
       <c r="H7" t="n">
-        <v>0.117</v>
+        <v>0.125</v>
       </c>
       <c r="I7" t="n">
-        <v>0.11</v>
+        <v>0.111</v>
       </c>
       <c r="J7" t="n">
-        <v>0.135</v>
+        <v>0.0984</v>
       </c>
     </row>
     <row r="8">
@@ -743,22 +743,22 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.283</v>
+        <v>0.227</v>
       </c>
       <c r="F8" t="n">
-        <v>0.806</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>0.827</v>
+        <v>0.838</v>
       </c>
       <c r="H8" t="n">
-        <v>0.117</v>
+        <v>0.125</v>
       </c>
       <c r="I8" t="n">
-        <v>0.108</v>
+        <v>0.111</v>
       </c>
       <c r="J8" t="n">
-        <v>0.424</v>
+        <v>0.272</v>
       </c>
     </row>
     <row r="9">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.166</v>
+        <v>0.153</v>
       </c>
       <c r="F9" t="n">
-        <v>0.806</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>0.827</v>
+        <v>0.838</v>
       </c>
       <c r="H9" t="n">
-        <v>0.117</v>
+        <v>0.125</v>
       </c>
       <c r="I9" t="n">
-        <v>0.108</v>
+        <v>0.111</v>
       </c>
       <c r="J9" t="n">
-        <v>0.249</v>
+        <v>0.229</v>
       </c>
     </row>
     <row r="10">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.488</v>
+        <v>0.453</v>
       </c>
       <c r="F10" t="n">
-        <v>0.694</v>
+        <v>0.698</v>
       </c>
       <c r="G10" t="n">
-        <v>0.673</v>
+        <v>0.675</v>
       </c>
       <c r="H10" t="n">
-        <v>0.165</v>
+        <v>0.166</v>
       </c>
       <c r="I10" t="n">
-        <v>0.171</v>
+        <v>0.173</v>
       </c>
       <c r="J10" t="n">
-        <v>0.504</v>
+        <v>0.453</v>
       </c>
     </row>
     <row r="11">
@@ -863,22 +863,22 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.607</v>
       </c>
       <c r="F11" t="n">
-        <v>0.694</v>
+        <v>0.698</v>
       </c>
       <c r="G11" t="n">
-        <v>0.673</v>
+        <v>0.675</v>
       </c>
       <c r="H11" t="n">
-        <v>0.165</v>
+        <v>0.166</v>
       </c>
       <c r="I11" t="n">
-        <v>0.171</v>
+        <v>0.173</v>
       </c>
       <c r="J11" t="n">
-        <v>0.827</v>
+        <v>0.607</v>
       </c>
     </row>
     <row r="12">
@@ -903,22 +903,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.0374</v>
+        <v>0.0448</v>
       </c>
       <c r="F12" t="n">
-        <v>0.694</v>
+        <v>0.698</v>
       </c>
       <c r="G12" t="n">
-        <v>0.765</v>
+        <v>0.767</v>
       </c>
       <c r="H12" t="n">
-        <v>0.165</v>
+        <v>0.166</v>
       </c>
       <c r="I12" t="n">
-        <v>0.136</v>
+        <v>0.143</v>
       </c>
       <c r="J12" t="n">
-        <v>0.112</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="13">
@@ -943,22 +943,22 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.0449</v>
+        <v>0.0492</v>
       </c>
       <c r="F13" t="n">
-        <v>0.694</v>
+        <v>0.698</v>
       </c>
       <c r="G13" t="n">
-        <v>0.765</v>
+        <v>0.767</v>
       </c>
       <c r="H13" t="n">
-        <v>0.165</v>
+        <v>0.166</v>
       </c>
       <c r="I13" t="n">
-        <v>0.136</v>
+        <v>0.143</v>
       </c>
       <c r="J13" t="n">
-        <v>0.135</v>
+        <v>0.0984</v>
       </c>
     </row>
     <row r="14">
@@ -983,22 +983,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.0375</v>
+        <v>0.0675</v>
       </c>
       <c r="F14" t="n">
-        <v>0.761</v>
+        <v>0.833</v>
       </c>
       <c r="G14" t="n">
-        <v>0.828</v>
+        <v>0.891</v>
       </c>
       <c r="H14" t="n">
-        <v>0.21</v>
+        <v>0.184</v>
       </c>
       <c r="I14" t="n">
-        <v>0.152</v>
+        <v>0.104</v>
       </c>
       <c r="J14" t="n">
-        <v>0.112</v>
+        <v>0.405</v>
       </c>
     </row>
     <row r="15">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.0229</v>
+        <v>0.0329</v>
       </c>
       <c r="F15" t="n">
-        <v>0.761</v>
+        <v>0.833</v>
       </c>
       <c r="G15" t="n">
-        <v>0.828</v>
+        <v>0.891</v>
       </c>
       <c r="H15" t="n">
-        <v>0.21</v>
+        <v>0.184</v>
       </c>
       <c r="I15" t="n">
-        <v>0.152</v>
+        <v>0.104</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0562</v>
+        <v>0.0987</v>
       </c>
     </row>
     <row r="16">
@@ -1063,22 +1063,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.037</v>
+        <v>0.536</v>
       </c>
       <c r="F16" t="n">
-        <v>0.761</v>
+        <v>0.833</v>
       </c>
       <c r="G16" t="n">
-        <v>0.84</v>
+        <v>0.841</v>
       </c>
       <c r="H16" t="n">
-        <v>0.21</v>
+        <v>0.184</v>
       </c>
       <c r="I16" t="n">
         <v>0.192</v>
       </c>
       <c r="J16" t="n">
-        <v>0.112</v>
+        <v>0.588</v>
       </c>
     </row>
     <row r="17">
@@ -1103,22 +1103,22 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.00604</v>
+        <v>0.285</v>
       </c>
       <c r="F17" t="n">
-        <v>0.761</v>
+        <v>0.833</v>
       </c>
       <c r="G17" t="n">
-        <v>0.84</v>
+        <v>0.841</v>
       </c>
       <c r="H17" t="n">
-        <v>0.21</v>
+        <v>0.184</v>
       </c>
       <c r="I17" t="n">
         <v>0.192</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0362</v>
+        <v>0.311</v>
       </c>
     </row>
     <row r="18">
@@ -1143,22 +1143,22 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.652</v>
+        <v>0.588</v>
       </c>
       <c r="F18" t="n">
-        <v>0.853</v>
+        <v>0.857</v>
       </c>
       <c r="G18" t="n">
-        <v>0.867</v>
+        <v>0.874</v>
       </c>
       <c r="H18" t="n">
-        <v>0.13</v>
+        <v>0.123</v>
       </c>
       <c r="I18" t="n">
-        <v>0.186</v>
+        <v>0.177</v>
       </c>
       <c r="J18" t="n">
-        <v>0.652</v>
+        <v>0.588</v>
       </c>
     </row>
     <row r="19">
@@ -1186,19 +1186,19 @@
         <v>0.0844</v>
       </c>
       <c r="F19" t="n">
-        <v>0.853</v>
+        <v>0.857</v>
       </c>
       <c r="G19" t="n">
-        <v>0.867</v>
+        <v>0.874</v>
       </c>
       <c r="H19" t="n">
-        <v>0.13</v>
+        <v>0.123</v>
       </c>
       <c r="I19" t="n">
-        <v>0.186</v>
+        <v>0.177</v>
       </c>
       <c r="J19" t="n">
-        <v>0.127</v>
+        <v>0.165</v>
       </c>
     </row>
     <row r="20">
@@ -1223,22 +1223,22 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.534</v>
+        <v>0.437</v>
       </c>
       <c r="F20" t="n">
-        <v>0.853</v>
+        <v>0.857</v>
       </c>
       <c r="G20" t="n">
-        <v>0.877</v>
+        <v>0.888</v>
       </c>
       <c r="H20" t="n">
-        <v>0.13</v>
+        <v>0.123</v>
       </c>
       <c r="I20" t="n">
-        <v>0.185</v>
+        <v>0.179</v>
       </c>
       <c r="J20" t="n">
-        <v>0.641</v>
+        <v>0.588</v>
       </c>
     </row>
     <row r="21">
@@ -1263,22 +1263,22 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.139</v>
+        <v>0.11</v>
       </c>
       <c r="F21" t="n">
-        <v>0.853</v>
+        <v>0.857</v>
       </c>
       <c r="G21" t="n">
-        <v>0.877</v>
+        <v>0.888</v>
       </c>
       <c r="H21" t="n">
-        <v>0.13</v>
+        <v>0.123</v>
       </c>
       <c r="I21" t="n">
-        <v>0.185</v>
+        <v>0.179</v>
       </c>
       <c r="J21" t="n">
-        <v>0.167</v>
+        <v>0.165</v>
       </c>
     </row>
     <row r="22">
@@ -1303,22 +1303,22 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.222</v>
+        <v>0.217</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>0.861</v>
+        <v>0.868</v>
       </c>
       <c r="H22" t="n">
-        <v>0.156</v>
+        <v>0.148</v>
       </c>
       <c r="I22" t="n">
-        <v>0.175</v>
+        <v>0.167</v>
       </c>
       <c r="J22" t="n">
-        <v>0.444</v>
+        <v>0.588</v>
       </c>
     </row>
     <row r="23">
@@ -1346,19 +1346,19 @@
         <v>0.0281</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>0.861</v>
+        <v>0.868</v>
       </c>
       <c r="H23" t="n">
-        <v>0.156</v>
+        <v>0.148</v>
       </c>
       <c r="I23" t="n">
-        <v>0.175</v>
+        <v>0.167</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0562</v>
+        <v>0.0987</v>
       </c>
     </row>
     <row r="24">
@@ -1383,22 +1383,22 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.299</v>
+        <v>0.296</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>0.78</v>
+        <v>0.786</v>
       </c>
       <c r="H24" t="n">
-        <v>0.156</v>
+        <v>0.148</v>
       </c>
       <c r="I24" t="n">
-        <v>0.188</v>
+        <v>0.182</v>
       </c>
       <c r="J24" t="n">
-        <v>0.449</v>
+        <v>0.588</v>
       </c>
     </row>
     <row r="25">
@@ -1423,22 +1423,22 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.272</v>
+        <v>0.311</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>0.78</v>
+        <v>0.786</v>
       </c>
       <c r="H25" t="n">
-        <v>0.156</v>
+        <v>0.148</v>
       </c>
       <c r="I25" t="n">
-        <v>0.188</v>
+        <v>0.182</v>
       </c>
       <c r="J25" t="n">
-        <v>0.272</v>
+        <v>0.311</v>
       </c>
     </row>
     <row r="26">
@@ -1463,22 +1463,22 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.61</v>
+        <v>0.648</v>
       </c>
       <c r="F26" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="G26" t="n">
-        <v>0.806</v>
+        <v>0.848</v>
       </c>
       <c r="H26" t="n">
-        <v>0.171</v>
+        <v>0.166</v>
       </c>
       <c r="I26" t="n">
-        <v>0.167</v>
+        <v>0.148</v>
       </c>
       <c r="J26" t="n">
-        <v>0.61</v>
+        <v>0.648</v>
       </c>
     </row>
     <row r="27">
@@ -1503,22 +1503,22 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.35</v>
+        <v>0.286</v>
       </c>
       <c r="F27" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="G27" t="n">
-        <v>0.806</v>
+        <v>0.848</v>
       </c>
       <c r="H27" t="n">
-        <v>0.171</v>
+        <v>0.166</v>
       </c>
       <c r="I27" t="n">
-        <v>0.167</v>
+        <v>0.148</v>
       </c>
       <c r="J27" t="n">
-        <v>0.42</v>
+        <v>0.343</v>
       </c>
     </row>
     <row r="28">
@@ -1543,22 +1543,22 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.0538</v>
+        <v>0.00444</v>
       </c>
       <c r="F28" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="G28" t="n">
-        <v>0.744</v>
+        <v>0.758</v>
       </c>
       <c r="H28" t="n">
-        <v>0.171</v>
+        <v>0.166</v>
       </c>
       <c r="I28" t="n">
-        <v>0.25</v>
+        <v>0.262</v>
       </c>
       <c r="J28" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.0133</v>
       </c>
     </row>
     <row r="29">
@@ -1583,22 +1583,22 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.00585</v>
       </c>
       <c r="F29" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="G29" t="n">
-        <v>0.744</v>
+        <v>0.758</v>
       </c>
       <c r="H29" t="n">
-        <v>0.171</v>
+        <v>0.166</v>
       </c>
       <c r="I29" t="n">
-        <v>0.25</v>
+        <v>0.262</v>
       </c>
       <c r="J29" t="n">
-        <v>0.104</v>
+        <v>0.0175</v>
       </c>
     </row>
     <row r="30">
@@ -1623,22 +1623,22 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.00468</v>
+        <v>0.00442</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="G30" t="n">
-        <v>0.637</v>
+        <v>0.651</v>
       </c>
       <c r="H30" t="n">
-        <v>0.203</v>
+        <v>0.213</v>
       </c>
       <c r="I30" t="n">
-        <v>0.222</v>
+        <v>0.226</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0281</v>
+        <v>0.0133</v>
       </c>
     </row>
     <row r="31">
@@ -1666,16 +1666,16 @@
         <v>0.00147</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="G31" t="n">
-        <v>0.637</v>
+        <v>0.651</v>
       </c>
       <c r="H31" t="n">
-        <v>0.203</v>
+        <v>0.213</v>
       </c>
       <c r="I31" t="n">
-        <v>0.222</v>
+        <v>0.226</v>
       </c>
       <c r="J31" t="n">
         <v>0.00882</v>
@@ -1703,22 +1703,22 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.489</v>
+        <v>0.556</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="G32" t="n">
-        <v>0.787</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>0.203</v>
+        <v>0.213</v>
       </c>
       <c r="I32" t="n">
-        <v>0.202</v>
+        <v>0.21</v>
       </c>
       <c r="J32" t="n">
-        <v>0.587</v>
+        <v>0.648</v>
       </c>
     </row>
     <row r="33">
@@ -1746,16 +1746,16 @@
         <v>0.878</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="G33" t="n">
-        <v>0.787</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>0.203</v>
+        <v>0.213</v>
       </c>
       <c r="I33" t="n">
-        <v>0.202</v>
+        <v>0.21</v>
       </c>
       <c r="J33" t="n">
         <v>0.878</v>
@@ -1783,22 +1783,22 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.018</v>
+        <v>0.0169</v>
       </c>
       <c r="F34" t="n">
-        <v>0.646</v>
+        <v>0.656</v>
       </c>
       <c r="G34" t="n">
-        <v>0.518</v>
+        <v>0.519</v>
       </c>
       <c r="H34" t="n">
-        <v>0.214</v>
+        <v>0.221</v>
       </c>
       <c r="I34" t="n">
-        <v>0.182</v>
+        <v>0.183</v>
       </c>
       <c r="J34" t="n">
-        <v>0.0508</v>
+        <v>0.0301</v>
       </c>
     </row>
     <row r="35">
@@ -1823,22 +1823,22 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.0303</v>
+        <v>0.0408</v>
       </c>
       <c r="F35" t="n">
-        <v>0.646</v>
+        <v>0.656</v>
       </c>
       <c r="G35" t="n">
-        <v>0.518</v>
+        <v>0.519</v>
       </c>
       <c r="H35" t="n">
-        <v>0.214</v>
+        <v>0.221</v>
       </c>
       <c r="I35" t="n">
-        <v>0.182</v>
+        <v>0.183</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0606</v>
+        <v>0.0612</v>
       </c>
     </row>
     <row r="36">
@@ -1863,22 +1863,22 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.0254</v>
+        <v>0.0201</v>
       </c>
       <c r="F36" t="n">
-        <v>0.646</v>
+        <v>0.656</v>
       </c>
       <c r="G36" t="n">
-        <v>0.79</v>
+        <v>0.802</v>
       </c>
       <c r="H36" t="n">
-        <v>0.214</v>
+        <v>0.221</v>
       </c>
       <c r="I36" t="n">
-        <v>0.199</v>
+        <v>0.207</v>
       </c>
       <c r="J36" t="n">
-        <v>0.0508</v>
+        <v>0.0301</v>
       </c>
     </row>
     <row r="37">
@@ -1903,22 +1903,22 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.0281</v>
+        <v>0.028</v>
       </c>
       <c r="F37" t="n">
-        <v>0.646</v>
+        <v>0.656</v>
       </c>
       <c r="G37" t="n">
-        <v>0.79</v>
+        <v>0.802</v>
       </c>
       <c r="H37" t="n">
-        <v>0.214</v>
+        <v>0.221</v>
       </c>
       <c r="I37" t="n">
-        <v>0.199</v>
+        <v>0.207</v>
       </c>
       <c r="J37" t="n">
-        <v>0.0606</v>
+        <v>0.056</v>
       </c>
     </row>
   </sheetData>
@@ -2081,7 +2081,7 @@
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>0.967</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -2118,13 +2118,13 @@
         <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>0.733</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8</v>
+        <v>0.967</v>
       </c>
       <c r="H5" t="n">
-        <v>0.761</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -2155,10 +2155,10 @@
         <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>0.533</v>
+        <v>0.633</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
@@ -2229,10 +2229,10 @@
         <v>7</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8</v>
+        <v>0.867</v>
       </c>
       <c r="G8" t="n">
-        <v>0.767</v>
+        <v>0.9</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
@@ -2306,7 +2306,7 @@
         <v>0.833</v>
       </c>
       <c r="G10" t="n">
-        <v>0.833</v>
+        <v>0.867</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
@@ -2340,10 +2340,10 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>0.533</v>
+        <v>0.767</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5</v>
+        <v>0.733</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
@@ -2380,10 +2380,10 @@
         <v>0.633</v>
       </c>
       <c r="G12" t="n">
-        <v>0.767</v>
+        <v>0.733</v>
       </c>
       <c r="H12" t="n">
-        <v>0.399</v>
+        <v>0.58</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
@@ -2525,13 +2525,13 @@
         <v>15</v>
       </c>
       <c r="F16" t="n">
-        <v>0.667</v>
+        <v>0.8</v>
       </c>
       <c r="G16" t="n">
-        <v>0.767</v>
+        <v>0.867</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.731</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
@@ -2562,13 +2562,13 @@
         <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>0.467</v>
+        <v>0.533</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.733</v>
       </c>
       <c r="H17" t="n">
-        <v>0.606</v>
+        <v>0.18</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
@@ -2710,10 +2710,10 @@
         <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>0.462</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>0.556</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
@@ -2747,13 +2747,13 @@
         <v>5</v>
       </c>
       <c r="F22" t="n">
-        <v>0.75</v>
+        <v>0.842</v>
       </c>
       <c r="G22" t="n">
-        <v>0.867</v>
+        <v>0.875</v>
       </c>
       <c r="H22" t="n">
-        <v>0.672</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
@@ -2821,10 +2821,10 @@
         <v>7</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.857</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8</v>
+        <v>0.864</v>
       </c>
       <c r="H24" t="n">
         <v>1</v>
@@ -2932,10 +2932,10 @@
         <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>0.722</v>
+        <v>0.833</v>
       </c>
       <c r="G27" t="n">
-        <v>0.706</v>
+        <v>0.826</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
@@ -2969,13 +2969,13 @@
         <v>11</v>
       </c>
       <c r="F28" t="n">
-        <v>0.76</v>
+        <v>0.792</v>
       </c>
       <c r="G28" t="n">
         <v>0.905</v>
       </c>
       <c r="H28" t="n">
-        <v>0.26</v>
+        <v>0.422</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
@@ -3117,13 +3117,13 @@
         <v>15</v>
       </c>
       <c r="F32" t="n">
-        <v>0.727</v>
+        <v>0.889</v>
       </c>
       <c r="G32" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.944</v>
       </c>
       <c r="H32" t="n">
-        <v>0.721</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
         <v>1</v>
@@ -3154,13 +3154,13 @@
         <v>16</v>
       </c>
       <c r="F33" t="n">
-        <v>0.462</v>
+        <v>0.636</v>
       </c>
       <c r="G33" t="n">
-        <v>0.556</v>
+        <v>0.8</v>
       </c>
       <c r="H33" t="n">
-        <v>0.722</v>
+        <v>0.407</v>
       </c>
       <c r="I33" t="n">
         <v>1</v>
@@ -3265,7 +3265,7 @@
         <v>3</v>
       </c>
       <c r="F36" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
         <v>1</v>
@@ -3302,10 +3302,10 @@
         <v>4</v>
       </c>
       <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" t="n">
         <v>0.857</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.714</v>
       </c>
       <c r="H37" t="n">
         <v>1</v>
@@ -3339,13 +3339,13 @@
         <v>5</v>
       </c>
       <c r="F38" t="n">
-        <v>0.625</v>
+        <v>0.667</v>
       </c>
       <c r="G38" t="n">
-        <v>0.542</v>
+        <v>0.583</v>
       </c>
       <c r="H38" t="n">
-        <v>0.77</v>
+        <v>0.766</v>
       </c>
       <c r="I38" t="n">
         <v>1</v>
@@ -3413,10 +3413,10 @@
         <v>7</v>
       </c>
       <c r="F40" t="n">
-        <v>0.895</v>
+        <v>0.947</v>
       </c>
       <c r="G40" t="n">
-        <v>0.842</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
         <v>1</v>
@@ -3490,7 +3490,7 @@
         <v>0.833</v>
       </c>
       <c r="G42" t="n">
-        <v>0.833</v>
+        <v>0.867</v>
       </c>
       <c r="H42" t="n">
         <v>1</v>
@@ -3524,10 +3524,10 @@
         <v>10</v>
       </c>
       <c r="F43" t="n">
-        <v>0.591</v>
+        <v>0.87</v>
       </c>
       <c r="G43" t="n">
-        <v>0.545</v>
+        <v>0.826</v>
       </c>
       <c r="H43" t="n">
         <v>1</v>
@@ -3561,10 +3561,10 @@
         <v>11</v>
       </c>
       <c r="F44" t="n">
-        <v>0.792</v>
+        <v>0.76</v>
       </c>
       <c r="G44" t="n">
-        <v>0.792</v>
+        <v>0.76</v>
       </c>
       <c r="H44" t="n">
         <v>1</v>
@@ -3746,13 +3746,13 @@
         <v>16</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4</v>
+        <v>0.412</v>
       </c>
       <c r="G49" t="n">
-        <v>0.667</v>
+        <v>0.706</v>
       </c>
       <c r="H49" t="n">
-        <v>0.272</v>
+        <v>0.166</v>
       </c>
       <c r="I49" t="n">
         <v>1</v>
@@ -3857,7 +3857,7 @@
         <v>3</v>
       </c>
       <c r="F52" t="n">
-        <v>0.967</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
@@ -3894,16 +3894,16 @@
         <v>4</v>
       </c>
       <c r="F53" t="n">
-        <v>0.733</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>0.967</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>0.0257</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>0.411</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3931,13 +3931,13 @@
         <v>5</v>
       </c>
       <c r="F54" t="n">
-        <v>0.533</v>
+        <v>0.633</v>
       </c>
       <c r="G54" t="n">
         <v>0.633</v>
       </c>
       <c r="H54" t="n">
-        <v>0.601</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
         <v>1</v>
@@ -4005,13 +4005,13 @@
         <v>7</v>
       </c>
       <c r="F56" t="n">
-        <v>0.8</v>
+        <v>0.867</v>
       </c>
       <c r="G56" t="n">
-        <v>0.733</v>
+        <v>0.833</v>
       </c>
       <c r="H56" t="n">
-        <v>0.761</v>
+        <v>1</v>
       </c>
       <c r="I56" t="n">
         <v>1</v>
@@ -4116,13 +4116,13 @@
         <v>10</v>
       </c>
       <c r="F59" t="n">
-        <v>0.533</v>
+        <v>0.767</v>
       </c>
       <c r="G59" t="n">
-        <v>0.733</v>
+        <v>0.7</v>
       </c>
       <c r="H59" t="n">
-        <v>0.18</v>
+        <v>0.771</v>
       </c>
       <c r="I59" t="n">
         <v>1</v>
@@ -4156,7 +4156,7 @@
         <v>0.633</v>
       </c>
       <c r="G60" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="H60" t="n">
         <v>1</v>
@@ -4301,13 +4301,13 @@
         <v>15</v>
       </c>
       <c r="F64" t="n">
-        <v>0.667</v>
+        <v>0.8</v>
       </c>
       <c r="G64" t="n">
         <v>0.633</v>
       </c>
       <c r="H64" t="n">
-        <v>1</v>
+        <v>0.252</v>
       </c>
       <c r="I64" t="n">
         <v>1</v>
@@ -4338,13 +4338,13 @@
         <v>16</v>
       </c>
       <c r="F65" t="n">
-        <v>0.467</v>
+        <v>0.533</v>
       </c>
       <c r="G65" t="n">
-        <v>0.5</v>
+        <v>0.433</v>
       </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>0.606</v>
       </c>
       <c r="I65" t="n">
         <v>1</v>
@@ -4486,16 +4486,16 @@
         <v>4</v>
       </c>
       <c r="F69" t="n">
-        <v>0.462</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
         <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>0.0436</v>
+        <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>0.698</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4523,13 +4523,13 @@
         <v>5</v>
       </c>
       <c r="F70" t="n">
-        <v>0.75</v>
+        <v>0.842</v>
       </c>
       <c r="G70" t="n">
         <v>0.842</v>
       </c>
       <c r="H70" t="n">
-        <v>0.695</v>
+        <v>1</v>
       </c>
       <c r="I70" t="n">
         <v>1</v>
@@ -4597,10 +4597,10 @@
         <v>7</v>
       </c>
       <c r="F72" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.857</v>
       </c>
       <c r="G72" t="n">
-        <v>0.824</v>
+        <v>0.85</v>
       </c>
       <c r="H72" t="n">
         <v>1</v>
@@ -4708,13 +4708,13 @@
         <v>10</v>
       </c>
       <c r="F75" t="n">
-        <v>0.722</v>
+        <v>0.833</v>
       </c>
       <c r="G75" t="n">
         <v>0.889</v>
       </c>
       <c r="H75" t="n">
-        <v>0.402</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="I75" t="n">
         <v>1</v>
@@ -4745,7 +4745,7 @@
         <v>11</v>
       </c>
       <c r="F76" t="n">
-        <v>0.76</v>
+        <v>0.792</v>
       </c>
       <c r="G76" t="n">
         <v>0.85</v>
@@ -4893,13 +4893,13 @@
         <v>15</v>
       </c>
       <c r="F80" t="n">
-        <v>0.727</v>
+        <v>0.889</v>
       </c>
       <c r="G80" t="n">
         <v>0.909</v>
       </c>
       <c r="H80" t="n">
-        <v>0.378</v>
+        <v>1</v>
       </c>
       <c r="I80" t="n">
         <v>1</v>
@@ -4930,7 +4930,7 @@
         <v>16</v>
       </c>
       <c r="F81" t="n">
-        <v>0.462</v>
+        <v>0.636</v>
       </c>
       <c r="G81" t="n">
         <v>0.5</v>
@@ -5041,7 +5041,7 @@
         <v>3</v>
       </c>
       <c r="F84" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="G84" t="n">
         <v>1</v>
@@ -5078,10 +5078,10 @@
         <v>4</v>
       </c>
       <c r="F85" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="G85" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="H85" t="n">
         <v>1</v>
@@ -5115,7 +5115,7 @@
         <v>5</v>
       </c>
       <c r="F86" t="n">
-        <v>0.625</v>
+        <v>0.667</v>
       </c>
       <c r="G86" t="n">
         <v>0.667</v>
@@ -5189,13 +5189,13 @@
         <v>7</v>
       </c>
       <c r="F88" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="G88" t="n">
         <v>0.895</v>
       </c>
-      <c r="G88" t="n">
-        <v>0.737</v>
-      </c>
       <c r="H88" t="n">
-        <v>0.405</v>
+        <v>1</v>
       </c>
       <c r="I88" t="n">
         <v>1</v>
@@ -5300,13 +5300,13 @@
         <v>10</v>
       </c>
       <c r="F91" t="n">
-        <v>0.591</v>
+        <v>0.87</v>
       </c>
       <c r="G91" t="n">
-        <v>0.727</v>
+        <v>0.696</v>
       </c>
       <c r="H91" t="n">
-        <v>0.526</v>
+        <v>0.284</v>
       </c>
       <c r="I91" t="n">
         <v>1</v>
@@ -5337,13 +5337,13 @@
         <v>11</v>
       </c>
       <c r="F92" t="n">
-        <v>0.792</v>
+        <v>0.76</v>
       </c>
       <c r="G92" t="n">
-        <v>0.708</v>
+        <v>0.68</v>
       </c>
       <c r="H92" t="n">
-        <v>0.74</v>
+        <v>0.754</v>
       </c>
       <c r="I92" t="n">
         <v>1</v>
@@ -5494,7 +5494,7 @@
         <v>0.0958</v>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="97">
@@ -5522,16 +5522,16 @@
         <v>16</v>
       </c>
       <c r="F97" t="n">
-        <v>0.4</v>
+        <v>0.412</v>
       </c>
       <c r="G97" t="n">
-        <v>0.133</v>
+        <v>0.118</v>
       </c>
       <c r="H97" t="n">
-        <v>0.215</v>
+        <v>0.118</v>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="98">
@@ -5670,13 +5670,13 @@
         <v>4</v>
       </c>
       <c r="F101" t="n">
-        <v>0.967</v>
+        <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>0.9</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="H101" t="n">
-        <v>0.612</v>
+        <v>0.492</v>
       </c>
       <c r="I101" t="n">
         <v>1</v>
@@ -5781,13 +5781,13 @@
         <v>7</v>
       </c>
       <c r="F104" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G104" t="n">
         <v>0.8</v>
       </c>
-      <c r="G104" t="n">
-        <v>0.767</v>
-      </c>
       <c r="H104" t="n">
-        <v>1</v>
+        <v>0.472</v>
       </c>
       <c r="I104" t="n">
         <v>1</v>
@@ -5929,13 +5929,13 @@
         <v>11</v>
       </c>
       <c r="F108" t="n">
-        <v>0.7</v>
+        <v>0.667</v>
       </c>
       <c r="G108" t="n">
-        <v>0.633</v>
+        <v>0.6</v>
       </c>
       <c r="H108" t="n">
-        <v>0.785</v>
+        <v>0.789</v>
       </c>
       <c r="I108" t="n">
         <v>1</v>
@@ -6117,10 +6117,10 @@
         <v>0.5669999999999999</v>
       </c>
       <c r="G113" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="H113" t="n">
-        <v>1</v>
+        <v>0.596</v>
       </c>
       <c r="I113" t="n">
         <v>1</v>
@@ -6373,10 +6373,10 @@
         <v>7</v>
       </c>
       <c r="F120" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="G120" t="n">
         <v>0.842</v>
-      </c>
-      <c r="G120" t="n">
-        <v>0.833</v>
       </c>
       <c r="H120" t="n">
         <v>1</v>
@@ -6706,13 +6706,13 @@
         <v>16</v>
       </c>
       <c r="F129" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="H129" t="n">
         <v>0.542</v>
-      </c>
-      <c r="G129" t="n">
-        <v>0.579</v>
-      </c>
-      <c r="H129" t="n">
-        <v>1</v>
       </c>
       <c r="I129" t="n">
         <v>1</v>
@@ -6752,7 +6752,7 @@
         <v>0.348</v>
       </c>
       <c r="I130" t="n">
-        <v>1</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="131">
@@ -6789,7 +6789,7 @@
         <v>0.4</v>
       </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="132">
@@ -6854,16 +6854,16 @@
         <v>4</v>
       </c>
       <c r="F133" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="G133" t="n">
-        <v>0.571</v>
+        <v>0.714</v>
       </c>
       <c r="H133" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.462</v>
       </c>
       <c r="I133" t="n">
-        <v>1</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="134">
@@ -6965,16 +6965,16 @@
         <v>7</v>
       </c>
       <c r="F136" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" t="n">
         <v>0.842</v>
       </c>
-      <c r="G136" t="n">
-        <v>0.789</v>
-      </c>
       <c r="H136" t="n">
-        <v>1</v>
+        <v>0.23</v>
       </c>
       <c r="I136" t="n">
-        <v>1</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="137">
@@ -7048,7 +7048,7 @@
         <v>0.158</v>
       </c>
       <c r="I138" t="n">
-        <v>1</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="139">
@@ -7076,16 +7076,16 @@
         <v>10</v>
       </c>
       <c r="F139" t="n">
-        <v>0.727</v>
+        <v>0.739</v>
       </c>
       <c r="G139" t="n">
-        <v>0.591</v>
+        <v>0.609</v>
       </c>
       <c r="H139" t="n">
-        <v>0.526</v>
+        <v>0.53</v>
       </c>
       <c r="I139" t="n">
-        <v>1</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="140">
@@ -7113,16 +7113,16 @@
         <v>11</v>
       </c>
       <c r="F140" t="n">
-        <v>0.708</v>
+        <v>0.68</v>
       </c>
       <c r="G140" t="n">
-        <v>0.583</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H140" t="n">
-        <v>0.547</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="I140" t="n">
-        <v>1</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="141">
@@ -7233,7 +7233,7 @@
         <v>0.407</v>
       </c>
       <c r="I143" t="n">
-        <v>1</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="144">
@@ -7298,13 +7298,13 @@
         <v>16</v>
       </c>
       <c r="F145" t="n">
-        <v>0.867</v>
+        <v>0.824</v>
       </c>
       <c r="G145" t="n">
-        <v>0.733</v>
+        <v>0.765</v>
       </c>
       <c r="H145" t="n">
-        <v>0.651</v>
+        <v>1</v>
       </c>
       <c r="I145" t="n">
         <v>1</v>
@@ -7446,10 +7446,10 @@
         <v>4</v>
       </c>
       <c r="F149" t="n">
-        <v>0.967</v>
+        <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>0.967</v>
+        <v>1</v>
       </c>
       <c r="H149" t="n">
         <v>1</v>
@@ -7557,10 +7557,10 @@
         <v>7</v>
       </c>
       <c r="F152" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G152" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H152" t="n">
         <v>1</v>
@@ -7705,13 +7705,13 @@
         <v>11</v>
       </c>
       <c r="F156" t="n">
-        <v>0.7</v>
+        <v>0.667</v>
       </c>
       <c r="G156" t="n">
-        <v>0.767</v>
+        <v>0.8</v>
       </c>
       <c r="H156" t="n">
-        <v>0.771</v>
+        <v>0.382</v>
       </c>
       <c r="I156" t="n">
         <v>1</v>
@@ -8149,10 +8149,10 @@
         <v>7</v>
       </c>
       <c r="F168" t="n">
-        <v>0.842</v>
+        <v>0.864</v>
       </c>
       <c r="G168" t="n">
-        <v>0.882</v>
+        <v>0.9</v>
       </c>
       <c r="H168" t="n">
         <v>1</v>
@@ -8300,7 +8300,7 @@
         <v>0.895</v>
       </c>
       <c r="G172" t="n">
-        <v>0.87</v>
+        <v>0.913</v>
       </c>
       <c r="H172" t="n">
         <v>1</v>
@@ -8482,13 +8482,13 @@
         <v>16</v>
       </c>
       <c r="F177" t="n">
-        <v>0.542</v>
+        <v>0.583</v>
       </c>
       <c r="G177" t="n">
-        <v>0.667</v>
+        <v>0.778</v>
       </c>
       <c r="H177" t="n">
-        <v>0.698</v>
+        <v>0.429</v>
       </c>
       <c r="I177" t="n">
         <v>1</v>
@@ -8630,10 +8630,10 @@
         <v>4</v>
       </c>
       <c r="F181" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="G181" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="H181" t="n">
         <v>1</v>
@@ -8741,10 +8741,10 @@
         <v>7</v>
       </c>
       <c r="F184" t="n">
-        <v>0.842</v>
+        <v>1</v>
       </c>
       <c r="G184" t="n">
-        <v>0.789</v>
+        <v>0.947</v>
       </c>
       <c r="H184" t="n">
         <v>1</v>
@@ -8852,13 +8852,13 @@
         <v>10</v>
       </c>
       <c r="F187" t="n">
-        <v>0.727</v>
+        <v>0.739</v>
       </c>
       <c r="G187" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.826</v>
       </c>
       <c r="H187" t="n">
-        <v>0.721</v>
+        <v>0.722</v>
       </c>
       <c r="I187" t="n">
         <v>1</v>
@@ -8889,13 +8889,13 @@
         <v>11</v>
       </c>
       <c r="F188" t="n">
-        <v>0.708</v>
+        <v>0.68</v>
       </c>
       <c r="G188" t="n">
-        <v>0.833</v>
+        <v>0.84</v>
       </c>
       <c r="H188" t="n">
-        <v>0.494</v>
+        <v>0.321</v>
       </c>
       <c r="I188" t="n">
         <v>1</v>
@@ -9074,16 +9074,16 @@
         <v>16</v>
       </c>
       <c r="F193" t="n">
-        <v>0.867</v>
+        <v>0.824</v>
       </c>
       <c r="G193" t="n">
-        <v>0.4</v>
+        <v>0.412</v>
       </c>
       <c r="H193" t="n">
-        <v>0.0209</v>
+        <v>0.0324</v>
       </c>
       <c r="I193" t="n">
-        <v>0.335</v>
+        <v>0.518</v>
       </c>
     </row>
     <row r="194">
@@ -9120,7 +9120,7 @@
         <v>0.288</v>
       </c>
       <c r="I194" t="n">
-        <v>1</v>
+        <v>0.922</v>
       </c>
     </row>
     <row r="195">
@@ -9222,16 +9222,16 @@
         <v>4</v>
       </c>
       <c r="F197" t="n">
-        <v>0.967</v>
+        <v>1</v>
       </c>
       <c r="G197" t="n">
         <v>0.9</v>
       </c>
       <c r="H197" t="n">
-        <v>0.612</v>
+        <v>0.237</v>
       </c>
       <c r="I197" t="n">
-        <v>1</v>
+        <v>0.922</v>
       </c>
     </row>
     <row r="198">
@@ -9259,10 +9259,10 @@
         <v>5</v>
       </c>
       <c r="F198" t="n">
-        <v>0.433</v>
+        <v>0.467</v>
       </c>
       <c r="G198" t="n">
-        <v>0.433</v>
+        <v>0.467</v>
       </c>
       <c r="H198" t="n">
         <v>1</v>
@@ -9305,7 +9305,7 @@
         <v>0.267</v>
       </c>
       <c r="I199" t="n">
-        <v>1</v>
+        <v>0.922</v>
       </c>
     </row>
     <row r="200">
@@ -9333,13 +9333,13 @@
         <v>7</v>
       </c>
       <c r="F200" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="G200" t="n">
         <v>0.667</v>
       </c>
       <c r="H200" t="n">
-        <v>0.596</v>
+        <v>0.789</v>
       </c>
       <c r="I200" t="n">
         <v>1</v>
@@ -9416,7 +9416,7 @@
         <v>0.12</v>
       </c>
       <c r="I202" t="n">
-        <v>0.964</v>
+        <v>0.922</v>
       </c>
     </row>
     <row r="203">
@@ -9444,10 +9444,10 @@
         <v>10</v>
       </c>
       <c r="F203" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="G203" t="n">
         <v>0.6</v>
-      </c>
-      <c r="G203" t="n">
-        <v>0.633</v>
       </c>
       <c r="H203" t="n">
         <v>1</v>
@@ -9481,13 +9481,13 @@
         <v>11</v>
       </c>
       <c r="F204" t="n">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="G204" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="H204" t="n">
-        <v>0.606</v>
+        <v>0.604</v>
       </c>
       <c r="I204" t="n">
         <v>1</v>
@@ -9666,13 +9666,13 @@
         <v>16</v>
       </c>
       <c r="F209" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="G209" t="n">
-        <v>0.667</v>
+        <v>0.733</v>
       </c>
       <c r="H209" t="n">
-        <v>0.596</v>
+        <v>0.412</v>
       </c>
       <c r="I209" t="n">
         <v>1</v>
@@ -9851,10 +9851,10 @@
         <v>5</v>
       </c>
       <c r="F214" t="n">
-        <v>0.769</v>
+        <v>0.786</v>
       </c>
       <c r="G214" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.833</v>
       </c>
       <c r="H214" t="n">
         <v>1</v>
@@ -9925,13 +9925,13 @@
         <v>7</v>
       </c>
       <c r="F216" t="n">
-        <v>0.8</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="G216" t="n">
         <v>0.909</v>
       </c>
       <c r="H216" t="n">
-        <v>0.586</v>
+        <v>1</v>
       </c>
       <c r="I216" t="n">
         <v>1</v>
@@ -10258,13 +10258,13 @@
         <v>16</v>
       </c>
       <c r="F225" t="n">
-        <v>0.545</v>
+        <v>0.619</v>
       </c>
       <c r="G225" t="n">
-        <v>0.632</v>
+        <v>0.737</v>
       </c>
       <c r="H225" t="n">
-        <v>0.752</v>
+        <v>0.511</v>
       </c>
       <c r="I225" t="n">
         <v>1</v>
@@ -10304,7 +10304,7 @@
         <v>0.0687</v>
       </c>
       <c r="I226" t="n">
-        <v>0.858</v>
+        <v>0.6870000000000001</v>
       </c>
     </row>
     <row r="227">
@@ -10378,7 +10378,7 @@
         <v>0.192</v>
       </c>
       <c r="I228" t="n">
-        <v>0.858</v>
+        <v>0.6870000000000001</v>
       </c>
     </row>
     <row r="229">
@@ -10406,16 +10406,16 @@
         <v>4</v>
       </c>
       <c r="F229" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="G229" t="n">
         <v>0.571</v>
       </c>
       <c r="H229" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.192</v>
       </c>
       <c r="I229" t="n">
-        <v>1</v>
+        <v>0.6870000000000001</v>
       </c>
     </row>
     <row r="230">
@@ -10443,10 +10443,10 @@
         <v>5</v>
       </c>
       <c r="F230" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="G230" t="n">
         <v>0.417</v>
-      </c>
-      <c r="G230" t="n">
-        <v>0.375</v>
       </c>
       <c r="H230" t="n">
         <v>1</v>
@@ -10489,7 +10489,7 @@
         <v>0.215</v>
       </c>
       <c r="I231" t="n">
-        <v>0.858</v>
+        <v>0.6870000000000001</v>
       </c>
     </row>
     <row r="232">
@@ -10517,13 +10517,13 @@
         <v>7</v>
       </c>
       <c r="F232" t="n">
-        <v>0.421</v>
+        <v>0.474</v>
       </c>
       <c r="G232" t="n">
         <v>0.526</v>
       </c>
       <c r="H232" t="n">
-        <v>0.746</v>
+        <v>1</v>
       </c>
       <c r="I232" t="n">
         <v>1</v>
@@ -10600,7 +10600,7 @@
         <v>0.12</v>
       </c>
       <c r="I234" t="n">
-        <v>0.858</v>
+        <v>0.6870000000000001</v>
       </c>
     </row>
     <row r="235">
@@ -10628,10 +10628,10 @@
         <v>10</v>
       </c>
       <c r="F235" t="n">
-        <v>0.5</v>
+        <v>0.478</v>
       </c>
       <c r="G235" t="n">
-        <v>0.545</v>
+        <v>0.522</v>
       </c>
       <c r="H235" t="n">
         <v>1</v>
@@ -10665,13 +10665,13 @@
         <v>11</v>
       </c>
       <c r="F236" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="G236" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="H236" t="n">
-        <v>0.38</v>
+        <v>0.387</v>
       </c>
       <c r="I236" t="n">
         <v>1</v>
@@ -10850,10 +10850,10 @@
         <v>16</v>
       </c>
       <c r="F241" t="n">
-        <v>0.8</v>
+        <v>0.765</v>
       </c>
       <c r="G241" t="n">
-        <v>0.8</v>
+        <v>0.824</v>
       </c>
       <c r="H241" t="n">
         <v>1</v>
@@ -10998,10 +10998,10 @@
         <v>4</v>
       </c>
       <c r="F245" t="n">
-        <v>0.967</v>
+        <v>1</v>
       </c>
       <c r="G245" t="n">
-        <v>0.967</v>
+        <v>1</v>
       </c>
       <c r="H245" t="n">
         <v>1</v>
@@ -11035,16 +11035,16 @@
         <v>5</v>
       </c>
       <c r="F246" t="n">
-        <v>0.433</v>
+        <v>0.467</v>
       </c>
       <c r="G246" t="n">
         <v>0.6</v>
       </c>
       <c r="H246" t="n">
-        <v>0.301</v>
+        <v>0.438</v>
       </c>
       <c r="I246" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.876</v>
       </c>
     </row>
     <row r="247">
@@ -11109,16 +11109,16 @@
         <v>7</v>
       </c>
       <c r="F248" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="G248" t="n">
-        <v>0.767</v>
+        <v>0.8</v>
       </c>
       <c r="H248" t="n">
-        <v>0.17</v>
+        <v>0.158</v>
       </c>
       <c r="I248" t="n">
-        <v>0.545</v>
+        <v>0.506</v>
       </c>
     </row>
     <row r="249">
@@ -11220,16 +11220,16 @@
         <v>10</v>
       </c>
       <c r="F251" t="n">
-        <v>0.6</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G251" t="n">
         <v>0.7</v>
       </c>
       <c r="H251" t="n">
-        <v>0.589</v>
+        <v>0.422</v>
       </c>
       <c r="I251" t="n">
-        <v>1</v>
+        <v>0.876</v>
       </c>
     </row>
     <row r="252">
@@ -11257,10 +11257,10 @@
         <v>11</v>
       </c>
       <c r="F252" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G252" t="n">
         <v>0.533</v>
-      </c>
-      <c r="G252" t="n">
-        <v>0.5669999999999999</v>
       </c>
       <c r="H252" t="n">
         <v>1</v>
@@ -11442,13 +11442,13 @@
         <v>16</v>
       </c>
       <c r="F257" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="G257" t="n">
         <v>0.533</v>
       </c>
       <c r="H257" t="n">
-        <v>1</v>
+        <v>0.795</v>
       </c>
       <c r="I257" t="n">
         <v>1</v>
@@ -11627,13 +11627,13 @@
         <v>5</v>
       </c>
       <c r="F262" t="n">
-        <v>0.769</v>
+        <v>0.786</v>
       </c>
       <c r="G262" t="n">
         <v>0.833</v>
       </c>
       <c r="H262" t="n">
-        <v>0.676</v>
+        <v>1</v>
       </c>
       <c r="I262" t="n">
         <v>1</v>
@@ -11701,10 +11701,10 @@
         <v>7</v>
       </c>
       <c r="F264" t="n">
-        <v>0.8</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="G264" t="n">
-        <v>0.773</v>
+        <v>0.783</v>
       </c>
       <c r="H264" t="n">
         <v>1</v>
@@ -11815,7 +11815,7 @@
         <v>0.917</v>
       </c>
       <c r="G267" t="n">
-        <v>0.882</v>
+        <v>0.889</v>
       </c>
       <c r="H267" t="n">
         <v>1</v>
@@ -12034,10 +12034,10 @@
         <v>16</v>
       </c>
       <c r="F273" t="n">
-        <v>0.545</v>
+        <v>0.619</v>
       </c>
       <c r="G273" t="n">
-        <v>0.545</v>
+        <v>0.636</v>
       </c>
       <c r="H273" t="n">
         <v>1</v>
@@ -12182,10 +12182,10 @@
         <v>4</v>
       </c>
       <c r="F277" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="G277" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="H277" t="n">
         <v>1</v>
@@ -12219,16 +12219,16 @@
         <v>5</v>
       </c>
       <c r="F278" t="n">
-        <v>0.417</v>
+        <v>0.458</v>
       </c>
       <c r="G278" t="n">
         <v>0.625</v>
       </c>
       <c r="H278" t="n">
-        <v>0.248</v>
+        <v>0.385</v>
       </c>
       <c r="I278" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="279">
@@ -12293,13 +12293,13 @@
         <v>7</v>
       </c>
       <c r="F280" t="n">
-        <v>0.421</v>
+        <v>0.474</v>
       </c>
       <c r="G280" t="n">
-        <v>0.895</v>
+        <v>0.947</v>
       </c>
       <c r="H280" t="n">
-        <v>0.00514</v>
+        <v>0.00304</v>
       </c>
       <c r="I280" t="n">
         <v>0.0471</v>
@@ -12404,16 +12404,16 @@
         <v>10</v>
       </c>
       <c r="F283" t="n">
-        <v>0.5</v>
+        <v>0.478</v>
       </c>
       <c r="G283" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.696</v>
       </c>
       <c r="H283" t="n">
-        <v>0.358</v>
+        <v>0.231</v>
       </c>
       <c r="I283" t="n">
-        <v>0.716</v>
+        <v>0.527</v>
       </c>
     </row>
     <row r="284">
@@ -12441,16 +12441,16 @@
         <v>11</v>
       </c>
       <c r="F284" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="G284" t="n">
-        <v>0.625</v>
+        <v>0.6</v>
       </c>
       <c r="H284" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.571</v>
       </c>
       <c r="I284" t="n">
-        <v>0.898</v>
+        <v>0.913</v>
       </c>
     </row>
     <row r="285">
@@ -12626,16 +12626,16 @@
         <v>16</v>
       </c>
       <c r="F289" t="n">
-        <v>0.8</v>
+        <v>0.765</v>
       </c>
       <c r="G289" t="n">
-        <v>0.4</v>
+        <v>0.412</v>
       </c>
       <c r="H289" t="n">
-        <v>0.0604</v>
+        <v>0.0799</v>
       </c>
       <c r="I289" t="n">
-        <v>0.161</v>
+        <v>0.213</v>
       </c>
     </row>
   </sheetData>

--- a/eval/results/statistical_tests_new30.xlsx
+++ b/eval/results/statistical_tests_new30.xlsx
@@ -503,22 +503,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.132</v>
+        <v>0.104</v>
       </c>
       <c r="F2" t="n">
         <v>0.823</v>
       </c>
       <c r="G2" t="n">
-        <v>0.854</v>
+        <v>0.856</v>
       </c>
       <c r="H2" t="n">
         <v>0.133</v>
       </c>
       <c r="I2" t="n">
-        <v>0.105</v>
+        <v>0.102</v>
       </c>
       <c r="J2" t="n">
-        <v>0.198</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="3">
@@ -543,22 +543,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.213</v>
+        <v>0.127</v>
       </c>
       <c r="F3" t="n">
         <v>0.823</v>
       </c>
       <c r="G3" t="n">
-        <v>0.854</v>
+        <v>0.856</v>
       </c>
       <c r="H3" t="n">
         <v>0.133</v>
       </c>
       <c r="I3" t="n">
-        <v>0.105</v>
+        <v>0.102</v>
       </c>
       <c r="J3" t="n">
-        <v>0.256</v>
+        <v>0.182</v>
       </c>
     </row>
     <row r="4">
@@ -598,7 +598,7 @@
         <v>0.153</v>
       </c>
       <c r="J4" t="n">
-        <v>0.099</v>
+        <v>0.0922</v>
       </c>
     </row>
     <row r="5">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.0506</v>
+        <v>0.0461</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>0.771</v>
@@ -678,7 +678,7 @@
         <v>0.111</v>
       </c>
       <c r="J6" t="n">
-        <v>0.101</v>
+        <v>0.0922</v>
       </c>
     </row>
     <row r="7">
@@ -706,7 +706,7 @@
         <v>0.047</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>0.771</v>
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.227</v>
+        <v>0.262</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>0.838</v>
@@ -758,7 +758,7 @@
         <v>0.111</v>
       </c>
       <c r="J8" t="n">
-        <v>0.272</v>
+        <v>0.314</v>
       </c>
     </row>
     <row r="9">
@@ -783,10 +783,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.153</v>
+        <v>0.152</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>0.838</v>
@@ -798,7 +798,7 @@
         <v>0.111</v>
       </c>
       <c r="J9" t="n">
-        <v>0.229</v>
+        <v>0.182</v>
       </c>
     </row>
     <row r="10">
@@ -826,16 +826,16 @@
         <v>0.453</v>
       </c>
       <c r="F10" t="n">
-        <v>0.698</v>
+        <v>0.7</v>
       </c>
       <c r="G10" t="n">
-        <v>0.675</v>
+        <v>0.677</v>
       </c>
       <c r="H10" t="n">
-        <v>0.166</v>
+        <v>0.165</v>
       </c>
       <c r="I10" t="n">
-        <v>0.173</v>
+        <v>0.172</v>
       </c>
       <c r="J10" t="n">
         <v>0.453</v>
@@ -866,16 +866,16 @@
         <v>0.607</v>
       </c>
       <c r="F11" t="n">
-        <v>0.698</v>
+        <v>0.7</v>
       </c>
       <c r="G11" t="n">
-        <v>0.675</v>
+        <v>0.677</v>
       </c>
       <c r="H11" t="n">
-        <v>0.166</v>
+        <v>0.165</v>
       </c>
       <c r="I11" t="n">
-        <v>0.173</v>
+        <v>0.172</v>
       </c>
       <c r="J11" t="n">
         <v>0.607</v>
@@ -906,19 +906,19 @@
         <v>0.0448</v>
       </c>
       <c r="F12" t="n">
-        <v>0.698</v>
+        <v>0.7</v>
       </c>
       <c r="G12" t="n">
-        <v>0.767</v>
+        <v>0.769</v>
       </c>
       <c r="H12" t="n">
-        <v>0.166</v>
+        <v>0.165</v>
       </c>
       <c r="I12" t="n">
-        <v>0.143</v>
+        <v>0.142</v>
       </c>
       <c r="J12" t="n">
-        <v>0.101</v>
+        <v>0.0922</v>
       </c>
     </row>
     <row r="13">
@@ -946,16 +946,16 @@
         <v>0.0492</v>
       </c>
       <c r="F13" t="n">
-        <v>0.698</v>
+        <v>0.7</v>
       </c>
       <c r="G13" t="n">
-        <v>0.767</v>
+        <v>0.769</v>
       </c>
       <c r="H13" t="n">
-        <v>0.166</v>
+        <v>0.165</v>
       </c>
       <c r="I13" t="n">
-        <v>0.143</v>
+        <v>0.142</v>
       </c>
       <c r="J13" t="n">
         <v>0.0984</v>
@@ -983,22 +983,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.0675</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="F14" t="n">
         <v>0.833</v>
       </c>
       <c r="G14" t="n">
-        <v>0.891</v>
+        <v>0.892</v>
       </c>
       <c r="H14" t="n">
         <v>0.184</v>
       </c>
       <c r="I14" t="n">
-        <v>0.104</v>
+        <v>0.103</v>
       </c>
       <c r="J14" t="n">
-        <v>0.405</v>
+        <v>0.391</v>
       </c>
     </row>
     <row r="15">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.0329</v>
+        <v>0.0218</v>
       </c>
       <c r="F15" t="n">
         <v>0.833</v>
       </c>
       <c r="G15" t="n">
-        <v>0.891</v>
+        <v>0.892</v>
       </c>
       <c r="H15" t="n">
         <v>0.184</v>
       </c>
       <c r="I15" t="n">
-        <v>0.104</v>
+        <v>0.103</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0987</v>
+        <v>0.0843</v>
       </c>
     </row>
     <row r="16">
@@ -1306,13 +1306,13 @@
         <v>0.217</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>0.868</v>
+        <v>0.869</v>
       </c>
       <c r="H22" t="n">
-        <v>0.148</v>
+        <v>0.149</v>
       </c>
       <c r="I22" t="n">
         <v>0.167</v>
@@ -1346,19 +1346,19 @@
         <v>0.0281</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>0.868</v>
+        <v>0.869</v>
       </c>
       <c r="H23" t="n">
-        <v>0.148</v>
+        <v>0.149</v>
       </c>
       <c r="I23" t="n">
         <v>0.167</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0987</v>
+        <v>0.0843</v>
       </c>
     </row>
     <row r="24">
@@ -1383,19 +1383,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.296</v>
+        <v>0.295</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>0.786</v>
+        <v>0.787</v>
       </c>
       <c r="H24" t="n">
-        <v>0.148</v>
+        <v>0.149</v>
       </c>
       <c r="I24" t="n">
-        <v>0.182</v>
+        <v>0.183</v>
       </c>
       <c r="J24" t="n">
         <v>0.588</v>
@@ -1426,16 +1426,16 @@
         <v>0.311</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>0.786</v>
+        <v>0.787</v>
       </c>
       <c r="H25" t="n">
-        <v>0.148</v>
+        <v>0.149</v>
       </c>
       <c r="I25" t="n">
-        <v>0.182</v>
+        <v>0.183</v>
       </c>
       <c r="J25" t="n">
         <v>0.311</v>
@@ -1463,13 +1463,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.648</v>
+        <v>0.723</v>
       </c>
       <c r="F26" t="n">
         <v>0.86</v>
       </c>
       <c r="G26" t="n">
-        <v>0.848</v>
+        <v>0.85</v>
       </c>
       <c r="H26" t="n">
         <v>0.166</v>
@@ -1478,7 +1478,7 @@
         <v>0.148</v>
       </c>
       <c r="J26" t="n">
-        <v>0.648</v>
+        <v>0.723</v>
       </c>
     </row>
     <row r="27">
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.286</v>
+        <v>0.332</v>
       </c>
       <c r="F27" t="n">
         <v>0.86</v>
       </c>
       <c r="G27" t="n">
-        <v>0.848</v>
+        <v>0.85</v>
       </c>
       <c r="H27" t="n">
         <v>0.166</v>
@@ -1518,7 +1518,7 @@
         <v>0.148</v>
       </c>
       <c r="J27" t="n">
-        <v>0.343</v>
+        <v>0.398</v>
       </c>
     </row>
     <row r="28">
@@ -1623,16 +1623,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.00442</v>
+        <v>0.00393</v>
       </c>
       <c r="F30" t="n">
-        <v>0.83</v>
+        <v>0.832</v>
       </c>
       <c r="G30" t="n">
         <v>0.651</v>
       </c>
       <c r="H30" t="n">
-        <v>0.213</v>
+        <v>0.212</v>
       </c>
       <c r="I30" t="n">
         <v>0.226</v>
@@ -1666,13 +1666,13 @@
         <v>0.00147</v>
       </c>
       <c r="F31" t="n">
-        <v>0.83</v>
+        <v>0.832</v>
       </c>
       <c r="G31" t="n">
         <v>0.651</v>
       </c>
       <c r="H31" t="n">
-        <v>0.213</v>
+        <v>0.212</v>
       </c>
       <c r="I31" t="n">
         <v>0.226</v>
@@ -1703,22 +1703,22 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.556</v>
+        <v>0.505</v>
       </c>
       <c r="F32" t="n">
-        <v>0.83</v>
+        <v>0.832</v>
       </c>
       <c r="G32" t="n">
         <v>0.8070000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>0.213</v>
+        <v>0.212</v>
       </c>
       <c r="I32" t="n">
         <v>0.21</v>
       </c>
       <c r="J32" t="n">
-        <v>0.648</v>
+        <v>0.606</v>
       </c>
     </row>
     <row r="33">
@@ -1743,22 +1743,22 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.878</v>
+        <v>0.721</v>
       </c>
       <c r="F33" t="n">
-        <v>0.83</v>
+        <v>0.832</v>
       </c>
       <c r="G33" t="n">
         <v>0.8070000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>0.213</v>
+        <v>0.212</v>
       </c>
       <c r="I33" t="n">
         <v>0.21</v>
       </c>
       <c r="J33" t="n">
-        <v>0.878</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="34">
@@ -1786,16 +1786,16 @@
         <v>0.0169</v>
       </c>
       <c r="F34" t="n">
-        <v>0.656</v>
+        <v>0.659</v>
       </c>
       <c r="G34" t="n">
-        <v>0.519</v>
+        <v>0.522</v>
       </c>
       <c r="H34" t="n">
-        <v>0.221</v>
+        <v>0.219</v>
       </c>
       <c r="I34" t="n">
-        <v>0.183</v>
+        <v>0.184</v>
       </c>
       <c r="J34" t="n">
         <v>0.0301</v>
@@ -1826,16 +1826,16 @@
         <v>0.0408</v>
       </c>
       <c r="F35" t="n">
-        <v>0.656</v>
+        <v>0.659</v>
       </c>
       <c r="G35" t="n">
-        <v>0.519</v>
+        <v>0.522</v>
       </c>
       <c r="H35" t="n">
-        <v>0.221</v>
+        <v>0.219</v>
       </c>
       <c r="I35" t="n">
-        <v>0.183</v>
+        <v>0.184</v>
       </c>
       <c r="J35" t="n">
         <v>0.0612</v>
@@ -1866,16 +1866,16 @@
         <v>0.0201</v>
       </c>
       <c r="F36" t="n">
-        <v>0.656</v>
+        <v>0.659</v>
       </c>
       <c r="G36" t="n">
-        <v>0.802</v>
+        <v>0.805</v>
       </c>
       <c r="H36" t="n">
-        <v>0.221</v>
+        <v>0.219</v>
       </c>
       <c r="I36" t="n">
-        <v>0.207</v>
+        <v>0.206</v>
       </c>
       <c r="J36" t="n">
         <v>0.0301</v>
@@ -1906,16 +1906,16 @@
         <v>0.028</v>
       </c>
       <c r="F37" t="n">
-        <v>0.656</v>
+        <v>0.659</v>
       </c>
       <c r="G37" t="n">
-        <v>0.802</v>
+        <v>0.805</v>
       </c>
       <c r="H37" t="n">
-        <v>0.221</v>
+        <v>0.219</v>
       </c>
       <c r="I37" t="n">
-        <v>0.207</v>
+        <v>0.206</v>
       </c>
       <c r="J37" t="n">
         <v>0.056</v>
@@ -2343,7 +2343,7 @@
         <v>0.767</v>
       </c>
       <c r="G11" t="n">
-        <v>0.733</v>
+        <v>0.767</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
@@ -2935,7 +2935,7 @@
         <v>0.833</v>
       </c>
       <c r="G27" t="n">
-        <v>0.826</v>
+        <v>0.833</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
@@ -3527,7 +3527,7 @@
         <v>0.87</v>
       </c>
       <c r="G43" t="n">
-        <v>0.826</v>
+        <v>0.87</v>
       </c>
       <c r="H43" t="n">
         <v>1</v>
@@ -5892,13 +5892,13 @@
         <v>10</v>
       </c>
       <c r="F107" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="G107" t="n">
         <v>0.7</v>
       </c>
       <c r="H107" t="n">
-        <v>0.552</v>
+        <v>0.36</v>
       </c>
       <c r="I107" t="n">
         <v>1</v>
@@ -6752,7 +6752,7 @@
         <v>0.348</v>
       </c>
       <c r="I130" t="n">
-        <v>0.997</v>
+        <v>0.923</v>
       </c>
     </row>
     <row r="131">
@@ -6789,7 +6789,7 @@
         <v>0.4</v>
       </c>
       <c r="I131" t="n">
-        <v>0.997</v>
+        <v>0.923</v>
       </c>
     </row>
     <row r="132">
@@ -6863,7 +6863,7 @@
         <v>0.462</v>
       </c>
       <c r="I133" t="n">
-        <v>0.997</v>
+        <v>0.923</v>
       </c>
     </row>
     <row r="134">
@@ -6974,7 +6974,7 @@
         <v>0.23</v>
       </c>
       <c r="I136" t="n">
-        <v>0.997</v>
+        <v>0.923</v>
       </c>
     </row>
     <row r="137">
@@ -7048,7 +7048,7 @@
         <v>0.158</v>
       </c>
       <c r="I138" t="n">
-        <v>0.997</v>
+        <v>0.923</v>
       </c>
     </row>
     <row r="139">
@@ -7076,16 +7076,16 @@
         <v>10</v>
       </c>
       <c r="F139" t="n">
-        <v>0.739</v>
+        <v>0.783</v>
       </c>
       <c r="G139" t="n">
         <v>0.609</v>
       </c>
       <c r="H139" t="n">
-        <v>0.53</v>
+        <v>0.337</v>
       </c>
       <c r="I139" t="n">
-        <v>0.997</v>
+        <v>0.923</v>
       </c>
     </row>
     <row r="140">
@@ -7233,7 +7233,7 @@
         <v>0.407</v>
       </c>
       <c r="I143" t="n">
-        <v>0.997</v>
+        <v>0.923</v>
       </c>
     </row>
     <row r="144">
@@ -7668,13 +7668,13 @@
         <v>10</v>
       </c>
       <c r="F155" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="G155" t="n">
         <v>0.867</v>
       </c>
       <c r="H155" t="n">
-        <v>0.731</v>
+        <v>1</v>
       </c>
       <c r="I155" t="n">
         <v>1</v>
@@ -8852,13 +8852,13 @@
         <v>10</v>
       </c>
       <c r="F187" t="n">
-        <v>0.739</v>
+        <v>0.783</v>
       </c>
       <c r="G187" t="n">
         <v>0.826</v>
       </c>
       <c r="H187" t="n">
-        <v>0.722</v>
+        <v>1</v>
       </c>
       <c r="I187" t="n">
         <v>1</v>
@@ -9444,10 +9444,10 @@
         <v>10</v>
       </c>
       <c r="F203" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="G203" t="n">
-        <v>0.6</v>
+        <v>0.633</v>
       </c>
       <c r="H203" t="n">
         <v>1</v>
@@ -10036,10 +10036,10 @@
         <v>10</v>
       </c>
       <c r="F219" t="n">
-        <v>0.917</v>
+        <v>0.923</v>
       </c>
       <c r="G219" t="n">
-        <v>0.923</v>
+        <v>0.929</v>
       </c>
       <c r="H219" t="n">
         <v>1</v>
@@ -10628,10 +10628,10 @@
         <v>10</v>
       </c>
       <c r="F235" t="n">
-        <v>0.478</v>
+        <v>0.522</v>
       </c>
       <c r="G235" t="n">
-        <v>0.522</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="H235" t="n">
         <v>1</v>
@@ -11220,13 +11220,13 @@
         <v>10</v>
       </c>
       <c r="F251" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="G251" t="n">
-        <v>0.7</v>
+        <v>0.733</v>
       </c>
       <c r="H251" t="n">
-        <v>0.422</v>
+        <v>0.412</v>
       </c>
       <c r="I251" t="n">
         <v>0.876</v>
@@ -11812,10 +11812,10 @@
         <v>10</v>
       </c>
       <c r="F267" t="n">
-        <v>0.917</v>
+        <v>0.923</v>
       </c>
       <c r="G267" t="n">
-        <v>0.889</v>
+        <v>0.895</v>
       </c>
       <c r="H267" t="n">
         <v>1</v>
@@ -12404,16 +12404,16 @@
         <v>10</v>
       </c>
       <c r="F283" t="n">
-        <v>0.478</v>
+        <v>0.522</v>
       </c>
       <c r="G283" t="n">
-        <v>0.696</v>
+        <v>0.739</v>
       </c>
       <c r="H283" t="n">
-        <v>0.231</v>
+        <v>0.221</v>
       </c>
       <c r="I283" t="n">
-        <v>0.527</v>
+        <v>0.506</v>
       </c>
     </row>
     <row r="284">

--- a/eval/results/statistical_tests_new30.xlsx
+++ b/eval/results/statistical_tests_new30.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Paired Tests" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Fisher Exact Test" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Table3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16673,4 +16674,110 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>QID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>base_prec</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>FT_prec</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>QSP_prec</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>base_rec</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>FT_rec</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>QSP_rec</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>69.2</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>69.6</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>100.0*†</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/eval/results/statistical_tests_new30.xlsx
+++ b/eval/results/statistical_tests_new30.xlsx
@@ -16682,7 +16682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16777,6 +16777,231 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>82.6</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>85.7</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>85.7</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>79.2</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>100.0*†</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>85.7**</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>81.8</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>90.9</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>78.3</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>47.4</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>94.7**</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>85.7</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>94.7**</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>81.2</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>90.9</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>86.4</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>95.0*†</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/eval/results/statistical_tests_new30.xlsx
+++ b/eval/results/statistical_tests_new30.xlsx
@@ -504,22 +504,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.104</v>
+        <v>0.155</v>
       </c>
       <c r="F2" t="n">
-        <v>0.823</v>
+        <v>0.783</v>
       </c>
       <c r="G2" t="n">
-        <v>0.856</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.133</v>
+        <v>0.172</v>
       </c>
       <c r="I2" t="n">
-        <v>0.102</v>
+        <v>0.144</v>
       </c>
       <c r="J2" t="n">
-        <v>0.156</v>
+        <v>0.376</v>
       </c>
     </row>
     <row r="3">
@@ -544,22 +544,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.127</v>
+        <v>0.199</v>
       </c>
       <c r="F3" t="n">
-        <v>0.823</v>
+        <v>0.783</v>
       </c>
       <c r="G3" t="n">
-        <v>0.856</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>0.133</v>
+        <v>0.172</v>
       </c>
       <c r="I3" t="n">
-        <v>0.102</v>
+        <v>0.144</v>
       </c>
       <c r="J3" t="n">
-        <v>0.182</v>
+        <v>0.298</v>
       </c>
     </row>
     <row r="4">
@@ -584,22 +584,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.0165</v>
+        <v>0.478</v>
       </c>
       <c r="F4" t="n">
-        <v>0.823</v>
+        <v>0.783</v>
       </c>
       <c r="G4" t="n">
-        <v>0.783</v>
+        <v>0.771</v>
       </c>
       <c r="H4" t="n">
-        <v>0.133</v>
+        <v>0.172</v>
       </c>
       <c r="I4" t="n">
-        <v>0.153</v>
+        <v>0.169</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0922</v>
+        <v>0.478</v>
       </c>
     </row>
     <row r="5">
@@ -624,22 +624,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.016</v>
+        <v>0.304</v>
       </c>
       <c r="F5" t="n">
-        <v>0.823</v>
+        <v>0.783</v>
       </c>
       <c r="G5" t="n">
-        <v>0.783</v>
+        <v>0.771</v>
       </c>
       <c r="H5" t="n">
-        <v>0.133</v>
+        <v>0.172</v>
       </c>
       <c r="I5" t="n">
-        <v>0.153</v>
+        <v>0.169</v>
       </c>
       <c r="J5" t="n">
-        <v>0.096</v>
+        <v>0.365</v>
       </c>
     </row>
     <row r="6">
@@ -664,22 +664,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.0461</v>
+        <v>0.188</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.796</v>
       </c>
       <c r="G6" t="n">
-        <v>0.771</v>
+        <v>0.762</v>
       </c>
       <c r="H6" t="n">
-        <v>0.125</v>
+        <v>0.15</v>
       </c>
       <c r="I6" t="n">
-        <v>0.111</v>
+        <v>0.124</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0922</v>
+        <v>0.376</v>
       </c>
     </row>
     <row r="7">
@@ -704,22 +704,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.047</v>
+        <v>0.0859</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.796</v>
       </c>
       <c r="G7" t="n">
-        <v>0.771</v>
+        <v>0.762</v>
       </c>
       <c r="H7" t="n">
-        <v>0.125</v>
+        <v>0.15</v>
       </c>
       <c r="I7" t="n">
-        <v>0.111</v>
+        <v>0.124</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0984</v>
+        <v>0.258</v>
       </c>
     </row>
     <row r="8">
@@ -744,22 +744,22 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.262</v>
+        <v>0.273</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.796</v>
       </c>
       <c r="G8" t="n">
-        <v>0.838</v>
+        <v>0.819</v>
       </c>
       <c r="H8" t="n">
-        <v>0.125</v>
+        <v>0.15</v>
       </c>
       <c r="I8" t="n">
-        <v>0.111</v>
+        <v>0.132</v>
       </c>
       <c r="J8" t="n">
-        <v>0.314</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="9">
@@ -784,22 +784,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.152</v>
+        <v>0.165</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.796</v>
       </c>
       <c r="G9" t="n">
-        <v>0.838</v>
+        <v>0.819</v>
       </c>
       <c r="H9" t="n">
-        <v>0.125</v>
+        <v>0.15</v>
       </c>
       <c r="I9" t="n">
-        <v>0.111</v>
+        <v>0.132</v>
       </c>
       <c r="J9" t="n">
-        <v>0.182</v>
+        <v>0.298</v>
       </c>
     </row>
     <row r="10">
@@ -827,19 +827,19 @@
         <v>0.453</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7</v>
+        <v>0.679</v>
       </c>
       <c r="G10" t="n">
-        <v>0.677</v>
+        <v>0.656</v>
       </c>
       <c r="H10" t="n">
-        <v>0.165</v>
+        <v>0.191</v>
       </c>
       <c r="I10" t="n">
-        <v>0.172</v>
+        <v>0.186</v>
       </c>
       <c r="J10" t="n">
-        <v>0.453</v>
+        <v>0.478</v>
       </c>
     </row>
     <row r="11">
@@ -867,16 +867,16 @@
         <v>0.607</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7</v>
+        <v>0.679</v>
       </c>
       <c r="G11" t="n">
-        <v>0.677</v>
+        <v>0.656</v>
       </c>
       <c r="H11" t="n">
-        <v>0.165</v>
+        <v>0.191</v>
       </c>
       <c r="I11" t="n">
-        <v>0.172</v>
+        <v>0.186</v>
       </c>
       <c r="J11" t="n">
         <v>0.607</v>
@@ -904,22 +904,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.0448</v>
+        <v>0.0253</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7</v>
+        <v>0.679</v>
       </c>
       <c r="G12" t="n">
-        <v>0.769</v>
+        <v>0.754</v>
       </c>
       <c r="H12" t="n">
-        <v>0.165</v>
+        <v>0.191</v>
       </c>
       <c r="I12" t="n">
-        <v>0.142</v>
+        <v>0.158</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0922</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="13">
@@ -944,22 +944,22 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.0492</v>
+        <v>0.0338</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7</v>
+        <v>0.679</v>
       </c>
       <c r="G13" t="n">
-        <v>0.769</v>
+        <v>0.754</v>
       </c>
       <c r="H13" t="n">
-        <v>0.165</v>
+        <v>0.191</v>
       </c>
       <c r="I13" t="n">
-        <v>0.142</v>
+        <v>0.158</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0984</v>
+        <v>0.203</v>
       </c>
     </row>
     <row r="14">
@@ -984,22 +984,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.0546</v>
       </c>
       <c r="F14" t="n">
-        <v>0.833</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>0.892</v>
+        <v>0.881</v>
       </c>
       <c r="H14" t="n">
-        <v>0.184</v>
+        <v>0.205</v>
       </c>
       <c r="I14" t="n">
-        <v>0.103</v>
+        <v>0.112</v>
       </c>
       <c r="J14" t="n">
-        <v>0.391</v>
+        <v>0.328</v>
       </c>
     </row>
     <row r="15">
@@ -1024,22 +1024,22 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.0218</v>
+        <v>0.0284</v>
       </c>
       <c r="F15" t="n">
-        <v>0.833</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>0.892</v>
+        <v>0.881</v>
       </c>
       <c r="H15" t="n">
-        <v>0.184</v>
+        <v>0.205</v>
       </c>
       <c r="I15" t="n">
-        <v>0.103</v>
+        <v>0.112</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0843</v>
+        <v>0.0852</v>
       </c>
     </row>
     <row r="16">
@@ -1064,22 +1064,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.536</v>
+        <v>0.261</v>
       </c>
       <c r="F16" t="n">
-        <v>0.833</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>0.841</v>
+        <v>0.828</v>
       </c>
       <c r="H16" t="n">
-        <v>0.184</v>
+        <v>0.205</v>
       </c>
       <c r="I16" t="n">
-        <v>0.192</v>
+        <v>0.214</v>
       </c>
       <c r="J16" t="n">
-        <v>0.588</v>
+        <v>0.502</v>
       </c>
     </row>
     <row r="17">
@@ -1104,22 +1104,22 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.285</v>
+        <v>0.241</v>
       </c>
       <c r="F17" t="n">
-        <v>0.833</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>0.841</v>
+        <v>0.828</v>
       </c>
       <c r="H17" t="n">
-        <v>0.184</v>
+        <v>0.205</v>
       </c>
       <c r="I17" t="n">
-        <v>0.192</v>
+        <v>0.214</v>
       </c>
       <c r="J17" t="n">
-        <v>0.311</v>
+        <v>0.289</v>
       </c>
     </row>
     <row r="18">
@@ -1144,22 +1144,22 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.588</v>
+        <v>0.502</v>
       </c>
       <c r="F18" t="n">
-        <v>0.857</v>
+        <v>0.85</v>
       </c>
       <c r="G18" t="n">
-        <v>0.874</v>
+        <v>0.873</v>
       </c>
       <c r="H18" t="n">
-        <v>0.123</v>
+        <v>0.138</v>
       </c>
       <c r="I18" t="n">
-        <v>0.177</v>
+        <v>0.178</v>
       </c>
       <c r="J18" t="n">
-        <v>0.588</v>
+        <v>0.502</v>
       </c>
     </row>
     <row r="19">
@@ -1184,22 +1184,22 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.0844</v>
+        <v>0.0712</v>
       </c>
       <c r="F19" t="n">
-        <v>0.857</v>
+        <v>0.85</v>
       </c>
       <c r="G19" t="n">
-        <v>0.874</v>
+        <v>0.873</v>
       </c>
       <c r="H19" t="n">
-        <v>0.123</v>
+        <v>0.138</v>
       </c>
       <c r="I19" t="n">
-        <v>0.177</v>
+        <v>0.178</v>
       </c>
       <c r="J19" t="n">
-        <v>0.165</v>
+        <v>0.142</v>
       </c>
     </row>
     <row r="20">
@@ -1224,22 +1224,22 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.437</v>
+        <v>0.415</v>
       </c>
       <c r="F20" t="n">
-        <v>0.857</v>
+        <v>0.85</v>
       </c>
       <c r="G20" t="n">
-        <v>0.888</v>
+        <v>0.884</v>
       </c>
       <c r="H20" t="n">
-        <v>0.123</v>
+        <v>0.138</v>
       </c>
       <c r="I20" t="n">
-        <v>0.179</v>
+        <v>0.182</v>
       </c>
       <c r="J20" t="n">
-        <v>0.588</v>
+        <v>0.502</v>
       </c>
     </row>
     <row r="21">
@@ -1267,16 +1267,16 @@
         <v>0.11</v>
       </c>
       <c r="F21" t="n">
-        <v>0.857</v>
+        <v>0.85</v>
       </c>
       <c r="G21" t="n">
-        <v>0.888</v>
+        <v>0.884</v>
       </c>
       <c r="H21" t="n">
-        <v>0.123</v>
+        <v>0.138</v>
       </c>
       <c r="I21" t="n">
-        <v>0.179</v>
+        <v>0.182</v>
       </c>
       <c r="J21" t="n">
         <v>0.165</v>
@@ -1304,22 +1304,22 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.217</v>
+        <v>0.201</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.801</v>
       </c>
       <c r="G22" t="n">
-        <v>0.869</v>
+        <v>0.856</v>
       </c>
       <c r="H22" t="n">
-        <v>0.149</v>
+        <v>0.178</v>
       </c>
       <c r="I22" t="n">
-        <v>0.167</v>
+        <v>0.183</v>
       </c>
       <c r="J22" t="n">
-        <v>0.588</v>
+        <v>0.502</v>
       </c>
     </row>
     <row r="23">
@@ -1347,19 +1347,19 @@
         <v>0.0281</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.801</v>
       </c>
       <c r="G23" t="n">
-        <v>0.869</v>
+        <v>0.856</v>
       </c>
       <c r="H23" t="n">
-        <v>0.149</v>
+        <v>0.178</v>
       </c>
       <c r="I23" t="n">
-        <v>0.167</v>
+        <v>0.183</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0843</v>
+        <v>0.0852</v>
       </c>
     </row>
     <row r="24">
@@ -1384,22 +1384,22 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.295</v>
+        <v>0.454</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.801</v>
       </c>
       <c r="G24" t="n">
-        <v>0.787</v>
+        <v>0.779</v>
       </c>
       <c r="H24" t="n">
-        <v>0.149</v>
+        <v>0.178</v>
       </c>
       <c r="I24" t="n">
-        <v>0.183</v>
+        <v>0.187</v>
       </c>
       <c r="J24" t="n">
-        <v>0.588</v>
+        <v>0.502</v>
       </c>
     </row>
     <row r="25">
@@ -1424,22 +1424,22 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.311</v>
+        <v>0.463</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.801</v>
       </c>
       <c r="G25" t="n">
-        <v>0.787</v>
+        <v>0.779</v>
       </c>
       <c r="H25" t="n">
-        <v>0.149</v>
+        <v>0.178</v>
       </c>
       <c r="I25" t="n">
-        <v>0.183</v>
+        <v>0.187</v>
       </c>
       <c r="J25" t="n">
-        <v>0.311</v>
+        <v>0.463</v>
       </c>
     </row>
     <row r="26">
@@ -1464,22 +1464,22 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.723</v>
+        <v>0.747</v>
       </c>
       <c r="F26" t="n">
-        <v>0.86</v>
+        <v>0.798</v>
       </c>
       <c r="G26" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="H26" t="n">
-        <v>0.166</v>
+        <v>0.226</v>
       </c>
       <c r="I26" t="n">
-        <v>0.148</v>
+        <v>0.187</v>
       </c>
       <c r="J26" t="n">
-        <v>0.723</v>
+        <v>0.747</v>
       </c>
     </row>
     <row r="27">
@@ -1504,22 +1504,22 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.332</v>
+        <v>0.327</v>
       </c>
       <c r="F27" t="n">
-        <v>0.86</v>
+        <v>0.798</v>
       </c>
       <c r="G27" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="H27" t="n">
-        <v>0.166</v>
+        <v>0.226</v>
       </c>
       <c r="I27" t="n">
-        <v>0.148</v>
+        <v>0.187</v>
       </c>
       <c r="J27" t="n">
-        <v>0.398</v>
+        <v>0.392</v>
       </c>
     </row>
     <row r="28">
@@ -1544,22 +1544,22 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.00444</v>
+        <v>0.0861</v>
       </c>
       <c r="F28" t="n">
-        <v>0.86</v>
+        <v>0.798</v>
       </c>
       <c r="G28" t="n">
-        <v>0.758</v>
+        <v>0.741</v>
       </c>
       <c r="H28" t="n">
-        <v>0.166</v>
+        <v>0.226</v>
       </c>
       <c r="I28" t="n">
-        <v>0.262</v>
+        <v>0.285</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0133</v>
+        <v>0.129</v>
       </c>
     </row>
     <row r="29">
@@ -1584,22 +1584,22 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.00585</v>
+        <v>0.117</v>
       </c>
       <c r="F29" t="n">
-        <v>0.86</v>
+        <v>0.798</v>
       </c>
       <c r="G29" t="n">
-        <v>0.758</v>
+        <v>0.741</v>
       </c>
       <c r="H29" t="n">
-        <v>0.166</v>
+        <v>0.226</v>
       </c>
       <c r="I29" t="n">
-        <v>0.262</v>
+        <v>0.285</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0175</v>
+        <v>0.176</v>
       </c>
     </row>
     <row r="30">
@@ -1624,22 +1624,22 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.00393</v>
+        <v>0.0113</v>
       </c>
       <c r="F30" t="n">
-        <v>0.832</v>
+        <v>0.805</v>
       </c>
       <c r="G30" t="n">
-        <v>0.651</v>
+        <v>0.641</v>
       </c>
       <c r="H30" t="n">
-        <v>0.212</v>
+        <v>0.224</v>
       </c>
       <c r="I30" t="n">
-        <v>0.226</v>
+        <v>0.227</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0133</v>
+        <v>0.0338</v>
       </c>
     </row>
     <row r="31">
@@ -1664,22 +1664,22 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.00147</v>
+        <v>0.00465</v>
       </c>
       <c r="F31" t="n">
-        <v>0.832</v>
+        <v>0.805</v>
       </c>
       <c r="G31" t="n">
-        <v>0.651</v>
+        <v>0.641</v>
       </c>
       <c r="H31" t="n">
-        <v>0.212</v>
+        <v>0.224</v>
       </c>
       <c r="I31" t="n">
-        <v>0.226</v>
+        <v>0.227</v>
       </c>
       <c r="J31" t="n">
-        <v>0.00882</v>
+        <v>0.0279</v>
       </c>
     </row>
     <row r="32">
@@ -1704,22 +1704,22 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.505</v>
+        <v>0.516</v>
       </c>
       <c r="F32" t="n">
-        <v>0.832</v>
+        <v>0.805</v>
       </c>
       <c r="G32" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="H32" t="n">
-        <v>0.212</v>
+        <v>0.224</v>
       </c>
       <c r="I32" t="n">
-        <v>0.21</v>
+        <v>0.238</v>
       </c>
       <c r="J32" t="n">
-        <v>0.606</v>
+        <v>0.619</v>
       </c>
     </row>
     <row r="33">
@@ -1747,16 +1747,16 @@
         <v>0.721</v>
       </c>
       <c r="F33" t="n">
-        <v>0.832</v>
+        <v>0.805</v>
       </c>
       <c r="G33" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="H33" t="n">
-        <v>0.212</v>
+        <v>0.224</v>
       </c>
       <c r="I33" t="n">
-        <v>0.21</v>
+        <v>0.238</v>
       </c>
       <c r="J33" t="n">
         <v>0.721</v>
@@ -1787,19 +1787,19 @@
         <v>0.0169</v>
       </c>
       <c r="F34" t="n">
-        <v>0.659</v>
+        <v>0.625</v>
       </c>
       <c r="G34" t="n">
-        <v>0.522</v>
+        <v>0.488</v>
       </c>
       <c r="H34" t="n">
-        <v>0.219</v>
+        <v>0.237</v>
       </c>
       <c r="I34" t="n">
-        <v>0.184</v>
+        <v>0.174</v>
       </c>
       <c r="J34" t="n">
-        <v>0.0301</v>
+        <v>0.0338</v>
       </c>
     </row>
     <row r="35">
@@ -1827,19 +1827,19 @@
         <v>0.0408</v>
       </c>
       <c r="F35" t="n">
-        <v>0.659</v>
+        <v>0.625</v>
       </c>
       <c r="G35" t="n">
-        <v>0.522</v>
+        <v>0.488</v>
       </c>
       <c r="H35" t="n">
-        <v>0.219</v>
+        <v>0.237</v>
       </c>
       <c r="I35" t="n">
-        <v>0.184</v>
+        <v>0.174</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0612</v>
+        <v>0.08160000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -1864,22 +1864,22 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.0201</v>
+        <v>0.00733</v>
       </c>
       <c r="F36" t="n">
-        <v>0.659</v>
+        <v>0.625</v>
       </c>
       <c r="G36" t="n">
-        <v>0.805</v>
+        <v>0.783</v>
       </c>
       <c r="H36" t="n">
-        <v>0.219</v>
+        <v>0.237</v>
       </c>
       <c r="I36" t="n">
-        <v>0.206</v>
+        <v>0.233</v>
       </c>
       <c r="J36" t="n">
-        <v>0.0301</v>
+        <v>0.0338</v>
       </c>
     </row>
     <row r="37">
@@ -1904,22 +1904,22 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.028</v>
+        <v>0.0134</v>
       </c>
       <c r="F37" t="n">
-        <v>0.659</v>
+        <v>0.625</v>
       </c>
       <c r="G37" t="n">
-        <v>0.805</v>
+        <v>0.783</v>
       </c>
       <c r="H37" t="n">
-        <v>0.219</v>
+        <v>0.237</v>
       </c>
       <c r="I37" t="n">
-        <v>0.206</v>
+        <v>0.233</v>
       </c>
       <c r="J37" t="n">
-        <v>0.056</v>
+        <v>0.0402</v>
       </c>
     </row>
     <row r="38">
@@ -1944,22 +1944,22 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.323</v>
+        <v>0.278</v>
       </c>
       <c r="F38" t="n">
-        <v>0.826</v>
+        <v>0.78</v>
       </c>
       <c r="G38" t="n">
-        <v>0.858</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="H38" t="n">
-        <v>0.155</v>
+        <v>0.196</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0927</v>
+        <v>0.121</v>
       </c>
       <c r="J38" t="n">
-        <v>0.388</v>
+        <v>0.334</v>
       </c>
     </row>
     <row r="39">
@@ -1984,22 +1984,22 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.6</v>
+        <v>0.534</v>
       </c>
       <c r="F39" t="n">
-        <v>0.826</v>
+        <v>0.78</v>
       </c>
       <c r="G39" t="n">
-        <v>0.858</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="H39" t="n">
-        <v>0.155</v>
+        <v>0.196</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0927</v>
+        <v>0.121</v>
       </c>
       <c r="J39" t="n">
-        <v>0.6</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="40">
@@ -2024,22 +2024,22 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.0297</v>
+        <v>0.175</v>
       </c>
       <c r="F40" t="n">
-        <v>0.826</v>
+        <v>0.78</v>
       </c>
       <c r="G40" t="n">
-        <v>0.76</v>
+        <v>0.742</v>
       </c>
       <c r="H40" t="n">
-        <v>0.155</v>
+        <v>0.196</v>
       </c>
       <c r="I40" t="n">
-        <v>0.216</v>
+        <v>0.24</v>
       </c>
       <c r="J40" t="n">
-        <v>0.102</v>
+        <v>0.262</v>
       </c>
     </row>
     <row r="41">
@@ -2064,22 +2064,22 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.0229</v>
+        <v>0.249</v>
       </c>
       <c r="F41" t="n">
-        <v>0.826</v>
+        <v>0.78</v>
       </c>
       <c r="G41" t="n">
-        <v>0.76</v>
+        <v>0.742</v>
       </c>
       <c r="H41" t="n">
-        <v>0.155</v>
+        <v>0.196</v>
       </c>
       <c r="I41" t="n">
-        <v>0.216</v>
+        <v>0.24</v>
       </c>
       <c r="J41" t="n">
-        <v>0.0687</v>
+        <v>0.373</v>
       </c>
     </row>
     <row r="42">
@@ -2104,22 +2104,22 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.0341</v>
+        <v>0.0634</v>
       </c>
       <c r="F42" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.799</v>
       </c>
       <c r="G42" t="n">
-        <v>0.716</v>
+        <v>0.708</v>
       </c>
       <c r="H42" t="n">
-        <v>0.161</v>
+        <v>0.171</v>
       </c>
       <c r="I42" t="n">
         <v>0.191</v>
       </c>
       <c r="J42" t="n">
-        <v>0.102</v>
+        <v>0.127</v>
       </c>
     </row>
     <row r="43">
@@ -2144,22 +2144,22 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.0171</v>
+        <v>0.0409</v>
       </c>
       <c r="F43" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.799</v>
       </c>
       <c r="G43" t="n">
-        <v>0.716</v>
+        <v>0.708</v>
       </c>
       <c r="H43" t="n">
-        <v>0.161</v>
+        <v>0.171</v>
       </c>
       <c r="I43" t="n">
         <v>0.191</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0687</v>
+        <v>0.123</v>
       </c>
     </row>
     <row r="44">
@@ -2184,22 +2184,22 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.919</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.799</v>
       </c>
       <c r="G44" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.791</v>
       </c>
       <c r="H44" t="n">
-        <v>0.161</v>
+        <v>0.171</v>
       </c>
       <c r="I44" t="n">
-        <v>0.168</v>
+        <v>0.187</v>
       </c>
       <c r="J44" t="n">
-        <v>0.919</v>
+        <v>0.8110000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -2224,22 +2224,22 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.583</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.799</v>
       </c>
       <c r="G45" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.791</v>
       </c>
       <c r="H45" t="n">
-        <v>0.161</v>
+        <v>0.171</v>
       </c>
       <c r="I45" t="n">
-        <v>0.168</v>
+        <v>0.187</v>
       </c>
       <c r="J45" t="n">
-        <v>0.6</v>
+        <v>0.8139999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -2264,22 +2264,22 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.0615</v>
+        <v>0.0597</v>
       </c>
       <c r="F46" t="n">
-        <v>0.697</v>
+        <v>0.671</v>
       </c>
       <c r="G46" t="n">
-        <v>0.619</v>
+        <v>0.592</v>
       </c>
       <c r="H46" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="J46" t="n">
         <v>0.127</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0.104</v>
       </c>
     </row>
     <row r="47">
@@ -2307,19 +2307,19 @@
         <v>0.0833</v>
       </c>
       <c r="F47" t="n">
-        <v>0.697</v>
+        <v>0.671</v>
       </c>
       <c r="G47" t="n">
-        <v>0.619</v>
+        <v>0.592</v>
       </c>
       <c r="H47" t="n">
-        <v>0.127</v>
+        <v>0.157</v>
       </c>
       <c r="I47" t="n">
-        <v>0.143</v>
+        <v>0.149</v>
       </c>
       <c r="J47" t="n">
-        <v>0.13</v>
+        <v>0.167</v>
       </c>
     </row>
     <row r="48">
@@ -2344,22 +2344,22 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0308</v>
       </c>
       <c r="F48" t="n">
-        <v>0.697</v>
+        <v>0.671</v>
       </c>
       <c r="G48" t="n">
-        <v>0.767</v>
+        <v>0.749</v>
       </c>
       <c r="H48" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="J48" t="n">
         <v>0.127</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0.161</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0.104</v>
       </c>
     </row>
     <row r="49">
@@ -2384,22 +2384,22 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.0355</v>
       </c>
       <c r="F49" t="n">
-        <v>0.697</v>
+        <v>0.671</v>
       </c>
       <c r="G49" t="n">
-        <v>0.767</v>
+        <v>0.749</v>
       </c>
       <c r="H49" t="n">
-        <v>0.127</v>
+        <v>0.157</v>
       </c>
       <c r="I49" t="n">
-        <v>0.161</v>
+        <v>0.177</v>
       </c>
       <c r="J49" t="n">
-        <v>0.13</v>
+        <v>0.123</v>
       </c>
     </row>
   </sheetData>
@@ -2599,7 +2599,7 @@
         <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0.967</v>
       </c>
       <c r="G5" t="n">
         <v>0.967</v>
@@ -2713,7 +2713,7 @@
         <v>0.867</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9</v>
+        <v>0.867</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
@@ -2784,10 +2784,10 @@
         <v>9</v>
       </c>
       <c r="F10" t="n">
-        <v>0.833</v>
+        <v>0.767</v>
       </c>
       <c r="G10" t="n">
-        <v>0.867</v>
+        <v>0.733</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
@@ -2821,10 +2821,10 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>0.767</v>
+        <v>0.533</v>
       </c>
       <c r="G11" t="n">
-        <v>0.767</v>
+        <v>0.533</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
@@ -2858,13 +2858,13 @@
         <v>11</v>
       </c>
       <c r="F12" t="n">
-        <v>0.633</v>
+        <v>0.6</v>
       </c>
       <c r="G12" t="n">
-        <v>0.733</v>
+        <v>0.7</v>
       </c>
       <c r="H12" t="n">
-        <v>0.58</v>
+        <v>0.589</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
@@ -3006,13 +3006,13 @@
         <v>15</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="G16" t="n">
-        <v>0.867</v>
+        <v>0.733</v>
       </c>
       <c r="H16" t="n">
-        <v>0.731</v>
+        <v>0.779</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
@@ -3043,13 +3043,13 @@
         <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>0.533</v>
+        <v>0.4</v>
       </c>
       <c r="G17" t="n">
-        <v>0.733</v>
+        <v>0.6</v>
       </c>
       <c r="H17" t="n">
-        <v>0.18</v>
+        <v>0.196</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
@@ -3305,7 +3305,7 @@
         <v>0.857</v>
       </c>
       <c r="G24" t="n">
-        <v>0.864</v>
+        <v>0.857</v>
       </c>
       <c r="H24" t="n">
         <v>1</v>
@@ -3413,10 +3413,10 @@
         <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>0.833</v>
+        <v>0.765</v>
       </c>
       <c r="G27" t="n">
-        <v>0.833</v>
+        <v>0.765</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
@@ -3450,13 +3450,13 @@
         <v>11</v>
       </c>
       <c r="F28" t="n">
-        <v>0.792</v>
+        <v>0.783</v>
       </c>
       <c r="G28" t="n">
-        <v>0.905</v>
+        <v>0.9</v>
       </c>
       <c r="H28" t="n">
-        <v>0.422</v>
+        <v>0.42</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
@@ -3598,10 +3598,10 @@
         <v>15</v>
       </c>
       <c r="F32" t="n">
-        <v>0.889</v>
+        <v>0.857</v>
       </c>
       <c r="G32" t="n">
-        <v>0.944</v>
+        <v>0.929</v>
       </c>
       <c r="H32" t="n">
         <v>1</v>
@@ -3635,13 +3635,13 @@
         <v>16</v>
       </c>
       <c r="F33" t="n">
-        <v>0.636</v>
+        <v>0.429</v>
       </c>
       <c r="G33" t="n">
-        <v>0.8</v>
+        <v>0.727</v>
       </c>
       <c r="H33" t="n">
-        <v>0.407</v>
+        <v>0.332</v>
       </c>
       <c r="I33" t="n">
         <v>1</v>
@@ -3783,7 +3783,7 @@
         <v>4</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>0.857</v>
       </c>
       <c r="G37" t="n">
         <v>0.857</v>
@@ -3897,7 +3897,7 @@
         <v>0.947</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>0.947</v>
       </c>
       <c r="H40" t="n">
         <v>1</v>
@@ -3968,10 +3968,10 @@
         <v>9</v>
       </c>
       <c r="F42" t="n">
-        <v>0.833</v>
+        <v>0.767</v>
       </c>
       <c r="G42" t="n">
-        <v>0.867</v>
+        <v>0.733</v>
       </c>
       <c r="H42" t="n">
         <v>1</v>
@@ -4005,10 +4005,10 @@
         <v>10</v>
       </c>
       <c r="F43" t="n">
-        <v>0.87</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>0.87</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="H43" t="n">
         <v>1</v>
@@ -4042,10 +4042,10 @@
         <v>11</v>
       </c>
       <c r="F44" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="G44" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="H44" t="n">
         <v>1</v>
@@ -4190,10 +4190,10 @@
         <v>15</v>
       </c>
       <c r="F48" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G48" t="n">
-        <v>0.85</v>
+        <v>0.65</v>
       </c>
       <c r="H48" t="n">
         <v>1</v>
@@ -4227,13 +4227,13 @@
         <v>16</v>
       </c>
       <c r="F49" t="n">
-        <v>0.412</v>
+        <v>0.176</v>
       </c>
       <c r="G49" t="n">
-        <v>0.706</v>
+        <v>0.471</v>
       </c>
       <c r="H49" t="n">
-        <v>0.166</v>
+        <v>0.141</v>
       </c>
       <c r="I49" t="n">
         <v>1</v>
@@ -4375,13 +4375,13 @@
         <v>4</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>0.923</v>
       </c>
       <c r="G53" t="n">
         <v>0.923</v>
       </c>
       <c r="H53" t="n">
-        <v>0.481</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
         <v>1</v>
@@ -4489,10 +4489,10 @@
         <v>0.9</v>
       </c>
       <c r="G56" t="n">
-        <v>0.927</v>
+        <v>0.9</v>
       </c>
       <c r="H56" t="n">
-        <v>0.712</v>
+        <v>1</v>
       </c>
       <c r="I56" t="n">
         <v>1</v>
@@ -4560,13 +4560,13 @@
         <v>9</v>
       </c>
       <c r="F58" t="n">
-        <v>0.909</v>
+        <v>0.868</v>
       </c>
       <c r="G58" t="n">
-        <v>0.929</v>
+        <v>0.846</v>
       </c>
       <c r="H58" t="n">
-        <v>0.742</v>
+        <v>0.787</v>
       </c>
       <c r="I58" t="n">
         <v>1</v>
@@ -4597,10 +4597,10 @@
         <v>10</v>
       </c>
       <c r="F59" t="n">
-        <v>0.851</v>
+        <v>0.65</v>
       </c>
       <c r="G59" t="n">
-        <v>0.851</v>
+        <v>0.65</v>
       </c>
       <c r="H59" t="n">
         <v>1</v>
@@ -4634,13 +4634,13 @@
         <v>11</v>
       </c>
       <c r="F60" t="n">
-        <v>0.776</v>
+        <v>0.75</v>
       </c>
       <c r="G60" t="n">
-        <v>0.826</v>
+        <v>0.8</v>
       </c>
       <c r="H60" t="n">
-        <v>0.613</v>
+        <v>0.625</v>
       </c>
       <c r="I60" t="n">
         <v>1</v>
@@ -4782,13 +4782,13 @@
         <v>15</v>
       </c>
       <c r="F64" t="n">
-        <v>0.842</v>
+        <v>0.706</v>
       </c>
       <c r="G64" t="n">
-        <v>0.895</v>
+        <v>0.765</v>
       </c>
       <c r="H64" t="n">
-        <v>0.736</v>
+        <v>0.784</v>
       </c>
       <c r="I64" t="n">
         <v>1</v>
@@ -4819,16 +4819,16 @@
         <v>16</v>
       </c>
       <c r="F65" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="G65" t="n">
-        <v>0.75</v>
+        <v>0.571</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0617</v>
+        <v>0.026</v>
       </c>
       <c r="I65" t="n">
-        <v>0.987</v>
+        <v>0.415</v>
       </c>
     </row>
     <row r="66">
@@ -4967,7 +4967,7 @@
         <v>4</v>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>0.967</v>
       </c>
       <c r="G69" t="n">
         <v>1</v>
@@ -5152,13 +5152,13 @@
         <v>9</v>
       </c>
       <c r="F74" t="n">
-        <v>0.833</v>
+        <v>0.767</v>
       </c>
       <c r="G74" t="n">
-        <v>0.7</v>
+        <v>0.667</v>
       </c>
       <c r="H74" t="n">
-        <v>0.36</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="I74" t="n">
         <v>1</v>
@@ -5189,13 +5189,13 @@
         <v>10</v>
       </c>
       <c r="F75" t="n">
-        <v>0.767</v>
+        <v>0.533</v>
       </c>
       <c r="G75" t="n">
         <v>0.7</v>
       </c>
       <c r="H75" t="n">
-        <v>0.771</v>
+        <v>0.288</v>
       </c>
       <c r="I75" t="n">
         <v>1</v>
@@ -5226,10 +5226,10 @@
         <v>11</v>
       </c>
       <c r="F76" t="n">
-        <v>0.633</v>
+        <v>0.6</v>
       </c>
       <c r="G76" t="n">
-        <v>0.633</v>
+        <v>0.6</v>
       </c>
       <c r="H76" t="n">
         <v>1</v>
@@ -5374,13 +5374,13 @@
         <v>15</v>
       </c>
       <c r="F80" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="G80" t="n">
-        <v>0.633</v>
+        <v>0.533</v>
       </c>
       <c r="H80" t="n">
-        <v>0.252</v>
+        <v>0.43</v>
       </c>
       <c r="I80" t="n">
         <v>1</v>
@@ -5411,13 +5411,13 @@
         <v>16</v>
       </c>
       <c r="F81" t="n">
-        <v>0.533</v>
+        <v>0.4</v>
       </c>
       <c r="G81" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="H81" t="n">
-        <v>0.606</v>
+        <v>1</v>
       </c>
       <c r="I81" t="n">
         <v>1</v>
@@ -5781,13 +5781,13 @@
         <v>10</v>
       </c>
       <c r="F91" t="n">
-        <v>0.833</v>
+        <v>0.765</v>
       </c>
       <c r="G91" t="n">
         <v>0.889</v>
       </c>
       <c r="H91" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.402</v>
       </c>
       <c r="I91" t="n">
         <v>1</v>
@@ -5818,13 +5818,13 @@
         <v>11</v>
       </c>
       <c r="F92" t="n">
-        <v>0.792</v>
+        <v>0.783</v>
       </c>
       <c r="G92" t="n">
-        <v>0.85</v>
+        <v>0.842</v>
       </c>
       <c r="H92" t="n">
-        <v>0.71</v>
+        <v>0.709</v>
       </c>
       <c r="I92" t="n">
         <v>1</v>
@@ -5966,10 +5966,10 @@
         <v>15</v>
       </c>
       <c r="F96" t="n">
-        <v>0.889</v>
+        <v>0.857</v>
       </c>
       <c r="G96" t="n">
-        <v>0.909</v>
+        <v>0.875</v>
       </c>
       <c r="H96" t="n">
         <v>1</v>
@@ -6003,10 +6003,10 @@
         <v>16</v>
       </c>
       <c r="F97" t="n">
-        <v>0.636</v>
+        <v>0.429</v>
       </c>
       <c r="G97" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="H97" t="n">
         <v>1</v>
@@ -6151,7 +6151,7 @@
         <v>4</v>
       </c>
       <c r="F101" t="n">
-        <v>1</v>
+        <v>0.857</v>
       </c>
       <c r="G101" t="n">
         <v>1</v>
@@ -6336,13 +6336,13 @@
         <v>9</v>
       </c>
       <c r="F106" t="n">
-        <v>0.833</v>
+        <v>0.767</v>
       </c>
       <c r="G106" t="n">
-        <v>0.7</v>
+        <v>0.667</v>
       </c>
       <c r="H106" t="n">
-        <v>0.36</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="I106" t="n">
         <v>1</v>
@@ -6373,13 +6373,13 @@
         <v>10</v>
       </c>
       <c r="F107" t="n">
-        <v>0.87</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="G107" t="n">
         <v>0.696</v>
       </c>
       <c r="H107" t="n">
-        <v>0.284</v>
+        <v>0.542</v>
       </c>
       <c r="I107" t="n">
         <v>1</v>
@@ -6410,13 +6410,13 @@
         <v>11</v>
       </c>
       <c r="F108" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="G108" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="H108" t="n">
-        <v>0.754</v>
+        <v>0.762</v>
       </c>
       <c r="I108" t="n">
         <v>1</v>
@@ -6558,16 +6558,16 @@
         <v>15</v>
       </c>
       <c r="F112" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G112" t="n">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="H112" t="n">
-        <v>0.0958</v>
+        <v>0.205</v>
       </c>
       <c r="I112" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -6595,16 +6595,16 @@
         <v>16</v>
       </c>
       <c r="F113" t="n">
-        <v>0.412</v>
+        <v>0.176</v>
       </c>
       <c r="G113" t="n">
-        <v>0.118</v>
+        <v>0.0588</v>
       </c>
       <c r="H113" t="n">
-        <v>0.118</v>
+        <v>0.601</v>
       </c>
       <c r="I113" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -6743,16 +6743,16 @@
         <v>4</v>
       </c>
       <c r="F117" t="n">
-        <v>1</v>
+        <v>0.923</v>
       </c>
       <c r="G117" t="n">
         <v>1</v>
       </c>
       <c r="H117" t="n">
-        <v>1</v>
+        <v>0.481</v>
       </c>
       <c r="I117" t="n">
-        <v>1</v>
+        <v>0.963</v>
       </c>
     </row>
     <row r="118">
@@ -6900,7 +6900,7 @@
         <v>0.321</v>
       </c>
       <c r="I121" t="n">
-        <v>1</v>
+        <v>0.963</v>
       </c>
     </row>
     <row r="122">
@@ -6928,16 +6928,16 @@
         <v>9</v>
       </c>
       <c r="F122" t="n">
-        <v>0.909</v>
+        <v>0.868</v>
       </c>
       <c r="G122" t="n">
-        <v>0.824</v>
+        <v>0.8</v>
       </c>
       <c r="H122" t="n">
-        <v>0.254</v>
+        <v>0.43</v>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>0.963</v>
       </c>
     </row>
     <row r="123">
@@ -6965,16 +6965,16 @@
         <v>10</v>
       </c>
       <c r="F123" t="n">
-        <v>0.851</v>
+        <v>0.65</v>
       </c>
       <c r="G123" t="n">
         <v>0.78</v>
       </c>
       <c r="H123" t="n">
-        <v>0.42</v>
+        <v>0.225</v>
       </c>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>0.963</v>
       </c>
     </row>
     <row r="124">
@@ -7002,13 +7002,13 @@
         <v>11</v>
       </c>
       <c r="F124" t="n">
-        <v>0.776</v>
+        <v>0.75</v>
       </c>
       <c r="G124" t="n">
-        <v>0.756</v>
+        <v>0.727</v>
       </c>
       <c r="H124" t="n">
-        <v>1</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="I124" t="n">
         <v>1</v>
@@ -7048,7 +7048,7 @@
         <v>0.473</v>
       </c>
       <c r="I125" t="n">
-        <v>1</v>
+        <v>0.963</v>
       </c>
     </row>
     <row r="126">
@@ -7122,7 +7122,7 @@
         <v>0.466</v>
       </c>
       <c r="I127" t="n">
-        <v>1</v>
+        <v>0.963</v>
       </c>
     </row>
     <row r="128">
@@ -7150,16 +7150,16 @@
         <v>15</v>
       </c>
       <c r="F128" t="n">
-        <v>0.842</v>
+        <v>0.706</v>
       </c>
       <c r="G128" t="n">
-        <v>0.645</v>
+        <v>0.5</v>
       </c>
       <c r="H128" t="n">
-        <v>0.0912</v>
+        <v>0.121</v>
       </c>
       <c r="I128" t="n">
-        <v>0.73</v>
+        <v>0.963</v>
       </c>
     </row>
     <row r="129">
@@ -7187,16 +7187,16 @@
         <v>16</v>
       </c>
       <c r="F129" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="G129" t="n">
-        <v>0.19</v>
+        <v>0.1</v>
       </c>
       <c r="H129" t="n">
-        <v>0.0372</v>
+        <v>0.259</v>
       </c>
       <c r="I129" t="n">
-        <v>0.596</v>
+        <v>0.963</v>
       </c>
     </row>
     <row r="130">
@@ -7520,13 +7520,13 @@
         <v>9</v>
       </c>
       <c r="F138" t="n">
-        <v>0.8</v>
+        <v>0.767</v>
       </c>
       <c r="G138" t="n">
-        <v>0.6</v>
+        <v>0.533</v>
       </c>
       <c r="H138" t="n">
-        <v>0.158</v>
+        <v>0.103</v>
       </c>
       <c r="I138" t="n">
         <v>1</v>
@@ -7557,13 +7557,13 @@
         <v>10</v>
       </c>
       <c r="F139" t="n">
-        <v>0.833</v>
+        <v>0.767</v>
       </c>
       <c r="G139" t="n">
         <v>0.7</v>
       </c>
       <c r="H139" t="n">
-        <v>0.36</v>
+        <v>0.771</v>
       </c>
       <c r="I139" t="n">
         <v>1</v>
@@ -7594,13 +7594,13 @@
         <v>11</v>
       </c>
       <c r="F140" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="G140" t="n">
-        <v>0.6</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H140" t="n">
-        <v>0.789</v>
+        <v>0.792</v>
       </c>
       <c r="I140" t="n">
         <v>1</v>
@@ -7742,7 +7742,7 @@
         <v>15</v>
       </c>
       <c r="F144" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="G144" t="n">
         <v>0.633</v>
@@ -7779,13 +7779,13 @@
         <v>16</v>
       </c>
       <c r="F145" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.433</v>
       </c>
       <c r="G145" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="H145" t="n">
-        <v>0.596</v>
+        <v>0.195</v>
       </c>
       <c r="I145" t="n">
         <v>1</v>
@@ -8186,10 +8186,10 @@
         <v>11</v>
       </c>
       <c r="F156" t="n">
-        <v>0.895</v>
+        <v>0.889</v>
       </c>
       <c r="G156" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.929</v>
       </c>
       <c r="H156" t="n">
         <v>1</v>
@@ -8334,7 +8334,7 @@
         <v>15</v>
       </c>
       <c r="F160" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="G160" t="n">
         <v>0.696</v>
@@ -8371,13 +8371,13 @@
         <v>16</v>
       </c>
       <c r="F161" t="n">
-        <v>0.583</v>
+        <v>0.5</v>
       </c>
       <c r="G161" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.667</v>
       </c>
       <c r="H161" t="n">
-        <v>0.542</v>
+        <v>0.342</v>
       </c>
       <c r="I161" t="n">
         <v>1</v>
@@ -8417,7 +8417,7 @@
         <v>0.348</v>
       </c>
       <c r="I162" t="n">
-        <v>0.923</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163">
@@ -8454,7 +8454,7 @@
         <v>0.4</v>
       </c>
       <c r="I163" t="n">
-        <v>0.923</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164">
@@ -8528,7 +8528,7 @@
         <v>0.462</v>
       </c>
       <c r="I165" t="n">
-        <v>0.923</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166">
@@ -8639,7 +8639,7 @@
         <v>0.23</v>
       </c>
       <c r="I168" t="n">
-        <v>0.923</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
@@ -8704,16 +8704,16 @@
         <v>9</v>
       </c>
       <c r="F170" t="n">
-        <v>0.8</v>
+        <v>0.767</v>
       </c>
       <c r="G170" t="n">
-        <v>0.6</v>
+        <v>0.533</v>
       </c>
       <c r="H170" t="n">
-        <v>0.158</v>
+        <v>0.103</v>
       </c>
       <c r="I170" t="n">
-        <v>0.923</v>
+        <v>0.827</v>
       </c>
     </row>
     <row r="171">
@@ -8741,16 +8741,16 @@
         <v>10</v>
       </c>
       <c r="F171" t="n">
-        <v>0.783</v>
+        <v>0.696</v>
       </c>
       <c r="G171" t="n">
         <v>0.609</v>
       </c>
       <c r="H171" t="n">
-        <v>0.337</v>
+        <v>0.758</v>
       </c>
       <c r="I171" t="n">
-        <v>0.923</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
@@ -8778,16 +8778,16 @@
         <v>11</v>
       </c>
       <c r="F172" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="G172" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="H172" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="I172" t="n">
-        <v>0.997</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173">
@@ -8898,7 +8898,7 @@
         <v>0.407</v>
       </c>
       <c r="I175" t="n">
-        <v>0.923</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176">
@@ -8926,13 +8926,13 @@
         <v>15</v>
       </c>
       <c r="F176" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G176" t="n">
         <v>0.8</v>
       </c>
       <c r="H176" t="n">
-        <v>0.661</v>
+        <v>1</v>
       </c>
       <c r="I176" t="n">
         <v>1</v>
@@ -8963,13 +8963,13 @@
         <v>16</v>
       </c>
       <c r="F177" t="n">
-        <v>0.824</v>
+        <v>0.588</v>
       </c>
       <c r="G177" t="n">
-        <v>0.765</v>
+        <v>0.706</v>
       </c>
       <c r="H177" t="n">
-        <v>1</v>
+        <v>0.721</v>
       </c>
       <c r="I177" t="n">
         <v>1</v>
@@ -9120,7 +9120,7 @@
         <v>0.203</v>
       </c>
       <c r="I181" t="n">
-        <v>0.762</v>
+        <v>0.751</v>
       </c>
     </row>
     <row r="182">
@@ -9296,16 +9296,16 @@
         <v>9</v>
       </c>
       <c r="F186" t="n">
-        <v>0.889</v>
+        <v>0.868</v>
       </c>
       <c r="G186" t="n">
-        <v>0.75</v>
+        <v>0.696</v>
       </c>
       <c r="H186" t="n">
-        <v>0.075</v>
+        <v>0.0489</v>
       </c>
       <c r="I186" t="n">
-        <v>0.547</v>
+        <v>0.391</v>
       </c>
     </row>
     <row r="187">
@@ -9333,16 +9333,16 @@
         <v>10</v>
       </c>
       <c r="F187" t="n">
-        <v>0.878</v>
+        <v>0.821</v>
       </c>
       <c r="G187" t="n">
         <v>0.757</v>
       </c>
       <c r="H187" t="n">
-        <v>0.238</v>
+        <v>0.579</v>
       </c>
       <c r="I187" t="n">
-        <v>0.762</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188">
@@ -9370,13 +9370,13 @@
         <v>11</v>
       </c>
       <c r="F188" t="n">
-        <v>0.773</v>
+        <v>0.744</v>
       </c>
       <c r="G188" t="n">
-        <v>0.7</v>
+        <v>0.667</v>
       </c>
       <c r="H188" t="n">
-        <v>0.468</v>
+        <v>0.475</v>
       </c>
       <c r="I188" t="n">
         <v>1</v>
@@ -9518,13 +9518,13 @@
         <v>15</v>
       </c>
       <c r="F192" t="n">
-        <v>0.783</v>
+        <v>0.756</v>
       </c>
       <c r="G192" t="n">
         <v>0.744</v>
       </c>
       <c r="H192" t="n">
-        <v>0.804</v>
+        <v>1</v>
       </c>
       <c r="I192" t="n">
         <v>1</v>
@@ -9555,16 +9555,16 @@
         <v>16</v>
       </c>
       <c r="F193" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.541</v>
       </c>
       <c r="G193" t="n">
-        <v>0.722</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="H193" t="n">
-        <v>0.805</v>
+        <v>0.235</v>
       </c>
       <c r="I193" t="n">
-        <v>1</v>
+        <v>0.751</v>
       </c>
     </row>
     <row r="194">
@@ -9888,13 +9888,13 @@
         <v>9</v>
       </c>
       <c r="F202" t="n">
-        <v>0.8</v>
+        <v>0.767</v>
       </c>
       <c r="G202" t="n">
-        <v>0.733</v>
+        <v>0.7</v>
       </c>
       <c r="H202" t="n">
-        <v>0.761</v>
+        <v>0.771</v>
       </c>
       <c r="I202" t="n">
         <v>1</v>
@@ -9925,10 +9925,10 @@
         <v>10</v>
       </c>
       <c r="F203" t="n">
-        <v>0.833</v>
+        <v>0.767</v>
       </c>
       <c r="G203" t="n">
-        <v>0.867</v>
+        <v>0.8</v>
       </c>
       <c r="H203" t="n">
         <v>1</v>
@@ -9962,13 +9962,13 @@
         <v>11</v>
       </c>
       <c r="F204" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="G204" t="n">
-        <v>0.8</v>
+        <v>0.767</v>
       </c>
       <c r="H204" t="n">
-        <v>0.382</v>
+        <v>0.399</v>
       </c>
       <c r="I204" t="n">
         <v>1</v>
@@ -10110,13 +10110,13 @@
         <v>15</v>
       </c>
       <c r="F208" t="n">
-        <v>0.667</v>
+        <v>0.633</v>
       </c>
       <c r="G208" t="n">
-        <v>0.733</v>
+        <v>0.633</v>
       </c>
       <c r="H208" t="n">
-        <v>0.779</v>
+        <v>1</v>
       </c>
       <c r="I208" t="n">
         <v>1</v>
@@ -10147,13 +10147,13 @@
         <v>16</v>
       </c>
       <c r="F209" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.433</v>
       </c>
       <c r="G209" t="n">
-        <v>0.6</v>
+        <v>0.533</v>
       </c>
       <c r="H209" t="n">
-        <v>1</v>
+        <v>0.606</v>
       </c>
       <c r="I209" t="n">
         <v>1</v>
@@ -10554,10 +10554,10 @@
         <v>11</v>
       </c>
       <c r="F220" t="n">
-        <v>0.895</v>
+        <v>0.889</v>
       </c>
       <c r="G220" t="n">
-        <v>0.913</v>
+        <v>0.909</v>
       </c>
       <c r="H220" t="n">
         <v>1</v>
@@ -10702,16 +10702,16 @@
         <v>15</v>
       </c>
       <c r="F224" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="G224" t="n">
         <v>1</v>
       </c>
       <c r="H224" t="n">
-        <v>0.0385</v>
+        <v>0.077</v>
       </c>
       <c r="I224" t="n">
-        <v>0.616</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225">
@@ -10739,13 +10739,13 @@
         <v>16</v>
       </c>
       <c r="F225" t="n">
-        <v>0.583</v>
+        <v>0.5</v>
       </c>
       <c r="G225" t="n">
-        <v>0.778</v>
+        <v>0.714</v>
       </c>
       <c r="H225" t="n">
-        <v>0.429</v>
+        <v>0.408</v>
       </c>
       <c r="I225" t="n">
         <v>1</v>
@@ -11072,13 +11072,13 @@
         <v>9</v>
       </c>
       <c r="F234" t="n">
-        <v>0.8</v>
+        <v>0.767</v>
       </c>
       <c r="G234" t="n">
-        <v>0.733</v>
+        <v>0.7</v>
       </c>
       <c r="H234" t="n">
-        <v>0.761</v>
+        <v>0.771</v>
       </c>
       <c r="I234" t="n">
         <v>1</v>
@@ -11109,10 +11109,10 @@
         <v>10</v>
       </c>
       <c r="F235" t="n">
-        <v>0.783</v>
+        <v>0.696</v>
       </c>
       <c r="G235" t="n">
-        <v>0.826</v>
+        <v>0.739</v>
       </c>
       <c r="H235" t="n">
         <v>1</v>
@@ -11146,13 +11146,13 @@
         <v>11</v>
       </c>
       <c r="F236" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="G236" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="H236" t="n">
-        <v>0.321</v>
+        <v>0.345</v>
       </c>
       <c r="I236" t="n">
         <v>1</v>
@@ -11294,16 +11294,16 @@
         <v>15</v>
       </c>
       <c r="F240" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G240" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="H240" t="n">
-        <v>0.0648</v>
+        <v>0.0187</v>
       </c>
       <c r="I240" t="n">
-        <v>0.519</v>
+        <v>0.299</v>
       </c>
     </row>
     <row r="241">
@@ -11331,16 +11331,16 @@
         <v>16</v>
       </c>
       <c r="F241" t="n">
-        <v>0.824</v>
+        <v>0.588</v>
       </c>
       <c r="G241" t="n">
-        <v>0.412</v>
+        <v>0.294</v>
       </c>
       <c r="H241" t="n">
-        <v>0.0324</v>
+        <v>0.166</v>
       </c>
       <c r="I241" t="n">
-        <v>0.518</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242">
@@ -11664,13 +11664,13 @@
         <v>9</v>
       </c>
       <c r="F250" t="n">
-        <v>0.889</v>
+        <v>0.868</v>
       </c>
       <c r="G250" t="n">
-        <v>0.846</v>
+        <v>0.824</v>
       </c>
       <c r="H250" t="n">
-        <v>0.575</v>
+        <v>0.594</v>
       </c>
       <c r="I250" t="n">
         <v>1</v>
@@ -11701,13 +11701,13 @@
         <v>10</v>
       </c>
       <c r="F251" t="n">
-        <v>0.878</v>
+        <v>0.821</v>
       </c>
       <c r="G251" t="n">
-        <v>0.905</v>
+        <v>0.85</v>
       </c>
       <c r="H251" t="n">
-        <v>0.738</v>
+        <v>0.77</v>
       </c>
       <c r="I251" t="n">
         <v>1</v>
@@ -11738,13 +11738,13 @@
         <v>11</v>
       </c>
       <c r="F252" t="n">
-        <v>0.773</v>
+        <v>0.744</v>
       </c>
       <c r="G252" t="n">
-        <v>0.875</v>
+        <v>0.851</v>
       </c>
       <c r="H252" t="n">
-        <v>0.272</v>
+        <v>0.292</v>
       </c>
       <c r="I252" t="n">
         <v>1</v>
@@ -11886,13 +11886,13 @@
         <v>15</v>
       </c>
       <c r="F256" t="n">
-        <v>0.783</v>
+        <v>0.756</v>
       </c>
       <c r="G256" t="n">
-        <v>0.75</v>
+        <v>0.621</v>
       </c>
       <c r="H256" t="n">
-        <v>0.789</v>
+        <v>0.298</v>
       </c>
       <c r="I256" t="n">
         <v>1</v>
@@ -11923,13 +11923,13 @@
         <v>16</v>
       </c>
       <c r="F257" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.541</v>
       </c>
       <c r="G257" t="n">
-        <v>0.538</v>
+        <v>0.417</v>
       </c>
       <c r="H257" t="n">
-        <v>0.302</v>
+        <v>0.434</v>
       </c>
       <c r="I257" t="n">
         <v>1</v>
@@ -12256,13 +12256,13 @@
         <v>9</v>
       </c>
       <c r="F266" t="n">
-        <v>0.6</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G266" t="n">
-        <v>0.367</v>
+        <v>0.333</v>
       </c>
       <c r="H266" t="n">
-        <v>0.12</v>
+        <v>0.119</v>
       </c>
       <c r="I266" t="n">
         <v>0.922</v>
@@ -12330,13 +12330,13 @@
         <v>11</v>
       </c>
       <c r="F268" t="n">
-        <v>0.5</v>
+        <v>0.467</v>
       </c>
       <c r="G268" t="n">
-        <v>0.4</v>
+        <v>0.367</v>
       </c>
       <c r="H268" t="n">
-        <v>0.604</v>
+        <v>0.601</v>
       </c>
       <c r="I268" t="n">
         <v>1</v>
@@ -12515,13 +12515,13 @@
         <v>16</v>
       </c>
       <c r="F273" t="n">
-        <v>0.6</v>
+        <v>0.333</v>
       </c>
       <c r="G273" t="n">
-        <v>0.733</v>
+        <v>0.467</v>
       </c>
       <c r="H273" t="n">
-        <v>0.412</v>
+        <v>0.43</v>
       </c>
       <c r="I273" t="n">
         <v>1</v>
@@ -12922,10 +12922,10 @@
         <v>11</v>
       </c>
       <c r="F284" t="n">
-        <v>0.857</v>
+        <v>0.846</v>
       </c>
       <c r="G284" t="n">
-        <v>0.889</v>
+        <v>0.875</v>
       </c>
       <c r="H284" t="n">
         <v>1</v>
@@ -13107,13 +13107,13 @@
         <v>16</v>
       </c>
       <c r="F289" t="n">
-        <v>0.619</v>
+        <v>0.385</v>
       </c>
       <c r="G289" t="n">
-        <v>0.737</v>
+        <v>0.545</v>
       </c>
       <c r="H289" t="n">
-        <v>0.511</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="I289" t="n">
         <v>1</v>
@@ -13440,13 +13440,13 @@
         <v>9</v>
       </c>
       <c r="F298" t="n">
-        <v>0.6</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G298" t="n">
-        <v>0.367</v>
+        <v>0.333</v>
       </c>
       <c r="H298" t="n">
-        <v>0.12</v>
+        <v>0.119</v>
       </c>
       <c r="I298" t="n">
         <v>0.6870000000000001</v>
@@ -13514,13 +13514,13 @@
         <v>11</v>
       </c>
       <c r="F300" t="n">
-        <v>0.48</v>
+        <v>0.44</v>
       </c>
       <c r="G300" t="n">
-        <v>0.32</v>
+        <v>0.28</v>
       </c>
       <c r="H300" t="n">
-        <v>0.387</v>
+        <v>0.377</v>
       </c>
       <c r="I300" t="n">
         <v>1</v>
@@ -13699,10 +13699,10 @@
         <v>16</v>
       </c>
       <c r="F305" t="n">
-        <v>0.765</v>
+        <v>0.294</v>
       </c>
       <c r="G305" t="n">
-        <v>0.824</v>
+        <v>0.353</v>
       </c>
       <c r="H305" t="n">
         <v>1</v>
@@ -14032,13 +14032,13 @@
         <v>9</v>
       </c>
       <c r="F314" t="n">
-        <v>0.75</v>
+        <v>0.723</v>
       </c>
       <c r="G314" t="n">
-        <v>0.537</v>
+        <v>0.5</v>
       </c>
       <c r="H314" t="n">
-        <v>0.0455</v>
+        <v>0.0459</v>
       </c>
       <c r="I314" t="n">
         <v>0.33</v>
@@ -14106,16 +14106,16 @@
         <v>11</v>
       </c>
       <c r="F316" t="n">
-        <v>0.615</v>
+        <v>0.579</v>
       </c>
       <c r="G316" t="n">
-        <v>0.471</v>
+        <v>0.424</v>
       </c>
       <c r="H316" t="n">
-        <v>0.245</v>
+        <v>0.238</v>
       </c>
       <c r="I316" t="n">
-        <v>0.654</v>
+        <v>0.634</v>
       </c>
     </row>
     <row r="317">
@@ -14291,13 +14291,13 @@
         <v>16</v>
       </c>
       <c r="F321" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.333</v>
       </c>
       <c r="G321" t="n">
-        <v>0.778</v>
+        <v>0.429</v>
       </c>
       <c r="H321" t="n">
-        <v>0.437</v>
+        <v>0.589</v>
       </c>
       <c r="I321" t="n">
         <v>0.919</v>
@@ -14624,7 +14624,7 @@
         <v>9</v>
       </c>
       <c r="F330" t="n">
-        <v>0.6</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G330" t="n">
         <v>0.6</v>
@@ -14664,13 +14664,13 @@
         <v>0.6</v>
       </c>
       <c r="G331" t="n">
-        <v>0.733</v>
+        <v>0.7</v>
       </c>
       <c r="H331" t="n">
-        <v>0.412</v>
+        <v>0.589</v>
       </c>
       <c r="I331" t="n">
-        <v>0.876</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
@@ -14698,10 +14698,10 @@
         <v>11</v>
       </c>
       <c r="F332" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="G332" t="n">
         <v>0.5</v>
-      </c>
-      <c r="G332" t="n">
-        <v>0.533</v>
       </c>
       <c r="H332" t="n">
         <v>1</v>
@@ -14849,10 +14849,10 @@
         <v>0.633</v>
       </c>
       <c r="G336" t="n">
-        <v>0.733</v>
+        <v>0.633</v>
       </c>
       <c r="H336" t="n">
-        <v>0.58</v>
+        <v>1</v>
       </c>
       <c r="I336" t="n">
         <v>1</v>
@@ -14883,16 +14883,16 @@
         <v>16</v>
       </c>
       <c r="F337" t="n">
-        <v>0.6</v>
+        <v>0.333</v>
       </c>
       <c r="G337" t="n">
-        <v>0.533</v>
+        <v>0.467</v>
       </c>
       <c r="H337" t="n">
-        <v>0.795</v>
+        <v>0.43</v>
       </c>
       <c r="I337" t="n">
-        <v>1</v>
+        <v>0.876</v>
       </c>
     </row>
     <row r="338">
@@ -15256,7 +15256,7 @@
         <v>0.923</v>
       </c>
       <c r="G347" t="n">
-        <v>0.895</v>
+        <v>0.889</v>
       </c>
       <c r="H347" t="n">
         <v>1</v>
@@ -15290,10 +15290,10 @@
         <v>11</v>
       </c>
       <c r="F348" t="n">
-        <v>0.857</v>
+        <v>0.846</v>
       </c>
       <c r="G348" t="n">
-        <v>0.789</v>
+        <v>0.778</v>
       </c>
       <c r="H348" t="n">
         <v>1</v>
@@ -15441,10 +15441,10 @@
         <v>0.68</v>
       </c>
       <c r="G352" t="n">
-        <v>0.875</v>
+        <v>0.846</v>
       </c>
       <c r="H352" t="n">
-        <v>0.265</v>
+        <v>0.441</v>
       </c>
       <c r="I352" t="n">
         <v>1</v>
@@ -15475,13 +15475,13 @@
         <v>16</v>
       </c>
       <c r="F353" t="n">
-        <v>0.619</v>
+        <v>0.385</v>
       </c>
       <c r="G353" t="n">
-        <v>0.636</v>
+        <v>0.556</v>
       </c>
       <c r="H353" t="n">
-        <v>1</v>
+        <v>0.666</v>
       </c>
       <c r="I353" t="n">
         <v>1</v>
@@ -15808,7 +15808,7 @@
         <v>9</v>
       </c>
       <c r="F362" t="n">
-        <v>0.6</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G362" t="n">
         <v>0.6</v>
@@ -15848,13 +15848,13 @@
         <v>0.522</v>
       </c>
       <c r="G363" t="n">
-        <v>0.739</v>
+        <v>0.696</v>
       </c>
       <c r="H363" t="n">
-        <v>0.221</v>
+        <v>0.365</v>
       </c>
       <c r="I363" t="n">
-        <v>0.506</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="364">
@@ -15882,16 +15882,16 @@
         <v>11</v>
       </c>
       <c r="F364" t="n">
-        <v>0.48</v>
+        <v>0.44</v>
       </c>
       <c r="G364" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H364" t="n">
-        <v>0.571</v>
+        <v>0.572</v>
       </c>
       <c r="I364" t="n">
-        <v>0.913</v>
+        <v>1</v>
       </c>
     </row>
     <row r="365">
@@ -16033,13 +16033,13 @@
         <v>0.85</v>
       </c>
       <c r="G368" t="n">
-        <v>0.7</v>
+        <v>0.55</v>
       </c>
       <c r="H368" t="n">
-        <v>0.451</v>
+        <v>0.0824</v>
       </c>
       <c r="I368" t="n">
-        <v>0.801</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="369">
@@ -16067,16 +16067,16 @@
         <v>16</v>
       </c>
       <c r="F369" t="n">
-        <v>0.765</v>
+        <v>0.294</v>
       </c>
       <c r="G369" t="n">
-        <v>0.412</v>
+        <v>0.294</v>
       </c>
       <c r="H369" t="n">
-        <v>0.0799</v>
+        <v>1</v>
       </c>
       <c r="I369" t="n">
-        <v>0.213</v>
+        <v>1</v>
       </c>
     </row>
     <row r="370">
@@ -16261,7 +16261,7 @@
         <v>0.245</v>
       </c>
       <c r="I374" t="n">
-        <v>0.49</v>
+        <v>0.653</v>
       </c>
     </row>
     <row r="375">
@@ -16400,13 +16400,13 @@
         <v>9</v>
       </c>
       <c r="F378" t="n">
-        <v>0.75</v>
+        <v>0.723</v>
       </c>
       <c r="G378" t="n">
         <v>0.75</v>
       </c>
       <c r="H378" t="n">
-        <v>1</v>
+        <v>0.819</v>
       </c>
       <c r="I378" t="n">
         <v>1</v>
@@ -16440,13 +16440,13 @@
         <v>0.667</v>
       </c>
       <c r="G379" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="H379" t="n">
-        <v>0.196</v>
+        <v>0.311</v>
       </c>
       <c r="I379" t="n">
-        <v>0.462</v>
+        <v>0.711</v>
       </c>
     </row>
     <row r="380">
@@ -16474,13 +16474,13 @@
         <v>11</v>
       </c>
       <c r="F380" t="n">
-        <v>0.615</v>
+        <v>0.579</v>
       </c>
       <c r="G380" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.651</v>
       </c>
       <c r="H380" t="n">
-        <v>0.645</v>
+        <v>0.647</v>
       </c>
       <c r="I380" t="n">
         <v>1</v>
@@ -16625,13 +16625,13 @@
         <v>0.756</v>
       </c>
       <c r="G384" t="n">
-        <v>0.778</v>
+        <v>0.667</v>
       </c>
       <c r="H384" t="n">
-        <v>1</v>
+        <v>0.45</v>
       </c>
       <c r="I384" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="385">
@@ -16659,16 +16659,16 @@
         <v>16</v>
       </c>
       <c r="F385" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.333</v>
       </c>
       <c r="G385" t="n">
-        <v>0.5</v>
+        <v>0.385</v>
       </c>
       <c r="H385" t="n">
-        <v>0.202</v>
+        <v>0.783</v>
       </c>
       <c r="I385" t="n">
-        <v>0.462</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -16735,45 +16735,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Llama3.1-70B</t>
+          <t>GPT-4o</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>69.2</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>100.0*†</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>5.9</t>
         </is>
       </c>
     </row>

--- a/eval/results/statistical_tests_new30.xlsx
+++ b/eval/results/statistical_tests_new30.xlsx
@@ -519,7 +519,7 @@
         <v>0.146</v>
       </c>
       <c r="J2" t="n">
-        <v>0.189</v>
+        <v>0.236</v>
       </c>
     </row>
     <row r="3">
@@ -559,7 +559,7 @@
         <v>0.146</v>
       </c>
       <c r="J3" t="n">
-        <v>0.14</v>
+        <v>0.164</v>
       </c>
     </row>
     <row r="4">
@@ -599,7 +599,7 @@
         <v>0.101</v>
       </c>
       <c r="J4" t="n">
-        <v>0.105</v>
+        <v>0.158</v>
       </c>
     </row>
     <row r="5">
@@ -639,7 +639,7 @@
         <v>0.101</v>
       </c>
       <c r="J5" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.145</v>
       </c>
     </row>
     <row r="6">
@@ -759,7 +759,7 @@
         <v>0.124</v>
       </c>
       <c r="J8" t="n">
-        <v>0.189</v>
+        <v>0.236</v>
       </c>
     </row>
     <row r="9">
@@ -799,7 +799,7 @@
         <v>0.124</v>
       </c>
       <c r="J9" t="n">
-        <v>0.14</v>
+        <v>0.164</v>
       </c>
     </row>
     <row r="10">
@@ -839,7 +839,7 @@
         <v>0.115</v>
       </c>
       <c r="J10" t="n">
-        <v>0.228</v>
+        <v>0.266</v>
       </c>
     </row>
     <row r="11">
@@ -879,7 +879,7 @@
         <v>0.115</v>
       </c>
       <c r="J11" t="n">
-        <v>0.14</v>
+        <v>0.164</v>
       </c>
     </row>
     <row r="12">
@@ -919,7 +919,7 @@
         <v>0.115</v>
       </c>
       <c r="J12" t="n">
-        <v>0.228</v>
+        <v>0.266</v>
       </c>
     </row>
     <row r="13">
@@ -959,7 +959,7 @@
         <v>0.115</v>
       </c>
       <c r="J13" t="n">
-        <v>0.14</v>
+        <v>0.164</v>
       </c>
     </row>
     <row r="14">
@@ -1064,22 +1064,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>8.410000000000001e-06</v>
+        <v>0.225</v>
       </c>
       <c r="F16" t="n">
         <v>0.6879999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>0.388</v>
+        <v>0.654</v>
       </c>
       <c r="H16" t="n">
         <v>0.177</v>
       </c>
       <c r="I16" t="n">
-        <v>0.223</v>
+        <v>0.136</v>
       </c>
       <c r="J16" t="n">
-        <v>7.57e-05</v>
+        <v>0.289</v>
       </c>
     </row>
     <row r="17">
@@ -1104,22 +1104,22 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.000436</v>
+        <v>0.306</v>
       </c>
       <c r="F17" t="n">
         <v>0.6879999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>0.388</v>
+        <v>0.654</v>
       </c>
       <c r="H17" t="n">
         <v>0.177</v>
       </c>
       <c r="I17" t="n">
-        <v>0.223</v>
+        <v>0.136</v>
       </c>
       <c r="J17" t="n">
-        <v>0.00392</v>
+        <v>0.393</v>
       </c>
     </row>
     <row r="18">
@@ -1159,7 +1159,7 @@
         <v>0.15</v>
       </c>
       <c r="J18" t="n">
-        <v>0.105</v>
+        <v>0.158</v>
       </c>
     </row>
     <row r="19">
@@ -1199,7 +1199,7 @@
         <v>0.15</v>
       </c>
       <c r="J19" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.145</v>
       </c>
     </row>
     <row r="20">
@@ -1239,7 +1239,7 @@
         <v>0.115</v>
       </c>
       <c r="J20" t="n">
-        <v>0.124</v>
+        <v>0.165</v>
       </c>
     </row>
     <row r="21">
@@ -1279,7 +1279,7 @@
         <v>0.115</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0511</v>
+        <v>0.0639</v>
       </c>
     </row>
     <row r="22">
@@ -1319,7 +1319,7 @@
         <v>0.127</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0536</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="23">
@@ -1359,7 +1359,7 @@
         <v>0.127</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0286</v>
+        <v>0.0527</v>
       </c>
     </row>
     <row r="24">
@@ -1399,7 +1399,7 @@
         <v>0.192</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0762</v>
+        <v>0.114</v>
       </c>
     </row>
     <row r="25">
@@ -1439,7 +1439,7 @@
         <v>0.192</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0511</v>
+        <v>0.0639</v>
       </c>
     </row>
     <row r="26">
@@ -1519,7 +1519,7 @@
         <v>0.178</v>
       </c>
       <c r="J27" t="n">
-        <v>0.107</v>
+        <v>0.128</v>
       </c>
     </row>
     <row r="28">
@@ -1599,7 +1599,7 @@
         <v>0.179</v>
       </c>
       <c r="J29" t="n">
-        <v>0.124</v>
+        <v>0.141</v>
       </c>
     </row>
     <row r="30">
@@ -1679,7 +1679,7 @@
         <v>0.179</v>
       </c>
       <c r="J31" t="n">
-        <v>0.124</v>
+        <v>0.141</v>
       </c>
     </row>
     <row r="32">
@@ -1719,7 +1719,7 @@
         <v>0.174</v>
       </c>
       <c r="J32" t="n">
-        <v>0.398</v>
+        <v>0.455</v>
       </c>
     </row>
     <row r="33">
@@ -1759,7 +1759,7 @@
         <v>0.174</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0511</v>
+        <v>0.0639</v>
       </c>
     </row>
     <row r="34">
@@ -1784,22 +1784,22 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.00284</v>
+        <v>0.389</v>
       </c>
       <c r="F34" t="n">
         <v>0.8110000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>0.435</v>
+        <v>0.772</v>
       </c>
       <c r="H34" t="n">
         <v>0.158</v>
       </c>
       <c r="I34" t="n">
-        <v>0.414</v>
+        <v>0.204</v>
       </c>
       <c r="J34" t="n">
-        <v>0.0256</v>
+        <v>0.455</v>
       </c>
     </row>
     <row r="35">
@@ -1824,22 +1824,22 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.00636</v>
+        <v>0.331</v>
       </c>
       <c r="F35" t="n">
         <v>0.8110000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>0.435</v>
+        <v>0.772</v>
       </c>
       <c r="H35" t="n">
         <v>0.158</v>
       </c>
       <c r="I35" t="n">
-        <v>0.414</v>
+        <v>0.204</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0286</v>
+        <v>0.372</v>
       </c>
     </row>
     <row r="36">
@@ -2119,7 +2119,7 @@
         <v>0.264</v>
       </c>
       <c r="J42" t="n">
-        <v>0.274</v>
+        <v>0.342</v>
       </c>
     </row>
     <row r="43">
@@ -2159,7 +2159,7 @@
         <v>0.264</v>
       </c>
       <c r="J43" t="n">
-        <v>0.245</v>
+        <v>0.306</v>
       </c>
     </row>
     <row r="44">
@@ -2199,7 +2199,7 @@
         <v>0.227</v>
       </c>
       <c r="J44" t="n">
-        <v>0.0208</v>
+        <v>0.0312</v>
       </c>
     </row>
     <row r="45">
@@ -2239,7 +2239,7 @@
         <v>0.227</v>
       </c>
       <c r="J45" t="n">
-        <v>0.009990000000000001</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="46">
@@ -2439,7 +2439,7 @@
         <v>0.171</v>
       </c>
       <c r="J50" t="n">
-        <v>0.0299</v>
+        <v>0.0399</v>
       </c>
     </row>
     <row r="51">
@@ -2479,7 +2479,7 @@
         <v>0.171</v>
       </c>
       <c r="J51" t="n">
-        <v>0.0682</v>
+        <v>0.09089999999999999</v>
       </c>
     </row>
     <row r="52">
@@ -2504,22 +2504,22 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.000122</v>
+        <v>0.509</v>
       </c>
       <c r="F52" t="n">
         <v>0.64</v>
       </c>
       <c r="G52" t="n">
-        <v>0.236</v>
+        <v>0.613</v>
       </c>
       <c r="H52" t="n">
         <v>0.222</v>
       </c>
       <c r="I52" t="n">
-        <v>0.332</v>
+        <v>0.213</v>
       </c>
       <c r="J52" t="n">
-        <v>0.0011</v>
+        <v>0.8159999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -2544,22 +2544,22 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.0016</v>
+        <v>0.382</v>
       </c>
       <c r="F53" t="n">
         <v>0.64</v>
       </c>
       <c r="G53" t="n">
-        <v>0.236</v>
+        <v>0.613</v>
       </c>
       <c r="H53" t="n">
         <v>0.222</v>
       </c>
       <c r="I53" t="n">
-        <v>0.332</v>
+        <v>0.213</v>
       </c>
       <c r="J53" t="n">
-        <v>0.009990000000000001</v>
+        <v>0.6879999999999999</v>
       </c>
     </row>
     <row r="54">
@@ -2599,7 +2599,7 @@
         <v>0.217</v>
       </c>
       <c r="J54" t="n">
-        <v>0.0208</v>
+        <v>0.0312</v>
       </c>
     </row>
     <row r="55">
@@ -2639,7 +2639,7 @@
         <v>0.217</v>
       </c>
       <c r="J55" t="n">
-        <v>0.0393</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="56">
@@ -2919,7 +2919,7 @@
         <v>0.191</v>
       </c>
       <c r="J62" t="n">
-        <v>0.109</v>
+        <v>0.145</v>
       </c>
     </row>
     <row r="63">
@@ -2959,7 +2959,7 @@
         <v>0.191</v>
       </c>
       <c r="J63" t="n">
-        <v>0.106</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="64">
@@ -3159,7 +3159,7 @@
         <v>0.142</v>
       </c>
       <c r="J68" t="n">
-        <v>0.109</v>
+        <v>0.145</v>
       </c>
     </row>
     <row r="69">
@@ -3199,7 +3199,7 @@
         <v>0.142</v>
       </c>
       <c r="J69" t="n">
-        <v>0.147</v>
+        <v>0.196</v>
       </c>
     </row>
     <row r="70">
@@ -3224,22 +3224,22 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2.11e-07</v>
+        <v>0.0771</v>
       </c>
       <c r="F70" t="n">
         <v>0.6840000000000001</v>
       </c>
       <c r="G70" t="n">
-        <v>0.199</v>
+        <v>0.628</v>
       </c>
       <c r="H70" t="n">
         <v>0.135</v>
       </c>
       <c r="I70" t="n">
-        <v>0.22</v>
+        <v>0.126</v>
       </c>
       <c r="J70" t="n">
-        <v>1.9e-06</v>
+        <v>0.173</v>
       </c>
     </row>
     <row r="71">
@@ -3264,22 +3264,22 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3.05e-05</v>
+        <v>0.109</v>
       </c>
       <c r="F71" t="n">
         <v>0.6840000000000001</v>
       </c>
       <c r="G71" t="n">
-        <v>0.199</v>
+        <v>0.628</v>
       </c>
       <c r="H71" t="n">
         <v>0.135</v>
       </c>
       <c r="I71" t="n">
-        <v>0.22</v>
+        <v>0.126</v>
       </c>
       <c r="J71" t="n">
-        <v>0.000275</v>
+        <v>0.223</v>
       </c>
     </row>
     <row r="72">
@@ -3319,7 +3319,7 @@
         <v>0.168</v>
       </c>
       <c r="J72" t="n">
-        <v>0.109</v>
+        <v>0.145</v>
       </c>
     </row>
     <row r="73">
@@ -3359,7 +3359,7 @@
         <v>0.168</v>
       </c>
       <c r="J73" t="n">
-        <v>0.106</v>
+        <v>0.16</v>
       </c>
     </row>
   </sheetData>
@@ -20027,7 +20027,7 @@
         <v>0.7</v>
       </c>
       <c r="G450" t="n">
-        <v>0.667</v>
+        <v>0.7</v>
       </c>
       <c r="H450" t="n">
         <v>1</v>
@@ -20064,13 +20064,13 @@
         <v>0.9</v>
       </c>
       <c r="G451" t="n">
-        <v>0.233</v>
+        <v>0.667</v>
       </c>
       <c r="H451" t="n">
-        <v>2.44e-07</v>
+        <v>0.0575</v>
       </c>
       <c r="I451" t="n">
-        <v>3.9e-06</v>
+        <v>0.306</v>
       </c>
     </row>
     <row r="452">
@@ -20101,13 +20101,13 @@
         <v>0.9</v>
       </c>
       <c r="G452" t="n">
-        <v>0.433</v>
+        <v>0.667</v>
       </c>
       <c r="H452" t="n">
-        <v>0.000251</v>
+        <v>0.0575</v>
       </c>
       <c r="I452" t="n">
-        <v>0.000802</v>
+        <v>0.306</v>
       </c>
     </row>
     <row r="453">
@@ -20138,13 +20138,13 @@
         <v>1</v>
       </c>
       <c r="G453" t="n">
-        <v>0.633</v>
+        <v>0.833</v>
       </c>
       <c r="H453" t="n">
-        <v>0.000319</v>
+        <v>0.0522</v>
       </c>
       <c r="I453" t="n">
-        <v>0.00085</v>
+        <v>0.306</v>
       </c>
     </row>
     <row r="454">
@@ -20175,13 +20175,13 @@
         <v>0.467</v>
       </c>
       <c r="G454" t="n">
-        <v>0.267</v>
+        <v>0.533</v>
       </c>
       <c r="H454" t="n">
-        <v>0.18</v>
+        <v>0.797</v>
       </c>
       <c r="I454" t="n">
-        <v>0.26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="455">
@@ -20212,13 +20212,13 @@
         <v>0.6</v>
       </c>
       <c r="G455" t="n">
-        <v>0.1</v>
+        <v>0.633</v>
       </c>
       <c r="H455" t="n">
-        <v>9.41e-05</v>
+        <v>1</v>
       </c>
       <c r="I455" t="n">
-        <v>0.000502</v>
+        <v>1</v>
       </c>
     </row>
     <row r="456">
@@ -20249,13 +20249,13 @@
         <v>0.6</v>
       </c>
       <c r="G456" t="n">
-        <v>0.333</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H456" t="n">
-        <v>0.0692</v>
+        <v>1</v>
       </c>
       <c r="I456" t="n">
-        <v>0.123</v>
+        <v>1</v>
       </c>
     </row>
     <row r="457">
@@ -20286,13 +20286,13 @@
         <v>0.867</v>
       </c>
       <c r="G457" t="n">
-        <v>0.8</v>
+        <v>0.867</v>
       </c>
       <c r="H457" t="n">
-        <v>0.731</v>
+        <v>1</v>
       </c>
       <c r="I457" t="n">
-        <v>0.779</v>
+        <v>1</v>
       </c>
     </row>
     <row r="458">
@@ -20323,13 +20323,13 @@
         <v>0.5669999999999999</v>
       </c>
       <c r="G458" t="n">
-        <v>0.1</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H458" t="n">
-        <v>0.000251</v>
+        <v>1</v>
       </c>
       <c r="I458" t="n">
-        <v>0.000802</v>
+        <v>1</v>
       </c>
     </row>
     <row r="459">
@@ -20360,13 +20360,13 @@
         <v>0.6</v>
       </c>
       <c r="G459" t="n">
-        <v>0.1</v>
+        <v>0.467</v>
       </c>
       <c r="H459" t="n">
-        <v>9.41e-05</v>
+        <v>0.438</v>
       </c>
       <c r="I459" t="n">
-        <v>0.000502</v>
+        <v>1</v>
       </c>
     </row>
     <row r="460">
@@ -20397,13 +20397,13 @@
         <v>0.467</v>
       </c>
       <c r="G460" t="n">
-        <v>0.233</v>
+        <v>0.433</v>
       </c>
       <c r="H460" t="n">
-        <v>0.103</v>
+        <v>1</v>
       </c>
       <c r="I460" t="n">
-        <v>0.165</v>
+        <v>1</v>
       </c>
     </row>
     <row r="461">
@@ -20434,13 +20434,13 @@
         <v>0.633</v>
       </c>
       <c r="G461" t="n">
-        <v>0.433</v>
+        <v>0.7</v>
       </c>
       <c r="H461" t="n">
-        <v>0.195</v>
+        <v>0.785</v>
       </c>
       <c r="I461" t="n">
-        <v>0.26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="462">
@@ -20471,13 +20471,13 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="G462" t="n">
-        <v>0.667</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="H462" t="n">
-        <v>0.0211</v>
+        <v>1</v>
       </c>
       <c r="I462" t="n">
-        <v>0.0423</v>
+        <v>1</v>
       </c>
     </row>
     <row r="463">
@@ -20508,13 +20508,13 @@
         <v>0.667</v>
       </c>
       <c r="G463" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.667</v>
       </c>
       <c r="H463" t="n">
-        <v>0.596</v>
+        <v>1</v>
       </c>
       <c r="I463" t="n">
-        <v>0.681</v>
+        <v>1</v>
       </c>
     </row>
     <row r="464">
@@ -20545,13 +20545,13 @@
         <v>0.633</v>
       </c>
       <c r="G464" t="n">
-        <v>0.3</v>
+        <v>0.633</v>
       </c>
       <c r="H464" t="n">
-        <v>0.0191</v>
+        <v>1</v>
       </c>
       <c r="I464" t="n">
-        <v>0.0423</v>
+        <v>1</v>
       </c>
     </row>
     <row r="465">
@@ -20582,13 +20582,13 @@
         <v>0.467</v>
       </c>
       <c r="G465" t="n">
-        <v>0.333</v>
+        <v>0.6</v>
       </c>
       <c r="H465" t="n">
-        <v>0.43</v>
+        <v>0.438</v>
       </c>
       <c r="I465" t="n">
-        <v>0.529</v>
+        <v>1</v>
       </c>
     </row>
     <row r="466">
@@ -20619,10 +20619,10 @@
         <v>0.826</v>
       </c>
       <c r="G466" t="n">
-        <v>0.769</v>
+        <v>0.778</v>
       </c>
       <c r="H466" t="n">
-        <v>0.731</v>
+        <v>0.736</v>
       </c>
       <c r="I466" t="n">
         <v>1</v>
@@ -20656,13 +20656,13 @@
         <v>0.5</v>
       </c>
       <c r="G467" t="n">
-        <v>0.115</v>
+        <v>0.231</v>
       </c>
       <c r="H467" t="n">
-        <v>0.119</v>
+        <v>0.538</v>
       </c>
       <c r="I467" t="n">
-        <v>0.38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="468">
@@ -20693,13 +20693,13 @@
         <v>0.7</v>
       </c>
       <c r="G468" t="n">
-        <v>0.0833</v>
+        <v>0.4</v>
       </c>
       <c r="H468" t="n">
-        <v>0.00619</v>
+        <v>0.226</v>
       </c>
       <c r="I468" t="n">
-        <v>0.0248</v>
+        <v>1</v>
       </c>
     </row>
     <row r="469">
@@ -20730,13 +20730,13 @@
         <v>1</v>
       </c>
       <c r="G469" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="H469" t="n">
-        <v>0.00303</v>
+        <v>0.103</v>
       </c>
       <c r="I469" t="n">
-        <v>0.0162</v>
+        <v>1</v>
       </c>
     </row>
     <row r="470">
@@ -20767,7 +20767,7 @@
         <v>0.786</v>
       </c>
       <c r="G470" t="n">
-        <v>0.75</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="H470" t="n">
         <v>1</v>
@@ -20804,13 +20804,13 @@
         <v>1</v>
       </c>
       <c r="G471" t="n">
-        <v>0</v>
+        <v>0.917</v>
       </c>
       <c r="H471" t="n">
-        <v>0.0002</v>
+        <v>1</v>
       </c>
       <c r="I471" t="n">
-        <v>0.0032</v>
+        <v>1</v>
       </c>
     </row>
     <row r="472">
@@ -20841,13 +20841,13 @@
         <v>0.8179999999999999</v>
       </c>
       <c r="G472" t="n">
-        <v>0.333</v>
+        <v>0.75</v>
       </c>
       <c r="H472" t="n">
-        <v>0.176</v>
+        <v>1</v>
       </c>
       <c r="I472" t="n">
-        <v>0.402</v>
+        <v>1</v>
       </c>
     </row>
     <row r="473">
@@ -20877,7 +20877,9 @@
       <c r="F473" t="n">
         <v>1</v>
       </c>
-      <c r="G473" t="inlineStr"/>
+      <c r="G473" t="n">
+        <v>1</v>
+      </c>
       <c r="H473" t="n">
         <v>1</v>
       </c>
@@ -20950,13 +20952,13 @@
         <v>0.923</v>
       </c>
       <c r="G475" t="n">
-        <v>0.167</v>
+        <v>0.889</v>
       </c>
       <c r="H475" t="n">
-        <v>0.00291</v>
+        <v>1</v>
       </c>
       <c r="I475" t="n">
-        <v>0.0162</v>
+        <v>1</v>
       </c>
     </row>
     <row r="476">
@@ -20987,7 +20989,7 @@
         <v>0.846</v>
       </c>
       <c r="G476" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="H476" t="n">
         <v>1</v>
@@ -21024,7 +21026,7 @@
         <v>0.833</v>
       </c>
       <c r="G477" t="n">
-        <v>1</v>
+        <v>0.857</v>
       </c>
       <c r="H477" t="n">
         <v>1</v>
@@ -21061,13 +21063,13 @@
         <v>0.714</v>
       </c>
       <c r="G478" t="n">
-        <v>0.308</v>
+        <v>0.8</v>
       </c>
       <c r="H478" t="n">
-        <v>0.16</v>
+        <v>1</v>
       </c>
       <c r="I478" t="n">
-        <v>0.402</v>
+        <v>1</v>
       </c>
     </row>
     <row r="479">
@@ -21098,13 +21100,13 @@
         <v>0.8120000000000001</v>
       </c>
       <c r="G479" t="n">
-        <v>1</v>
+        <v>0.778</v>
       </c>
       <c r="H479" t="n">
-        <v>0.526</v>
+        <v>1</v>
       </c>
       <c r="I479" t="n">
-        <v>0.841</v>
+        <v>1</v>
       </c>
     </row>
     <row r="480">
@@ -21135,13 +21137,13 @@
         <v>0.68</v>
       </c>
       <c r="G480" t="n">
-        <v>0.429</v>
+        <v>0.846</v>
       </c>
       <c r="H480" t="n">
-        <v>0.379</v>
+        <v>0.441</v>
       </c>
       <c r="I480" t="n">
-        <v>0.674</v>
+        <v>1</v>
       </c>
     </row>
     <row r="481">
@@ -21172,13 +21174,13 @@
         <v>0.529</v>
       </c>
       <c r="G481" t="n">
-        <v>0</v>
+        <v>0.857</v>
       </c>
       <c r="H481" t="n">
-        <v>0.218</v>
+        <v>0.191</v>
       </c>
       <c r="I481" t="n">
-        <v>0.437</v>
+        <v>1</v>
       </c>
     </row>
     <row r="482">
@@ -21209,10 +21211,10 @@
         <v>0.792</v>
       </c>
       <c r="G482" t="n">
-        <v>0.833</v>
+        <v>0.875</v>
       </c>
       <c r="H482" t="n">
-        <v>1</v>
+        <v>0.701</v>
       </c>
       <c r="I482" t="n">
         <v>1</v>
@@ -21283,13 +21285,13 @@
         <v>1</v>
       </c>
       <c r="G484" t="n">
-        <v>0.143</v>
+        <v>0.857</v>
       </c>
       <c r="H484" t="n">
-        <v>0.00466</v>
+        <v>1</v>
       </c>
       <c r="I484" t="n">
-        <v>0.0107</v>
+        <v>1</v>
       </c>
     </row>
     <row r="485">
@@ -21320,13 +21322,13 @@
         <v>1</v>
       </c>
       <c r="G485" t="n">
-        <v>0</v>
+        <v>0.857</v>
       </c>
       <c r="H485" t="n">
-        <v>0.000583</v>
+        <v>1</v>
       </c>
       <c r="I485" t="n">
-        <v>0.00253</v>
+        <v>1</v>
       </c>
     </row>
     <row r="486">
@@ -21357,13 +21359,13 @@
         <v>0.458</v>
       </c>
       <c r="G486" t="n">
-        <v>0.125</v>
+        <v>0.542</v>
       </c>
       <c r="H486" t="n">
-        <v>0.0243</v>
+        <v>0.773</v>
       </c>
       <c r="I486" t="n">
-        <v>0.0353</v>
+        <v>1</v>
       </c>
     </row>
     <row r="487">
@@ -21394,13 +21396,13 @@
         <v>0.429</v>
       </c>
       <c r="G487" t="n">
-        <v>0</v>
+        <v>0.524</v>
       </c>
       <c r="H487" t="n">
-        <v>0.00132</v>
+        <v>0.758</v>
       </c>
       <c r="I487" t="n">
-        <v>0.00352</v>
+        <v>1</v>
       </c>
     </row>
     <row r="488">
@@ -21431,13 +21433,13 @@
         <v>0.474</v>
       </c>
       <c r="G488" t="n">
-        <v>0.0526</v>
+        <v>0.474</v>
       </c>
       <c r="H488" t="n">
-        <v>0.007820000000000001</v>
+        <v>1</v>
       </c>
       <c r="I488" t="n">
-        <v>0.0148</v>
+        <v>1</v>
       </c>
     </row>
     <row r="489">
@@ -21468,13 +21470,13 @@
         <v>0.333</v>
       </c>
       <c r="G489" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="H489" t="n">
-        <v>0.455</v>
+        <v>1</v>
       </c>
       <c r="I489" t="n">
-        <v>0.5590000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="490">
@@ -21505,13 +21507,13 @@
         <v>0.5669999999999999</v>
       </c>
       <c r="G490" t="n">
-        <v>0.1</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H490" t="n">
-        <v>0.000251</v>
+        <v>1</v>
       </c>
       <c r="I490" t="n">
-        <v>0.00201</v>
+        <v>1</v>
       </c>
     </row>
     <row r="491">
@@ -21542,13 +21544,13 @@
         <v>0.522</v>
       </c>
       <c r="G491" t="n">
-        <v>0.0435</v>
+        <v>0.348</v>
       </c>
       <c r="H491" t="n">
-        <v>0.000634</v>
+        <v>0.373</v>
       </c>
       <c r="I491" t="n">
-        <v>0.00253</v>
+        <v>1</v>
       </c>
     </row>
     <row r="492">
@@ -21579,13 +21581,13 @@
         <v>0.44</v>
       </c>
       <c r="G492" t="n">
-        <v>0.08</v>
+        <v>0.4</v>
       </c>
       <c r="H492" t="n">
-        <v>0.0083</v>
+        <v>1</v>
       </c>
       <c r="I492" t="n">
-        <v>0.0148</v>
+        <v>1</v>
       </c>
     </row>
     <row r="493">
@@ -21616,13 +21618,13 @@
         <v>0.526</v>
       </c>
       <c r="G493" t="n">
-        <v>0.105</v>
+        <v>0.632</v>
       </c>
       <c r="H493" t="n">
-        <v>0.0128</v>
+        <v>0.743</v>
       </c>
       <c r="I493" t="n">
-        <v>0.0204</v>
+        <v>1</v>
       </c>
     </row>
     <row r="494">
@@ -21690,13 +21692,13 @@
         <v>0.65</v>
       </c>
       <c r="G495" t="n">
-        <v>0.35</v>
+        <v>0.7</v>
       </c>
       <c r="H495" t="n">
-        <v>0.113</v>
+        <v>1</v>
       </c>
       <c r="I495" t="n">
-        <v>0.15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="496">
@@ -21727,13 +21729,13 @@
         <v>0.85</v>
       </c>
       <c r="G496" t="n">
-        <v>0.15</v>
+        <v>0.55</v>
       </c>
       <c r="H496" t="n">
-        <v>1.94e-05</v>
+        <v>0.0824</v>
       </c>
       <c r="I496" t="n">
-        <v>0.00031</v>
+        <v>1</v>
       </c>
     </row>
     <row r="497">
@@ -21764,13 +21766,13 @@
         <v>0.529</v>
       </c>
       <c r="G497" t="n">
-        <v>0</v>
+        <v>0.353</v>
       </c>
       <c r="H497" t="n">
-        <v>0.000927</v>
+        <v>0.491</v>
       </c>
       <c r="I497" t="n">
-        <v>0.00297</v>
+        <v>1</v>
       </c>
     </row>
     <row r="498">
@@ -21801,7 +21803,7 @@
         <v>0.8090000000000001</v>
       </c>
       <c r="G498" t="n">
-        <v>0.8</v>
+        <v>0.824</v>
       </c>
       <c r="H498" t="n">
         <v>1</v>
@@ -21838,13 +21840,13 @@
         <v>0.571</v>
       </c>
       <c r="G499" t="n">
-        <v>0.207</v>
+        <v>0.375</v>
       </c>
       <c r="H499" t="n">
-        <v>0.0759</v>
+        <v>0.65</v>
       </c>
       <c r="I499" t="n">
-        <v>0.0934</v>
+        <v>1</v>
       </c>
     </row>
     <row r="500">
@@ -21875,13 +21877,13 @@
         <v>0.824</v>
       </c>
       <c r="G500" t="n">
-        <v>0.105</v>
+        <v>0.545</v>
       </c>
       <c r="H500" t="n">
-        <v>2.54e-05</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="I500" t="n">
-        <v>6.779999999999999e-05</v>
+        <v>0.746</v>
       </c>
     </row>
     <row r="501">
@@ -21912,13 +21914,13 @@
         <v>1</v>
       </c>
       <c r="G501" t="n">
-        <v>0</v>
+        <v>0.706</v>
       </c>
       <c r="H501" t="n">
-        <v>2.24e-07</v>
+        <v>0.0482</v>
       </c>
       <c r="I501" t="n">
-        <v>2.35e-06</v>
+        <v>0.746</v>
       </c>
     </row>
     <row r="502">
@@ -21949,13 +21951,13 @@
         <v>0.579</v>
       </c>
       <c r="G502" t="n">
-        <v>0.214</v>
+        <v>0.65</v>
       </c>
       <c r="H502" t="n">
-        <v>0.00516</v>
+        <v>0.642</v>
       </c>
       <c r="I502" t="n">
-        <v>0.00751</v>
+        <v>1</v>
       </c>
     </row>
     <row r="503">
@@ -21986,13 +21988,13 @@
         <v>0.6</v>
       </c>
       <c r="G503" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="H503" t="n">
-        <v>2.94e-07</v>
+        <v>0.611</v>
       </c>
       <c r="I503" t="n">
-        <v>2.35e-06</v>
+        <v>1</v>
       </c>
     </row>
     <row r="504">
@@ -22023,13 +22025,13 @@
         <v>0.6</v>
       </c>
       <c r="G504" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.581</v>
       </c>
       <c r="H504" t="n">
-        <v>0.000185</v>
+        <v>1</v>
       </c>
       <c r="I504" t="n">
-        <v>0.000371</v>
+        <v>1</v>
       </c>
     </row>
     <row r="505">
@@ -22060,13 +22062,13 @@
         <v>0.5</v>
       </c>
       <c r="G505" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H505" t="n">
-        <v>0.0849</v>
+        <v>1</v>
       </c>
       <c r="I505" t="n">
-        <v>0.097</v>
+        <v>1</v>
       </c>
     </row>
     <row r="506">
@@ -22097,13 +22099,13 @@
         <v>0.723</v>
       </c>
       <c r="G506" t="n">
-        <v>0.182</v>
+        <v>0.723</v>
       </c>
       <c r="H506" t="n">
-        <v>3.14e-06</v>
+        <v>1</v>
       </c>
       <c r="I506" t="n">
-        <v>1.26e-05</v>
+        <v>1</v>
       </c>
     </row>
     <row r="507">
@@ -22134,13 +22136,13 @@
         <v>0.667</v>
       </c>
       <c r="G507" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="H507" t="n">
-        <v>6.2e-07</v>
+        <v>0.219</v>
       </c>
       <c r="I507" t="n">
-        <v>3.3e-06</v>
+        <v>1</v>
       </c>
     </row>
     <row r="508">
@@ -22171,13 +22173,13 @@
         <v>0.579</v>
       </c>
       <c r="G508" t="n">
-        <v>0.148</v>
+        <v>0.541</v>
       </c>
       <c r="H508" t="n">
-        <v>0.000697</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="I508" t="n">
-        <v>0.00124</v>
+        <v>1</v>
       </c>
     </row>
     <row r="509">
@@ -22208,13 +22210,13 @@
         <v>0.645</v>
       </c>
       <c r="G509" t="n">
-        <v>0.19</v>
+        <v>0.727</v>
       </c>
       <c r="H509" t="n">
-        <v>0.00175</v>
+        <v>0.592</v>
       </c>
       <c r="I509" t="n">
-        <v>0.0028</v>
+        <v>1</v>
       </c>
     </row>
     <row r="510">
@@ -22245,13 +22247,13 @@
         <v>0.833</v>
       </c>
       <c r="G510" t="n">
-        <v>0.444</v>
+        <v>0.8</v>
       </c>
       <c r="H510" t="n">
-        <v>0.0577</v>
+        <v>1</v>
       </c>
       <c r="I510" t="n">
-        <v>0.077</v>
+        <v>1</v>
       </c>
     </row>
     <row r="511">
@@ -22282,13 +22284,13 @@
         <v>0.722</v>
       </c>
       <c r="G511" t="n">
-        <v>0.519</v>
+        <v>0.737</v>
       </c>
       <c r="H511" t="n">
-        <v>0.118</v>
+        <v>1</v>
       </c>
       <c r="I511" t="n">
-        <v>0.126</v>
+        <v>1</v>
       </c>
     </row>
     <row r="512">
@@ -22319,13 +22321,13 @@
         <v>0.756</v>
       </c>
       <c r="G512" t="n">
-        <v>0.222</v>
+        <v>0.667</v>
       </c>
       <c r="H512" t="n">
-        <v>1.86e-05</v>
+        <v>0.45</v>
       </c>
       <c r="I512" t="n">
-        <v>5.94e-05</v>
+        <v>1</v>
       </c>
     </row>
     <row r="513">
@@ -22356,13 +22358,13 @@
         <v>0.529</v>
       </c>
       <c r="G513" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H513" t="n">
-        <v>4.23e-05</v>
+        <v>1</v>
       </c>
       <c r="I513" t="n">
-        <v>9.66e-05</v>
+        <v>1</v>
       </c>
     </row>
     <row r="514">
@@ -24910,7 +24912,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -24925,7 +24927,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>83.3*†</t>
+          <t>87.5*†</t>
         </is>
       </c>
     </row>
@@ -24955,7 +24957,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -24970,7 +24972,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0**</t>
+          <t>52.4**</t>
         </is>
       </c>
     </row>
@@ -25000,7 +25002,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -25015,7 +25017,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.3**</t>
+          <t>47.4**</t>
         </is>
       </c>
     </row>
@@ -25045,7 +25047,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -25060,7 +25062,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10.5**</t>
+          <t>63.2**</t>
         </is>
       </c>
     </row>
@@ -25090,7 +25092,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -25105,7 +25107,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>35.0*†</t>
+          <t>70.0*†</t>
         </is>
       </c>
     </row>

--- a/eval/results/statistical_tests_new30.xlsx
+++ b/eval/results/statistical_tests_new30.xlsx
@@ -24746,7 +24746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24799,90 +24799,90 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GPT-4o</t>
+          <t>Llama3.1-8B</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>42.9</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>87.5</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>17.6</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>85.7**</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Llama3.1-70B</t>
+          <t>Llama3.1-8B</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>100.0*†</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>94.7**</t>
         </is>
       </c>
     </row>
@@ -24893,221 +24893,41 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>85.7</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>77.8</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>87.5*†</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>6</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>91.7</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>52.4**</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>7</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>81.8</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>90.9</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>47.4</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>47.4**</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>12</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>83.3</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>85.7</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>63.2**</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>14</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>81.2</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>90.9</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>77.8</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>70.0*†</t>
+          <t>94.7**</t>
         </is>
       </c>
     </row>

--- a/eval/results/statistical_tests_new30.xlsx
+++ b/eval/results/statistical_tests_new30.xlsx
@@ -519,7 +519,7 @@
         <v>0.146</v>
       </c>
       <c r="J2" t="n">
-        <v>0.236</v>
+        <v>0.189</v>
       </c>
     </row>
     <row r="3">
@@ -759,7 +759,7 @@
         <v>0.124</v>
       </c>
       <c r="J8" t="n">
-        <v>0.236</v>
+        <v>0.189</v>
       </c>
     </row>
     <row r="9">
@@ -824,22 +824,22 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.177</v>
+        <v>0.0571</v>
       </c>
       <c r="F10" t="n">
         <v>0.8</v>
       </c>
       <c r="G10" t="n">
-        <v>0.829</v>
+        <v>0.748</v>
       </c>
       <c r="H10" t="n">
         <v>0.14</v>
       </c>
       <c r="I10" t="n">
-        <v>0.115</v>
+        <v>0.178</v>
       </c>
       <c r="J10" t="n">
-        <v>0.266</v>
+        <v>0.171</v>
       </c>
     </row>
     <row r="11">
@@ -864,19 +864,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.105</v>
+        <v>0.0712</v>
       </c>
       <c r="F11" t="n">
         <v>0.8</v>
       </c>
       <c r="G11" t="n">
-        <v>0.829</v>
+        <v>0.748</v>
       </c>
       <c r="H11" t="n">
         <v>0.14</v>
       </c>
       <c r="I11" t="n">
-        <v>0.115</v>
+        <v>0.178</v>
       </c>
       <c r="J11" t="n">
         <v>0.164</v>
@@ -1479,7 +1479,7 @@
         <v>0.178</v>
       </c>
       <c r="J26" t="n">
-        <v>0.548</v>
+        <v>0.594</v>
       </c>
     </row>
     <row r="27">
@@ -1519,7 +1519,7 @@
         <v>0.178</v>
       </c>
       <c r="J27" t="n">
-        <v>0.128</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="28">
@@ -1544,22 +1544,22 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.404</v>
+        <v>0.594</v>
       </c>
       <c r="F28" t="n">
         <v>0.853</v>
       </c>
       <c r="G28" t="n">
-        <v>0.888</v>
+        <v>0.895</v>
       </c>
       <c r="H28" t="n">
         <v>0.13</v>
       </c>
       <c r="I28" t="n">
-        <v>0.179</v>
+        <v>0.256</v>
       </c>
       <c r="J28" t="n">
-        <v>0.455</v>
+        <v>0.594</v>
       </c>
     </row>
     <row r="29">
@@ -1584,22 +1584,22 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.11</v>
+        <v>0.0392</v>
       </c>
       <c r="F29" t="n">
         <v>0.853</v>
       </c>
       <c r="G29" t="n">
-        <v>0.888</v>
+        <v>0.895</v>
       </c>
       <c r="H29" t="n">
         <v>0.13</v>
       </c>
       <c r="I29" t="n">
-        <v>0.179</v>
+        <v>0.256</v>
       </c>
       <c r="J29" t="n">
-        <v>0.141</v>
+        <v>0.0706</v>
       </c>
     </row>
     <row r="30">
@@ -1639,7 +1639,7 @@
         <v>0.179</v>
       </c>
       <c r="J30" t="n">
-        <v>0.455</v>
+        <v>0.519</v>
       </c>
     </row>
     <row r="31">
@@ -1719,7 +1719,7 @@
         <v>0.174</v>
       </c>
       <c r="J32" t="n">
-        <v>0.455</v>
+        <v>0.497</v>
       </c>
     </row>
     <row r="33">
@@ -1799,7 +1799,7 @@
         <v>0.204</v>
       </c>
       <c r="J34" t="n">
-        <v>0.455</v>
+        <v>0.519</v>
       </c>
     </row>
     <row r="35">
@@ -1879,7 +1879,7 @@
         <v>0.185</v>
       </c>
       <c r="J36" t="n">
-        <v>0.455</v>
+        <v>0.519</v>
       </c>
     </row>
     <row r="37">
@@ -2119,7 +2119,7 @@
         <v>0.264</v>
       </c>
       <c r="J42" t="n">
-        <v>0.342</v>
+        <v>0.274</v>
       </c>
     </row>
     <row r="43">
@@ -2159,7 +2159,7 @@
         <v>0.264</v>
       </c>
       <c r="J43" t="n">
-        <v>0.306</v>
+        <v>0.245</v>
       </c>
     </row>
     <row r="44">
@@ -2199,7 +2199,7 @@
         <v>0.227</v>
       </c>
       <c r="J44" t="n">
-        <v>0.0312</v>
+        <v>0.0208</v>
       </c>
     </row>
     <row r="45">
@@ -2239,7 +2239,7 @@
         <v>0.227</v>
       </c>
       <c r="J45" t="n">
-        <v>0.02</v>
+        <v>0.009990000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -2264,22 +2264,22 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.635</v>
+        <v>0.000706</v>
       </c>
       <c r="F46" t="n">
         <v>0.8120000000000001</v>
       </c>
       <c r="G46" t="n">
-        <v>0.797</v>
+        <v>0.535</v>
       </c>
       <c r="H46" t="n">
         <v>0.218</v>
       </c>
       <c r="I46" t="n">
-        <v>0.212</v>
+        <v>0.297</v>
       </c>
       <c r="J46" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.00635</v>
       </c>
     </row>
     <row r="47">
@@ -2304,22 +2304,22 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.721</v>
+        <v>0.000153</v>
       </c>
       <c r="F47" t="n">
         <v>0.8120000000000001</v>
       </c>
       <c r="G47" t="n">
-        <v>0.797</v>
+        <v>0.535</v>
       </c>
       <c r="H47" t="n">
         <v>0.218</v>
       </c>
       <c r="I47" t="n">
-        <v>0.212</v>
+        <v>0.297</v>
       </c>
       <c r="J47" t="n">
-        <v>0.722</v>
+        <v>0.00138</v>
       </c>
     </row>
     <row r="48">
@@ -2439,7 +2439,7 @@
         <v>0.171</v>
       </c>
       <c r="J50" t="n">
-        <v>0.0399</v>
+        <v>0.0299</v>
       </c>
     </row>
     <row r="51">
@@ -2479,7 +2479,7 @@
         <v>0.171</v>
       </c>
       <c r="J51" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.0682</v>
       </c>
     </row>
     <row r="52">
@@ -2519,7 +2519,7 @@
         <v>0.213</v>
       </c>
       <c r="J52" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.764</v>
       </c>
     </row>
     <row r="53">
@@ -2559,7 +2559,7 @@
         <v>0.213</v>
       </c>
       <c r="J53" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.573</v>
       </c>
     </row>
     <row r="54">
@@ -2599,7 +2599,7 @@
         <v>0.217</v>
       </c>
       <c r="J54" t="n">
-        <v>0.0312</v>
+        <v>0.0208</v>
       </c>
     </row>
     <row r="55">
@@ -2639,7 +2639,7 @@
         <v>0.217</v>
       </c>
       <c r="J55" t="n">
-        <v>0.059</v>
+        <v>0.0393</v>
       </c>
     </row>
     <row r="56">
@@ -2679,7 +2679,7 @@
         <v>0.128</v>
       </c>
       <c r="J56" t="n">
-        <v>0.352</v>
+        <v>0.302</v>
       </c>
     </row>
     <row r="57">
@@ -2759,7 +2759,7 @@
         <v>0.137</v>
       </c>
       <c r="J58" t="n">
-        <v>0.352</v>
+        <v>0.302</v>
       </c>
     </row>
     <row r="59">
@@ -2799,7 +2799,7 @@
         <v>0.137</v>
       </c>
       <c r="J59" t="n">
-        <v>0.223</v>
+        <v>0.186</v>
       </c>
     </row>
     <row r="60">
@@ -2839,7 +2839,7 @@
         <v>0.216</v>
       </c>
       <c r="J60" t="n">
-        <v>0.44</v>
+        <v>0.385</v>
       </c>
     </row>
     <row r="61">
@@ -2919,7 +2919,7 @@
         <v>0.191</v>
       </c>
       <c r="J62" t="n">
-        <v>0.145</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="63">
@@ -2959,7 +2959,7 @@
         <v>0.191</v>
       </c>
       <c r="J63" t="n">
-        <v>0.16</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="64">
@@ -2984,22 +2984,22 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.927</v>
+        <v>0.00279</v>
       </c>
       <c r="F64" t="n">
         <v>0.803</v>
       </c>
       <c r="G64" t="n">
-        <v>0.806</v>
+        <v>0.628</v>
       </c>
       <c r="H64" t="n">
         <v>0.165</v>
       </c>
       <c r="I64" t="n">
-        <v>0.166</v>
+        <v>0.295</v>
       </c>
       <c r="J64" t="n">
-        <v>0.927</v>
+        <v>0.0251</v>
       </c>
     </row>
     <row r="65">
@@ -3024,22 +3024,22 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.388</v>
+        <v>0.00131</v>
       </c>
       <c r="F65" t="n">
         <v>0.803</v>
       </c>
       <c r="G65" t="n">
-        <v>0.806</v>
+        <v>0.628</v>
       </c>
       <c r="H65" t="n">
         <v>0.165</v>
       </c>
       <c r="I65" t="n">
-        <v>0.166</v>
+        <v>0.295</v>
       </c>
       <c r="J65" t="n">
-        <v>0.422</v>
+        <v>0.0118</v>
       </c>
     </row>
     <row r="66">
@@ -3159,7 +3159,7 @@
         <v>0.142</v>
       </c>
       <c r="J68" t="n">
-        <v>0.145</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="69">
@@ -3199,7 +3199,7 @@
         <v>0.142</v>
       </c>
       <c r="J69" t="n">
-        <v>0.196</v>
+        <v>0.147</v>
       </c>
     </row>
     <row r="70">
@@ -3239,7 +3239,7 @@
         <v>0.126</v>
       </c>
       <c r="J70" t="n">
-        <v>0.173</v>
+        <v>0.139</v>
       </c>
     </row>
     <row r="71">
@@ -3279,7 +3279,7 @@
         <v>0.126</v>
       </c>
       <c r="J71" t="n">
-        <v>0.223</v>
+        <v>0.186</v>
       </c>
     </row>
     <row r="72">
@@ -3319,7 +3319,7 @@
         <v>0.168</v>
       </c>
       <c r="J72" t="n">
-        <v>0.145</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="73">
@@ -3359,7 +3359,7 @@
         <v>0.168</v>
       </c>
       <c r="J73" t="n">
-        <v>0.16</v>
+        <v>0.106</v>
       </c>
     </row>
   </sheetData>
@@ -12960,13 +12960,13 @@
         <v>0.967</v>
       </c>
       <c r="G259" t="n">
-        <v>0.767</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="H259" t="n">
-        <v>0.0523</v>
+        <v>1</v>
       </c>
       <c r="I259" t="n">
-        <v>0.837</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260">
@@ -12997,7 +12997,7 @@
         <v>0.967</v>
       </c>
       <c r="G260" t="n">
-        <v>0.967</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="H260" t="n">
         <v>1</v>
@@ -13034,10 +13034,10 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H261" t="n">
-        <v>1</v>
+        <v>0.237</v>
       </c>
       <c r="I261" t="n">
         <v>1</v>
@@ -13071,10 +13071,10 @@
         <v>0.667</v>
       </c>
       <c r="G262" t="n">
-        <v>0.667</v>
+        <v>0.733</v>
       </c>
       <c r="H262" t="n">
-        <v>1</v>
+        <v>0.779</v>
       </c>
       <c r="I262" t="n">
         <v>1</v>
@@ -13108,10 +13108,10 @@
         <v>0.833</v>
       </c>
       <c r="G263" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="H263" t="n">
-        <v>0.424</v>
+        <v>0.706</v>
       </c>
       <c r="I263" t="n">
         <v>1</v>
@@ -13145,10 +13145,10 @@
         <v>0.9</v>
       </c>
       <c r="G264" t="n">
-        <v>0.9</v>
+        <v>0.833</v>
       </c>
       <c r="H264" t="n">
-        <v>1</v>
+        <v>0.706</v>
       </c>
       <c r="I264" t="n">
         <v>1</v>
@@ -13182,7 +13182,7 @@
         <v>0.833</v>
       </c>
       <c r="G265" t="n">
-        <v>0.867</v>
+        <v>0.8</v>
       </c>
       <c r="H265" t="n">
         <v>1</v>
@@ -13219,13 +13219,13 @@
         <v>0.767</v>
       </c>
       <c r="G266" t="n">
-        <v>0.7</v>
+        <v>0.467</v>
       </c>
       <c r="H266" t="n">
-        <v>0.771</v>
+        <v>0.0326</v>
       </c>
       <c r="I266" t="n">
-        <v>1</v>
+        <v>0.522</v>
       </c>
     </row>
     <row r="267">
@@ -13256,10 +13256,10 @@
         <v>0.767</v>
       </c>
       <c r="G267" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H267" t="n">
-        <v>1</v>
+        <v>0.771</v>
       </c>
       <c r="I267" t="n">
         <v>1</v>
@@ -13293,10 +13293,10 @@
         <v>0.633</v>
       </c>
       <c r="G268" t="n">
-        <v>0.767</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H268" t="n">
-        <v>0.399</v>
+        <v>0.792</v>
       </c>
       <c r="I268" t="n">
         <v>1</v>
@@ -13330,10 +13330,10 @@
         <v>0.8</v>
       </c>
       <c r="G269" t="n">
-        <v>0.9</v>
+        <v>0.767</v>
       </c>
       <c r="H269" t="n">
-        <v>0.472</v>
+        <v>1</v>
       </c>
       <c r="I269" t="n">
         <v>1</v>
@@ -13367,10 +13367,10 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="G270" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.867</v>
       </c>
       <c r="H270" t="n">
-        <v>1</v>
+        <v>0.671</v>
       </c>
       <c r="I270" t="n">
         <v>1</v>
@@ -13404,7 +13404,7 @@
         <v>0.833</v>
       </c>
       <c r="G271" t="n">
-        <v>0.867</v>
+        <v>0.833</v>
       </c>
       <c r="H271" t="n">
         <v>1</v>
@@ -13441,13 +13441,13 @@
         <v>0.633</v>
       </c>
       <c r="G272" t="n">
-        <v>0.733</v>
+        <v>0.4</v>
       </c>
       <c r="H272" t="n">
-        <v>0.58</v>
+        <v>0.12</v>
       </c>
       <c r="I272" t="n">
-        <v>1</v>
+        <v>0.964</v>
       </c>
     </row>
     <row r="273">
@@ -13478,10 +13478,10 @@
         <v>0.5</v>
       </c>
       <c r="G273" t="n">
-        <v>0.6</v>
+        <v>0.467</v>
       </c>
       <c r="H273" t="n">
-        <v>0.604</v>
+        <v>1</v>
       </c>
       <c r="I273" t="n">
         <v>1</v>
@@ -13515,10 +13515,10 @@
         <v>0.793</v>
       </c>
       <c r="G274" t="n">
-        <v>0.885</v>
+        <v>0.857</v>
       </c>
       <c r="H274" t="n">
-        <v>0.475</v>
+        <v>0.73</v>
       </c>
       <c r="I274" t="n">
         <v>1</v>
@@ -13552,10 +13552,10 @@
         <v>0.75</v>
       </c>
       <c r="G275" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="H275" t="n">
-        <v>0.245</v>
+        <v>1</v>
       </c>
       <c r="I275" t="n">
         <v>1</v>
@@ -13589,7 +13589,7 @@
         <v>0.875</v>
       </c>
       <c r="G276" t="n">
-        <v>0.875</v>
+        <v>0.857</v>
       </c>
       <c r="H276" t="n">
         <v>1</v>
@@ -13663,7 +13663,7 @@
         <v>0.889</v>
       </c>
       <c r="G278" t="n">
-        <v>0.889</v>
+        <v>0.944</v>
       </c>
       <c r="H278" t="n">
         <v>1</v>
@@ -13700,10 +13700,10 @@
         <v>0.864</v>
       </c>
       <c r="G279" t="n">
-        <v>0.952</v>
+        <v>1</v>
       </c>
       <c r="H279" t="n">
-        <v>0.607</v>
+        <v>0.238</v>
       </c>
       <c r="I279" t="n">
         <v>1</v>
@@ -13737,10 +13737,10 @@
         <v>0.864</v>
       </c>
       <c r="G280" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H280" t="n">
-        <v>1</v>
+        <v>0.267</v>
       </c>
       <c r="I280" t="n">
         <v>1</v>
@@ -13773,9 +13773,7 @@
       <c r="F281" t="n">
         <v>1</v>
       </c>
-      <c r="G281" t="n">
-        <v>1</v>
-      </c>
+      <c r="G281" t="inlineStr"/>
       <c r="H281" t="n">
         <v>1</v>
       </c>
@@ -13885,10 +13883,10 @@
         <v>0.889</v>
       </c>
       <c r="G284" t="n">
-        <v>0.909</v>
+        <v>1</v>
       </c>
       <c r="H284" t="n">
-        <v>1</v>
+        <v>0.503</v>
       </c>
       <c r="I284" t="n">
         <v>1</v>
@@ -13925,7 +13923,7 @@
         <v>1</v>
       </c>
       <c r="H285" t="n">
-        <v>0.484</v>
+        <v>1</v>
       </c>
       <c r="I285" t="n">
         <v>1</v>
@@ -13959,7 +13957,7 @@
         <v>0.714</v>
       </c>
       <c r="G286" t="n">
-        <v>0.714</v>
+        <v>0.667</v>
       </c>
       <c r="H286" t="n">
         <v>1</v>
@@ -13999,7 +13997,7 @@
         <v>1</v>
       </c>
       <c r="H287" t="n">
-        <v>0.243</v>
+        <v>0.25</v>
       </c>
       <c r="I287" t="n">
         <v>1</v>
@@ -14036,10 +14034,10 @@
         <v>1</v>
       </c>
       <c r="H288" t="n">
-        <v>0.0357</v>
+        <v>1</v>
       </c>
       <c r="I288" t="n">
-        <v>0.572</v>
+        <v>1</v>
       </c>
     </row>
     <row r="289">
@@ -14070,10 +14068,10 @@
         <v>0.545</v>
       </c>
       <c r="G289" t="n">
-        <v>0.778</v>
+        <v>1</v>
       </c>
       <c r="H289" t="n">
-        <v>0.418</v>
+        <v>1</v>
       </c>
       <c r="I289" t="n">
         <v>1</v>
@@ -14107,7 +14105,7 @@
         <v>0.958</v>
       </c>
       <c r="G290" t="n">
-        <v>0.958</v>
+        <v>1</v>
       </c>
       <c r="H290" t="n">
         <v>1</v>
@@ -14144,13 +14142,13 @@
         <v>1</v>
       </c>
       <c r="G291" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
       <c r="H291" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="I291" t="n">
-        <v>1</v>
+        <v>0.724</v>
       </c>
     </row>
     <row r="292">
@@ -14181,7 +14179,7 @@
         <v>1</v>
       </c>
       <c r="G292" t="n">
-        <v>1</v>
+        <v>0.857</v>
       </c>
       <c r="H292" t="n">
         <v>1</v>
@@ -14218,13 +14216,13 @@
         <v>1</v>
       </c>
       <c r="G293" t="n">
-        <v>1</v>
+        <v>0.571</v>
       </c>
       <c r="H293" t="n">
-        <v>1</v>
+        <v>0.192</v>
       </c>
       <c r="I293" t="n">
-        <v>1</v>
+        <v>0.513</v>
       </c>
     </row>
     <row r="294">
@@ -14255,7 +14253,7 @@
         <v>0.667</v>
       </c>
       <c r="G294" t="n">
-        <v>0.667</v>
+        <v>0.708</v>
       </c>
       <c r="H294" t="n">
         <v>1</v>
@@ -14292,7 +14290,7 @@
         <v>0.905</v>
       </c>
       <c r="G295" t="n">
-        <v>0.952</v>
+        <v>0.857</v>
       </c>
       <c r="H295" t="n">
         <v>1</v>
@@ -14329,13 +14327,13 @@
         <v>1</v>
       </c>
       <c r="G296" t="n">
-        <v>0.947</v>
+        <v>0.737</v>
       </c>
       <c r="H296" t="n">
-        <v>1</v>
+        <v>0.0463</v>
       </c>
       <c r="I296" t="n">
-        <v>1</v>
+        <v>0.185</v>
       </c>
     </row>
     <row r="297">
@@ -14366,7 +14364,7 @@
         <v>0.167</v>
       </c>
       <c r="G297" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="H297" t="n">
         <v>1</v>
@@ -14403,13 +14401,13 @@
         <v>0.767</v>
       </c>
       <c r="G298" t="n">
-        <v>0.7</v>
+        <v>0.467</v>
       </c>
       <c r="H298" t="n">
-        <v>0.771</v>
+        <v>0.0326</v>
       </c>
       <c r="I298" t="n">
-        <v>1</v>
+        <v>0.174</v>
       </c>
     </row>
     <row r="299">
@@ -14440,10 +14438,10 @@
         <v>0.696</v>
       </c>
       <c r="G299" t="n">
-        <v>0.739</v>
+        <v>0.609</v>
       </c>
       <c r="H299" t="n">
-        <v>1</v>
+        <v>0.758</v>
       </c>
       <c r="I299" t="n">
         <v>1</v>
@@ -14477,13 +14475,13 @@
         <v>0.64</v>
       </c>
       <c r="G300" t="n">
-        <v>0.8</v>
+        <v>0.48</v>
       </c>
       <c r="H300" t="n">
-        <v>0.345</v>
+        <v>0.393</v>
       </c>
       <c r="I300" t="n">
-        <v>1</v>
+        <v>0.724</v>
       </c>
     </row>
     <row r="301">
@@ -14514,10 +14512,10 @@
         <v>0.737</v>
       </c>
       <c r="G301" t="n">
-        <v>0.842</v>
+        <v>0.632</v>
       </c>
       <c r="H301" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.728</v>
       </c>
       <c r="I301" t="n">
         <v>1</v>
@@ -14551,13 +14549,13 @@
         <v>1</v>
       </c>
       <c r="G302" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="H302" t="n">
-        <v>1</v>
+        <v>0.167</v>
       </c>
       <c r="I302" t="n">
-        <v>1</v>
+        <v>0.513</v>
       </c>
     </row>
     <row r="303">
@@ -14588,13 +14586,13 @@
         <v>0.9</v>
       </c>
       <c r="G303" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="H303" t="n">
-        <v>0.661</v>
+        <v>0.407</v>
       </c>
       <c r="I303" t="n">
-        <v>1</v>
+        <v>0.724</v>
       </c>
     </row>
     <row r="304">
@@ -14625,13 +14623,13 @@
         <v>0.85</v>
       </c>
       <c r="G304" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="H304" t="n">
-        <v>0.155</v>
+        <v>3.36e-06</v>
       </c>
       <c r="I304" t="n">
-        <v>1</v>
+        <v>5.37e-05</v>
       </c>
     </row>
     <row r="305">
@@ -14662,13 +14660,13 @@
         <v>0.706</v>
       </c>
       <c r="G305" t="n">
-        <v>0.412</v>
+        <v>0.0588</v>
       </c>
       <c r="H305" t="n">
-        <v>0.166</v>
+        <v>0.000232</v>
       </c>
       <c r="I305" t="n">
-        <v>1</v>
+        <v>0.00185</v>
       </c>
     </row>
     <row r="306">
@@ -14699,13 +14697,13 @@
         <v>0.868</v>
       </c>
       <c r="G306" t="n">
-        <v>0.92</v>
+        <v>0.923</v>
       </c>
       <c r="H306" t="n">
-        <v>0.527</v>
+        <v>0.526</v>
       </c>
       <c r="I306" t="n">
-        <v>1</v>
+        <v>0.797</v>
       </c>
     </row>
     <row r="307">
@@ -14736,13 +14734,13 @@
         <v>0.857</v>
       </c>
       <c r="G307" t="n">
-        <v>0.462</v>
+        <v>0.5</v>
       </c>
       <c r="H307" t="n">
-        <v>0.158</v>
+        <v>0.491</v>
       </c>
       <c r="I307" t="n">
-        <v>1</v>
+        <v>0.797</v>
       </c>
     </row>
     <row r="308">
@@ -14773,13 +14771,13 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="G308" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.857</v>
       </c>
       <c r="H308" t="n">
-        <v>1</v>
+        <v>0.598</v>
       </c>
       <c r="I308" t="n">
-        <v>1</v>
+        <v>0.797</v>
       </c>
     </row>
     <row r="309">
@@ -14810,13 +14808,13 @@
         <v>1</v>
       </c>
       <c r="G309" t="n">
-        <v>1</v>
+        <v>0.727</v>
       </c>
       <c r="H309" t="n">
-        <v>1</v>
+        <v>0.0717</v>
       </c>
       <c r="I309" t="n">
-        <v>1</v>
+        <v>0.287</v>
       </c>
     </row>
     <row r="310">
@@ -14847,13 +14845,13 @@
         <v>0.762</v>
       </c>
       <c r="G310" t="n">
-        <v>0.762</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H310" t="n">
-        <v>1</v>
+        <v>0.791</v>
       </c>
       <c r="I310" t="n">
-        <v>1</v>
+        <v>0.844</v>
       </c>
     </row>
     <row r="311">
@@ -14884,13 +14882,13 @@
         <v>0.884</v>
       </c>
       <c r="G311" t="n">
-        <v>0.952</v>
+        <v>0.923</v>
       </c>
       <c r="H311" t="n">
-        <v>0.433</v>
+        <v>0.715</v>
       </c>
       <c r="I311" t="n">
-        <v>1</v>
+        <v>0.844</v>
       </c>
     </row>
     <row r="312">
@@ -14921,13 +14919,13 @@
         <v>0.927</v>
       </c>
       <c r="G312" t="n">
-        <v>0.923</v>
+        <v>0.848</v>
       </c>
       <c r="H312" t="n">
-        <v>1</v>
+        <v>0.454</v>
       </c>
       <c r="I312" t="n">
-        <v>1</v>
+        <v>0.797</v>
       </c>
     </row>
     <row r="313">
@@ -14958,13 +14956,13 @@
         <v>0.286</v>
       </c>
       <c r="G313" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H313" t="n">
-        <v>0.608</v>
+        <v>0.462</v>
       </c>
       <c r="I313" t="n">
-        <v>1</v>
+        <v>0.797</v>
       </c>
     </row>
     <row r="314">
@@ -14995,13 +14993,13 @@
         <v>0.868</v>
       </c>
       <c r="G314" t="n">
-        <v>0.824</v>
+        <v>0.636</v>
       </c>
       <c r="H314" t="n">
-        <v>0.594</v>
+        <v>0.00912</v>
       </c>
       <c r="I314" t="n">
-        <v>1</v>
+        <v>0.0486</v>
       </c>
     </row>
     <row r="315">
@@ -15032,13 +15030,13 @@
         <v>0.821</v>
       </c>
       <c r="G315" t="n">
-        <v>0.85</v>
+        <v>0.757</v>
       </c>
       <c r="H315" t="n">
-        <v>0.77</v>
+        <v>0.579</v>
       </c>
       <c r="I315" t="n">
-        <v>1</v>
+        <v>0.797</v>
       </c>
     </row>
     <row r="316">
@@ -15069,13 +15067,13 @@
         <v>0.744</v>
       </c>
       <c r="G316" t="n">
-        <v>0.851</v>
+        <v>0.649</v>
       </c>
       <c r="H316" t="n">
-        <v>0.292</v>
+        <v>0.464</v>
       </c>
       <c r="I316" t="n">
-        <v>1</v>
+        <v>0.797</v>
       </c>
     </row>
     <row r="317">
@@ -15106,13 +15104,13 @@
         <v>0.824</v>
       </c>
       <c r="G317" t="n">
-        <v>0.914</v>
+        <v>0.774</v>
       </c>
       <c r="H317" t="n">
-        <v>0.306</v>
+        <v>0.759</v>
       </c>
       <c r="I317" t="n">
-        <v>1</v>
+        <v>0.844</v>
       </c>
     </row>
     <row r="318">
@@ -15143,13 +15141,13 @@
         <v>0.833</v>
       </c>
       <c r="G318" t="n">
-        <v>0.833</v>
+        <v>0.5</v>
       </c>
       <c r="H318" t="n">
-        <v>1</v>
+        <v>0.161</v>
       </c>
       <c r="I318" t="n">
-        <v>1</v>
+        <v>0.516</v>
       </c>
     </row>
     <row r="319">
@@ -15180,7 +15178,7 @@
         <v>0.878</v>
       </c>
       <c r="G319" t="n">
-        <v>0.889</v>
+        <v>0.857</v>
       </c>
       <c r="H319" t="n">
         <v>1</v>
@@ -15217,13 +15215,13 @@
         <v>0.756</v>
       </c>
       <c r="G320" t="n">
-        <v>0.75</v>
+        <v>0.182</v>
       </c>
       <c r="H320" t="n">
-        <v>1</v>
+        <v>1.32e-05</v>
       </c>
       <c r="I320" t="n">
-        <v>1</v>
+        <v>0.000212</v>
       </c>
     </row>
     <row r="321">
@@ -15254,13 +15252,13 @@
         <v>0.615</v>
       </c>
       <c r="G321" t="n">
-        <v>0.538</v>
+        <v>0.111</v>
       </c>
       <c r="H321" t="n">
-        <v>0.612</v>
+        <v>0.000458</v>
       </c>
       <c r="I321" t="n">
-        <v>1</v>
+        <v>0.00366</v>
       </c>
     </row>
     <row r="322">

--- a/eval/results/statistical_tests_new30.xlsx
+++ b/eval/results/statistical_tests_new30.xlsx
@@ -519,7 +519,7 @@
         <v>0.146</v>
       </c>
       <c r="J2" t="n">
-        <v>0.189</v>
+        <v>0.198</v>
       </c>
     </row>
     <row r="3">
@@ -559,7 +559,7 @@
         <v>0.146</v>
       </c>
       <c r="J3" t="n">
-        <v>0.164</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="4">
@@ -599,7 +599,7 @@
         <v>0.101</v>
       </c>
       <c r="J4" t="n">
-        <v>0.158</v>
+        <v>0.126</v>
       </c>
     </row>
     <row r="5">
@@ -639,7 +639,7 @@
         <v>0.101</v>
       </c>
       <c r="J5" t="n">
-        <v>0.145</v>
+        <v>0.09660000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -679,7 +679,7 @@
         <v>0.157</v>
       </c>
       <c r="J6" t="n">
-        <v>0.889</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -759,7 +759,7 @@
         <v>0.124</v>
       </c>
       <c r="J8" t="n">
-        <v>0.189</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="9">
@@ -799,7 +799,7 @@
         <v>0.124</v>
       </c>
       <c r="J9" t="n">
-        <v>0.164</v>
+        <v>0.159</v>
       </c>
     </row>
     <row r="10">
@@ -839,7 +839,7 @@
         <v>0.178</v>
       </c>
       <c r="J10" t="n">
-        <v>0.171</v>
+        <v>0.147</v>
       </c>
     </row>
     <row r="11">
@@ -879,7 +879,7 @@
         <v>0.178</v>
       </c>
       <c r="J11" t="n">
-        <v>0.164</v>
+        <v>0.151</v>
       </c>
     </row>
     <row r="12">
@@ -919,7 +919,7 @@
         <v>0.115</v>
       </c>
       <c r="J12" t="n">
-        <v>0.266</v>
+        <v>0.335</v>
       </c>
     </row>
     <row r="13">
@@ -959,7 +959,7 @@
         <v>0.115</v>
       </c>
       <c r="J13" t="n">
-        <v>0.164</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="14">
@@ -999,7 +999,7 @@
         <v>0.181</v>
       </c>
       <c r="J14" t="n">
-        <v>0.455</v>
+        <v>0.519</v>
       </c>
     </row>
     <row r="15">
@@ -1039,7 +1039,7 @@
         <v>0.181</v>
       </c>
       <c r="J15" t="n">
-        <v>0.549</v>
+        <v>0.599</v>
       </c>
     </row>
     <row r="16">
@@ -1079,7 +1079,7 @@
         <v>0.136</v>
       </c>
       <c r="J16" t="n">
-        <v>0.289</v>
+        <v>0.368</v>
       </c>
     </row>
     <row r="17">
@@ -1119,7 +1119,7 @@
         <v>0.136</v>
       </c>
       <c r="J17" t="n">
-        <v>0.393</v>
+        <v>0.441</v>
       </c>
     </row>
     <row r="18">
@@ -1159,7 +1159,7 @@
         <v>0.15</v>
       </c>
       <c r="J18" t="n">
-        <v>0.158</v>
+        <v>0.114</v>
       </c>
     </row>
     <row r="19">
@@ -1199,7 +1199,7 @@
         <v>0.15</v>
       </c>
       <c r="J19" t="n">
-        <v>0.145</v>
+        <v>0.09660000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -1239,7 +1239,7 @@
         <v>0.115</v>
       </c>
       <c r="J20" t="n">
-        <v>0.165</v>
+        <v>0.147</v>
       </c>
     </row>
     <row r="21">
@@ -1279,7 +1279,7 @@
         <v>0.115</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0639</v>
+        <v>0.09660000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1319,7 +1319,7 @@
         <v>0.127</v>
       </c>
       <c r="J22" t="n">
-        <v>0.107</v>
+        <v>0.0798</v>
       </c>
     </row>
     <row r="23">
@@ -1439,7 +1439,7 @@
         <v>0.192</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0639</v>
+        <v>0.09660000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1479,7 +1479,7 @@
         <v>0.178</v>
       </c>
       <c r="J26" t="n">
-        <v>0.594</v>
+        <v>0.658</v>
       </c>
     </row>
     <row r="27">
@@ -1519,7 +1519,7 @@
         <v>0.178</v>
       </c>
       <c r="J27" t="n">
-        <v>0.107</v>
+        <v>0.151</v>
       </c>
     </row>
     <row r="28">
@@ -1559,7 +1559,7 @@
         <v>0.256</v>
       </c>
       <c r="J28" t="n">
-        <v>0.594</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -1599,7 +1599,7 @@
         <v>0.256</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0706</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="30">
@@ -1679,7 +1679,7 @@
         <v>0.179</v>
       </c>
       <c r="J31" t="n">
-        <v>0.141</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="32">
@@ -1719,7 +1719,7 @@
         <v>0.174</v>
       </c>
       <c r="J32" t="n">
-        <v>0.497</v>
+        <v>0.368</v>
       </c>
     </row>
     <row r="33">
@@ -1759,7 +1759,7 @@
         <v>0.174</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0639</v>
+        <v>0.09660000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1839,7 +1839,7 @@
         <v>0.204</v>
       </c>
       <c r="J35" t="n">
-        <v>0.372</v>
+        <v>0.458</v>
       </c>
     </row>
     <row r="36">
@@ -1879,7 +1879,7 @@
         <v>0.185</v>
       </c>
       <c r="J36" t="n">
-        <v>0.519</v>
+        <v>0.508</v>
       </c>
     </row>
     <row r="37">
@@ -1919,7 +1919,7 @@
         <v>0.185</v>
       </c>
       <c r="J37" t="n">
-        <v>0.382</v>
+        <v>0.466</v>
       </c>
     </row>
     <row r="38">
@@ -1959,7 +1959,7 @@
         <v>0.191</v>
       </c>
       <c r="J38" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.926</v>
       </c>
     </row>
     <row r="39">
@@ -1999,7 +1999,7 @@
         <v>0.191</v>
       </c>
       <c r="J39" t="n">
-        <v>0.722</v>
+        <v>0.714</v>
       </c>
     </row>
     <row r="40">
@@ -2119,7 +2119,7 @@
         <v>0.264</v>
       </c>
       <c r="J42" t="n">
-        <v>0.274</v>
+        <v>0.304</v>
       </c>
     </row>
     <row r="43">
@@ -2159,7 +2159,7 @@
         <v>0.264</v>
       </c>
       <c r="J43" t="n">
-        <v>0.245</v>
+        <v>0.204</v>
       </c>
     </row>
     <row r="44">
@@ -2199,7 +2199,7 @@
         <v>0.227</v>
       </c>
       <c r="J44" t="n">
-        <v>0.0208</v>
+        <v>0.0624</v>
       </c>
     </row>
     <row r="45">
@@ -2239,7 +2239,7 @@
         <v>0.227</v>
       </c>
       <c r="J45" t="n">
-        <v>0.009990000000000001</v>
+        <v>0.0266</v>
       </c>
     </row>
     <row r="46">
@@ -2279,7 +2279,7 @@
         <v>0.297</v>
       </c>
       <c r="J46" t="n">
-        <v>0.00635</v>
+        <v>0.0254</v>
       </c>
     </row>
     <row r="47">
@@ -2319,7 +2319,7 @@
         <v>0.297</v>
       </c>
       <c r="J47" t="n">
-        <v>0.00138</v>
+        <v>0.00551</v>
       </c>
     </row>
     <row r="48">
@@ -2359,7 +2359,7 @@
         <v>0.212</v>
       </c>
       <c r="J48" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.714</v>
       </c>
     </row>
     <row r="49">
@@ -2439,7 +2439,7 @@
         <v>0.171</v>
       </c>
       <c r="J50" t="n">
-        <v>0.0299</v>
+        <v>0.0798</v>
       </c>
     </row>
     <row r="51">
@@ -2479,7 +2479,7 @@
         <v>0.171</v>
       </c>
       <c r="J51" t="n">
-        <v>0.0682</v>
+        <v>0.09660000000000001</v>
       </c>
     </row>
     <row r="52">
@@ -2519,7 +2519,7 @@
         <v>0.213</v>
       </c>
       <c r="J52" t="n">
-        <v>0.764</v>
+        <v>0.632</v>
       </c>
     </row>
     <row r="53">
@@ -2559,7 +2559,7 @@
         <v>0.213</v>
       </c>
       <c r="J53" t="n">
-        <v>0.573</v>
+        <v>0.466</v>
       </c>
     </row>
     <row r="54">
@@ -2599,7 +2599,7 @@
         <v>0.217</v>
       </c>
       <c r="J54" t="n">
-        <v>0.0208</v>
+        <v>0.0624</v>
       </c>
     </row>
     <row r="55">
@@ -2639,7 +2639,7 @@
         <v>0.217</v>
       </c>
       <c r="J55" t="n">
-        <v>0.0393</v>
+        <v>0.09429999999999999</v>
       </c>
     </row>
     <row r="56">
@@ -2679,7 +2679,7 @@
         <v>0.128</v>
       </c>
       <c r="J56" t="n">
-        <v>0.302</v>
+        <v>0.368</v>
       </c>
     </row>
     <row r="57">
@@ -2719,7 +2719,7 @@
         <v>0.128</v>
       </c>
       <c r="J57" t="n">
-        <v>0.422</v>
+        <v>0.466</v>
       </c>
     </row>
     <row r="58">
@@ -2759,7 +2759,7 @@
         <v>0.137</v>
       </c>
       <c r="J58" t="n">
-        <v>0.302</v>
+        <v>0.368</v>
       </c>
     </row>
     <row r="59">
@@ -2799,7 +2799,7 @@
         <v>0.137</v>
       </c>
       <c r="J59" t="n">
-        <v>0.186</v>
+        <v>0.194</v>
       </c>
     </row>
     <row r="60">
@@ -2839,7 +2839,7 @@
         <v>0.216</v>
       </c>
       <c r="J60" t="n">
-        <v>0.385</v>
+        <v>0.508</v>
       </c>
     </row>
     <row r="61">
@@ -2879,7 +2879,7 @@
         <v>0.216</v>
       </c>
       <c r="J61" t="n">
-        <v>0.422</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="62">
@@ -2919,7 +2919,7 @@
         <v>0.191</v>
       </c>
       <c r="J62" t="n">
-        <v>0.109</v>
+        <v>0.145</v>
       </c>
     </row>
     <row r="63">
@@ -2959,7 +2959,7 @@
         <v>0.191</v>
       </c>
       <c r="J63" t="n">
-        <v>0.106</v>
+        <v>0.09660000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2999,7 +2999,7 @@
         <v>0.295</v>
       </c>
       <c r="J64" t="n">
-        <v>0.0251</v>
+        <v>0.0502</v>
       </c>
     </row>
     <row r="65">
@@ -3039,7 +3039,7 @@
         <v>0.295</v>
       </c>
       <c r="J65" t="n">
-        <v>0.0118</v>
+        <v>0.0236</v>
       </c>
     </row>
     <row r="66">
@@ -3079,7 +3079,7 @@
         <v>0.166</v>
       </c>
       <c r="J66" t="n">
-        <v>0.927</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -3119,7 +3119,7 @@
         <v>0.166</v>
       </c>
       <c r="J67" t="n">
-        <v>0.422</v>
+        <v>0.466</v>
       </c>
     </row>
     <row r="68">
@@ -3159,7 +3159,7 @@
         <v>0.142</v>
       </c>
       <c r="J68" t="n">
-        <v>0.109</v>
+        <v>0.145</v>
       </c>
     </row>
     <row r="69">
@@ -3199,7 +3199,7 @@
         <v>0.142</v>
       </c>
       <c r="J69" t="n">
-        <v>0.147</v>
+        <v>0.151</v>
       </c>
     </row>
     <row r="70">
@@ -3239,7 +3239,7 @@
         <v>0.126</v>
       </c>
       <c r="J70" t="n">
-        <v>0.139</v>
+        <v>0.185</v>
       </c>
     </row>
     <row r="71">
@@ -3279,7 +3279,7 @@
         <v>0.126</v>
       </c>
       <c r="J71" t="n">
-        <v>0.186</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="72">
@@ -3319,7 +3319,7 @@
         <v>0.168</v>
       </c>
       <c r="J72" t="n">
-        <v>0.109</v>
+        <v>0.126</v>
       </c>
     </row>
     <row r="73">
@@ -3359,7 +3359,7 @@
         <v>0.168</v>
       </c>
       <c r="J73" t="n">
-        <v>0.106</v>
+        <v>0.0983</v>
       </c>
     </row>
   </sheetData>

--- a/eval/results/statistical_tests_new30.xlsx
+++ b/eval/results/statistical_tests_new30.xlsx
@@ -3494,7 +3494,7 @@
         <v>0.0523</v>
       </c>
       <c r="I3" t="n">
-        <v>0.837</v>
+        <v>0.173</v>
       </c>
     </row>
     <row r="4">
@@ -4012,7 +4012,7 @@
         <v>0.301</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0.909</v>
       </c>
     </row>
     <row r="18">
@@ -4049,7 +4049,7 @@
         <v>0.277</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0.946</v>
       </c>
     </row>
     <row r="19">
@@ -4086,7 +4086,7 @@
         <v>0.245</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0.821</v>
       </c>
     </row>
     <row r="20">
@@ -4604,7 +4604,7 @@
         <v>0.35</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0.9409999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -5196,7 +5196,7 @@
         <v>0.259</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0.583</v>
       </c>
     </row>
     <row r="50">
@@ -5270,7 +5270,7 @@
         <v>0.158</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0.474</v>
       </c>
     </row>
     <row r="52">
@@ -5492,7 +5492,7 @@
         <v>0.628</v>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>0.9419999999999999</v>
       </c>
     </row>
     <row r="58">
@@ -5529,7 +5529,7 @@
         <v>0.796</v>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="59">
@@ -5603,7 +5603,7 @@
         <v>0.625</v>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>0.8179999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -5640,7 +5640,7 @@
         <v>0.711</v>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>0.788</v>
       </c>
     </row>
     <row r="62">
@@ -5788,7 +5788,7 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>0.252</v>
       </c>
     </row>
     <row r="66">
@@ -5862,7 +5862,7 @@
         <v>0.145</v>
       </c>
       <c r="I67" t="n">
-        <v>0.719</v>
+        <v>0.261</v>
       </c>
     </row>
     <row r="68">
@@ -6158,7 +6158,7 @@
         <v>0.18</v>
       </c>
       <c r="I75" t="n">
-        <v>0.719</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -6195,7 +6195,7 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>0.719</v>
+        <v>0.756</v>
       </c>
     </row>
     <row r="77">
@@ -6380,7 +6380,7 @@
         <v>0.12</v>
       </c>
       <c r="I81" t="n">
-        <v>0.719</v>
+        <v>0.909</v>
       </c>
     </row>
     <row r="82">
@@ -6417,7 +6417,7 @@
         <v>0.481</v>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>0.946</v>
       </c>
     </row>
     <row r="83">
@@ -6454,7 +6454,7 @@
         <v>0.329</v>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>0.821</v>
       </c>
     </row>
     <row r="84">
@@ -6972,7 +6972,7 @@
         <v>0.119</v>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="98">
@@ -7379,7 +7379,7 @@
         <v>0.496</v>
       </c>
       <c r="I108" t="n">
-        <v>1</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="109">
@@ -7416,7 +7416,7 @@
         <v>0.405</v>
       </c>
       <c r="I109" t="n">
-        <v>1</v>
+        <v>0.955</v>
       </c>
     </row>
     <row r="110">
@@ -7490,7 +7490,7 @@
         <v>0.605</v>
       </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="112">
@@ -7564,7 +7564,7 @@
         <v>0.259</v>
       </c>
       <c r="I113" t="n">
-        <v>1</v>
+        <v>0.583</v>
       </c>
     </row>
     <row r="114">
@@ -7638,7 +7638,7 @@
         <v>0.367</v>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>0.826</v>
       </c>
     </row>
     <row r="116">
@@ -7712,7 +7712,7 @@
         <v>0.481</v>
       </c>
       <c r="I117" t="n">
-        <v>1</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="118">
@@ -7860,7 +7860,7 @@
         <v>0.321</v>
       </c>
       <c r="I121" t="n">
-        <v>1</v>
+        <v>0.9419999999999999</v>
       </c>
     </row>
     <row r="122">
@@ -7897,7 +7897,7 @@
         <v>0.594</v>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="123">
@@ -7934,7 +7934,7 @@
         <v>0.136</v>
       </c>
       <c r="I123" t="n">
-        <v>0.727</v>
+        <v>0.675</v>
       </c>
     </row>
     <row r="124">
@@ -7971,7 +7971,7 @@
         <v>0.107</v>
       </c>
       <c r="I124" t="n">
-        <v>0.727</v>
+        <v>0.8179999999999999</v>
       </c>
     </row>
     <row r="125">
@@ -8008,7 +8008,7 @@
         <v>0.462</v>
       </c>
       <c r="I125" t="n">
-        <v>1</v>
+        <v>0.788</v>
       </c>
     </row>
     <row r="126">
@@ -8156,7 +8156,7 @@
         <v>0.0421</v>
       </c>
       <c r="I129" t="n">
-        <v>0.673</v>
+        <v>0.189</v>
       </c>
     </row>
     <row r="130">
@@ -8785,7 +8785,7 @@
         <v>0.734</v>
       </c>
       <c r="I146" t="n">
-        <v>1</v>
+        <v>0.946</v>
       </c>
     </row>
     <row r="147">
@@ -9747,7 +9747,7 @@
         <v>0.762</v>
       </c>
       <c r="I172" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="173">
@@ -9784,7 +9784,7 @@
         <v>0.66</v>
       </c>
       <c r="I173" t="n">
-        <v>1</v>
+        <v>0.955</v>
       </c>
     </row>
     <row r="174">
@@ -9858,7 +9858,7 @@
         <v>0.342</v>
       </c>
       <c r="I175" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="176">
@@ -9895,7 +9895,7 @@
         <v>0.523</v>
       </c>
       <c r="I176" t="n">
-        <v>1</v>
+        <v>0.9409999999999999</v>
       </c>
     </row>
     <row r="177">
@@ -10080,7 +10080,7 @@
         <v>0.481</v>
       </c>
       <c r="I181" t="n">
-        <v>1</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="182">
@@ -10228,7 +10228,7 @@
         <v>0.321</v>
       </c>
       <c r="I185" t="n">
-        <v>1</v>
+        <v>0.9419999999999999</v>
       </c>
     </row>
     <row r="186">
@@ -10265,7 +10265,7 @@
         <v>0.804</v>
       </c>
       <c r="I186" t="n">
-        <v>1</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="187">
@@ -10302,7 +10302,7 @@
         <v>0.225</v>
       </c>
       <c r="I187" t="n">
-        <v>1</v>
+        <v>0.675</v>
       </c>
     </row>
     <row r="188">
@@ -10339,7 +10339,7 @@
         <v>0.8169999999999999</v>
       </c>
       <c r="I188" t="n">
-        <v>1</v>
+        <v>0.8179999999999999</v>
       </c>
     </row>
     <row r="189">
@@ -10376,7 +10376,7 @@
         <v>0.473</v>
       </c>
       <c r="I189" t="n">
-        <v>1</v>
+        <v>0.788</v>
       </c>
     </row>
     <row r="190">
@@ -10524,7 +10524,7 @@
         <v>0.729</v>
       </c>
       <c r="I193" t="n">
-        <v>1</v>
+        <v>0.905</v>
       </c>
     </row>
     <row r="194">
@@ -10598,7 +10598,7 @@
         <v>0.353</v>
       </c>
       <c r="I195" t="n">
-        <v>1</v>
+        <v>0.529</v>
       </c>
     </row>
     <row r="196">
@@ -10635,7 +10635,7 @@
         <v>0.195</v>
       </c>
       <c r="I196" t="n">
-        <v>1</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="197">
@@ -10857,7 +10857,7 @@
         <v>0.103</v>
       </c>
       <c r="I202" t="n">
-        <v>1</v>
+        <v>0.357</v>
       </c>
     </row>
     <row r="203">
@@ -11116,7 +11116,7 @@
         <v>0.435</v>
       </c>
       <c r="I209" t="n">
-        <v>1</v>
+        <v>0.909</v>
       </c>
     </row>
     <row r="210">
@@ -11153,7 +11153,7 @@
         <v>0.44</v>
       </c>
       <c r="I210" t="n">
-        <v>1</v>
+        <v>0.946</v>
       </c>
     </row>
     <row r="211">
@@ -11190,7 +11190,7 @@
         <v>0.486</v>
       </c>
       <c r="I211" t="n">
-        <v>1</v>
+        <v>0.821</v>
       </c>
     </row>
     <row r="212">
@@ -11708,7 +11708,7 @@
         <v>0.526</v>
       </c>
       <c r="I225" t="n">
-        <v>1</v>
+        <v>0.947</v>
       </c>
     </row>
     <row r="226">
@@ -11819,7 +11819,7 @@
         <v>0.021</v>
       </c>
       <c r="I228" t="n">
-        <v>0.336</v>
+        <v>0.189</v>
       </c>
     </row>
     <row r="229">
@@ -11967,7 +11967,7 @@
         <v>0.23</v>
       </c>
       <c r="I232" t="n">
-        <v>1</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="233">
@@ -12041,7 +12041,7 @@
         <v>0.103</v>
       </c>
       <c r="I234" t="n">
-        <v>0.827</v>
+        <v>0.357</v>
       </c>
     </row>
     <row r="235">
@@ -12115,7 +12115,7 @@
         <v>0.5669999999999999</v>
       </c>
       <c r="I236" t="n">
-        <v>1</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="237">
@@ -12152,7 +12152,7 @@
         <v>0.728</v>
       </c>
       <c r="I237" t="n">
-        <v>1</v>
+        <v>0.955</v>
       </c>
     </row>
     <row r="238">
@@ -12226,7 +12226,7 @@
         <v>0.407</v>
       </c>
       <c r="I239" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="240">
@@ -12374,7 +12374,7 @@
         <v>0.103</v>
       </c>
       <c r="I243" t="n">
-        <v>0.547</v>
+        <v>0.474</v>
       </c>
     </row>
     <row r="244">
@@ -12411,7 +12411,7 @@
         <v>0.0147</v>
       </c>
       <c r="I244" t="n">
-        <v>0.235</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="245">
@@ -12448,7 +12448,7 @@
         <v>0.203</v>
       </c>
       <c r="I245" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.457</v>
       </c>
     </row>
     <row r="246">
@@ -12559,7 +12559,7 @@
         <v>0.3</v>
       </c>
       <c r="I248" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249">
@@ -12633,7 +12633,7 @@
         <v>0.0489</v>
       </c>
       <c r="I250" t="n">
-        <v>0.391</v>
+        <v>0.147</v>
       </c>
     </row>
     <row r="251">
@@ -12670,7 +12670,7 @@
         <v>0.579</v>
       </c>
       <c r="I251" t="n">
-        <v>1</v>
+        <v>0.868</v>
       </c>
     </row>
     <row r="252">
@@ -12707,7 +12707,7 @@
         <v>0.475</v>
       </c>
       <c r="I252" t="n">
-        <v>1</v>
+        <v>0.8179999999999999</v>
       </c>
     </row>
     <row r="253">
@@ -12744,7 +12744,7 @@
         <v>0.554</v>
       </c>
       <c r="I253" t="n">
-        <v>1</v>
+        <v>0.788</v>
       </c>
     </row>
     <row r="254">
@@ -12892,7 +12892,7 @@
         <v>0.628</v>
       </c>
       <c r="I257" t="n">
-        <v>1</v>
+        <v>0.905</v>
       </c>
     </row>
     <row r="258">
@@ -13040,7 +13040,7 @@
         <v>0.237</v>
       </c>
       <c r="I261" t="n">
-        <v>1</v>
+        <v>0.711</v>
       </c>
     </row>
     <row r="262">
@@ -13225,7 +13225,7 @@
         <v>0.0326</v>
       </c>
       <c r="I266" t="n">
-        <v>0.522</v>
+        <v>0.293</v>
       </c>
     </row>
     <row r="267">
@@ -13447,7 +13447,7 @@
         <v>0.12</v>
       </c>
       <c r="I272" t="n">
-        <v>0.964</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273">
@@ -13521,7 +13521,7 @@
         <v>0.73</v>
       </c>
       <c r="I274" t="n">
-        <v>1</v>
+        <v>0.946</v>
       </c>
     </row>
     <row r="275">
@@ -14148,7 +14148,7 @@
         <v>0.4</v>
       </c>
       <c r="I291" t="n">
-        <v>0.724</v>
+        <v>1</v>
       </c>
     </row>
     <row r="292">
@@ -14222,7 +14222,7 @@
         <v>0.192</v>
       </c>
       <c r="I293" t="n">
-        <v>0.513</v>
+        <v>0.864</v>
       </c>
     </row>
     <row r="294">
@@ -14333,7 +14333,7 @@
         <v>0.0463</v>
       </c>
       <c r="I296" t="n">
-        <v>0.185</v>
+        <v>0.208</v>
       </c>
     </row>
     <row r="297">
@@ -14407,7 +14407,7 @@
         <v>0.0326</v>
       </c>
       <c r="I298" t="n">
-        <v>0.174</v>
+        <v>0.293</v>
       </c>
     </row>
     <row r="299">
@@ -14481,7 +14481,7 @@
         <v>0.393</v>
       </c>
       <c r="I300" t="n">
-        <v>0.724</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="301">
@@ -14518,7 +14518,7 @@
         <v>0.728</v>
       </c>
       <c r="I301" t="n">
-        <v>1</v>
+        <v>0.955</v>
       </c>
     </row>
     <row r="302">
@@ -14555,7 +14555,7 @@
         <v>0.167</v>
       </c>
       <c r="I302" t="n">
-        <v>0.513</v>
+        <v>1</v>
       </c>
     </row>
     <row r="303">
@@ -14592,7 +14592,7 @@
         <v>0.407</v>
       </c>
       <c r="I303" t="n">
-        <v>0.724</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="304">
@@ -14629,7 +14629,7 @@
         <v>3.36e-06</v>
       </c>
       <c r="I304" t="n">
-        <v>5.37e-05</v>
+        <v>3.02e-05</v>
       </c>
     </row>
     <row r="305">
@@ -14666,7 +14666,7 @@
         <v>0.000232</v>
       </c>
       <c r="I305" t="n">
-        <v>0.00185</v>
+        <v>0.00209</v>
       </c>
     </row>
     <row r="306">
@@ -14703,7 +14703,7 @@
         <v>0.526</v>
       </c>
       <c r="I306" t="n">
-        <v>0.797</v>
+        <v>1</v>
       </c>
     </row>
     <row r="307">
@@ -14740,7 +14740,7 @@
         <v>0.491</v>
       </c>
       <c r="I307" t="n">
-        <v>0.797</v>
+        <v>0.838</v>
       </c>
     </row>
     <row r="308">
@@ -14777,7 +14777,7 @@
         <v>0.598</v>
       </c>
       <c r="I308" t="n">
-        <v>0.797</v>
+        <v>1</v>
       </c>
     </row>
     <row r="309">
@@ -14814,7 +14814,7 @@
         <v>0.0717</v>
       </c>
       <c r="I309" t="n">
-        <v>0.287</v>
+        <v>0.215</v>
       </c>
     </row>
     <row r="310">
@@ -14851,7 +14851,7 @@
         <v>0.791</v>
       </c>
       <c r="I310" t="n">
-        <v>0.844</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
@@ -14888,7 +14888,7 @@
         <v>0.715</v>
       </c>
       <c r="I311" t="n">
-        <v>0.844</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312">
@@ -14925,7 +14925,7 @@
         <v>0.454</v>
       </c>
       <c r="I312" t="n">
-        <v>0.797</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313">
@@ -14962,7 +14962,7 @@
         <v>0.462</v>
       </c>
       <c r="I313" t="n">
-        <v>0.797</v>
+        <v>0.9419999999999999</v>
       </c>
     </row>
     <row r="314">
@@ -14999,7 +14999,7 @@
         <v>0.00912</v>
       </c>
       <c r="I314" t="n">
-        <v>0.0486</v>
+        <v>0.08210000000000001</v>
       </c>
     </row>
     <row r="315">
@@ -15036,7 +15036,7 @@
         <v>0.579</v>
       </c>
       <c r="I315" t="n">
-        <v>0.797</v>
+        <v>0.868</v>
       </c>
     </row>
     <row r="316">
@@ -15073,7 +15073,7 @@
         <v>0.464</v>
       </c>
       <c r="I316" t="n">
-        <v>0.797</v>
+        <v>0.8179999999999999</v>
       </c>
     </row>
     <row r="317">
@@ -15110,7 +15110,7 @@
         <v>0.759</v>
       </c>
       <c r="I317" t="n">
-        <v>0.844</v>
+        <v>0.788</v>
       </c>
     </row>
     <row r="318">
@@ -15147,7 +15147,7 @@
         <v>0.161</v>
       </c>
       <c r="I318" t="n">
-        <v>0.516</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319">
@@ -15221,7 +15221,7 @@
         <v>1.32e-05</v>
       </c>
       <c r="I320" t="n">
-        <v>0.000212</v>
+        <v>0.000119</v>
       </c>
     </row>
     <row r="321">
@@ -15258,7 +15258,7 @@
         <v>0.000458</v>
       </c>
       <c r="I321" t="n">
-        <v>0.00366</v>
+        <v>0.00412</v>
       </c>
     </row>
     <row r="322">
@@ -15332,7 +15332,7 @@
         <v>0.0523</v>
       </c>
       <c r="I323" t="n">
-        <v>0.837</v>
+        <v>0.173</v>
       </c>
     </row>
     <row r="324">
@@ -15850,7 +15850,7 @@
         <v>0.604</v>
       </c>
       <c r="I337" t="n">
-        <v>1</v>
+        <v>0.909</v>
       </c>
     </row>
     <row r="338">
@@ -15887,7 +15887,7 @@
         <v>0.475</v>
       </c>
       <c r="I338" t="n">
-        <v>1</v>
+        <v>0.946</v>
       </c>
     </row>
     <row r="339">
@@ -15924,7 +15924,7 @@
         <v>0.245</v>
       </c>
       <c r="I339" t="n">
-        <v>1</v>
+        <v>0.821</v>
       </c>
     </row>
     <row r="340">
@@ -16405,7 +16405,7 @@
         <v>0.0357</v>
       </c>
       <c r="I352" t="n">
-        <v>0.572</v>
+        <v>0.321</v>
       </c>
     </row>
     <row r="353">
@@ -16442,7 +16442,7 @@
         <v>0.418</v>
       </c>
       <c r="I353" t="n">
-        <v>1</v>
+        <v>0.9409999999999999</v>
       </c>
     </row>
     <row r="354">
@@ -16849,7 +16849,7 @@
         <v>0.345</v>
       </c>
       <c r="I364" t="n">
-        <v>1</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="365">
@@ -16886,7 +16886,7 @@
         <v>0.6929999999999999</v>
       </c>
       <c r="I365" t="n">
-        <v>1</v>
+        <v>0.955</v>
       </c>
     </row>
     <row r="366">
@@ -16960,7 +16960,7 @@
         <v>0.661</v>
       </c>
       <c r="I367" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="368">
@@ -16997,7 +16997,7 @@
         <v>0.155</v>
       </c>
       <c r="I368" t="n">
-        <v>1</v>
+        <v>0.465</v>
       </c>
     </row>
     <row r="369">
@@ -17034,7 +17034,7 @@
         <v>0.166</v>
       </c>
       <c r="I369" t="n">
-        <v>1</v>
+        <v>0.583</v>
       </c>
     </row>
     <row r="370">
@@ -17108,7 +17108,7 @@
         <v>0.158</v>
       </c>
       <c r="I371" t="n">
-        <v>1</v>
+        <v>0.474</v>
       </c>
     </row>
     <row r="372">
@@ -17330,7 +17330,7 @@
         <v>0.608</v>
       </c>
       <c r="I377" t="n">
-        <v>1</v>
+        <v>0.9419999999999999</v>
       </c>
     </row>
     <row r="378">
@@ -17367,7 +17367,7 @@
         <v>0.594</v>
       </c>
       <c r="I378" t="n">
-        <v>1</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="379">
@@ -17404,7 +17404,7 @@
         <v>0.77</v>
       </c>
       <c r="I379" t="n">
-        <v>1</v>
+        <v>0.905</v>
       </c>
     </row>
     <row r="380">
@@ -17441,7 +17441,7 @@
         <v>0.292</v>
       </c>
       <c r="I380" t="n">
-        <v>1</v>
+        <v>0.8179999999999999</v>
       </c>
     </row>
     <row r="381">
@@ -17478,7 +17478,7 @@
         <v>0.306</v>
       </c>
       <c r="I381" t="n">
-        <v>1</v>
+        <v>0.788</v>
       </c>
     </row>
     <row r="382">
@@ -17626,7 +17626,7 @@
         <v>0.612</v>
       </c>
       <c r="I385" t="n">
-        <v>1</v>
+        <v>0.905</v>
       </c>
     </row>
     <row r="386">
@@ -17663,7 +17663,7 @@
         <v>0.288</v>
       </c>
       <c r="I386" t="n">
-        <v>0.922</v>
+        <v>1</v>
       </c>
     </row>
     <row r="387">
@@ -17737,7 +17737,7 @@
         <v>0.0575</v>
       </c>
       <c r="I388" t="n">
-        <v>0.919</v>
+        <v>0.259</v>
       </c>
     </row>
     <row r="389">
@@ -17774,7 +17774,7 @@
         <v>0.237</v>
       </c>
       <c r="I389" t="n">
-        <v>0.922</v>
+        <v>0.711</v>
       </c>
     </row>
     <row r="390">
@@ -17848,7 +17848,7 @@
         <v>0.267</v>
       </c>
       <c r="I391" t="n">
-        <v>0.922</v>
+        <v>1</v>
       </c>
     </row>
     <row r="392">
@@ -17959,7 +17959,7 @@
         <v>0.119</v>
       </c>
       <c r="I394" t="n">
-        <v>0.922</v>
+        <v>0.357</v>
       </c>
     </row>
     <row r="395">
@@ -18218,7 +18218,7 @@
         <v>0.606</v>
       </c>
       <c r="I401" t="n">
-        <v>1</v>
+        <v>0.909</v>
       </c>
     </row>
     <row r="402">
@@ -18847,7 +18847,7 @@
         <v>0.0687</v>
       </c>
       <c r="I418" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.309</v>
       </c>
     </row>
     <row r="419">
@@ -18921,7 +18921,7 @@
         <v>0.192</v>
       </c>
       <c r="I420" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.864</v>
       </c>
     </row>
     <row r="421">
@@ -18958,7 +18958,7 @@
         <v>0.192</v>
       </c>
       <c r="I421" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.864</v>
       </c>
     </row>
     <row r="422">
@@ -19032,7 +19032,7 @@
         <v>0.215</v>
       </c>
       <c r="I423" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.968</v>
       </c>
     </row>
     <row r="424">
@@ -19143,7 +19143,7 @@
         <v>0.119</v>
       </c>
       <c r="I426" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.357</v>
       </c>
     </row>
     <row r="427">
@@ -19217,7 +19217,7 @@
         <v>0.377</v>
       </c>
       <c r="I428" t="n">
-        <v>1</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="429">
@@ -19328,7 +19328,7 @@
         <v>0.523</v>
       </c>
       <c r="I431" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="432">
@@ -19439,7 +19439,7 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I434" t="n">
-        <v>0.33</v>
+        <v>0.612</v>
       </c>
     </row>
     <row r="435">
@@ -19513,7 +19513,7 @@
         <v>0.0354</v>
       </c>
       <c r="I436" t="n">
-        <v>0.33</v>
+        <v>0.159</v>
       </c>
     </row>
     <row r="437">
@@ -19550,7 +19550,7 @@
         <v>0.0717</v>
       </c>
       <c r="I437" t="n">
-        <v>0.33</v>
+        <v>0.215</v>
       </c>
     </row>
     <row r="438">
@@ -19624,7 +19624,7 @@
         <v>0.103</v>
       </c>
       <c r="I439" t="n">
-        <v>0.33</v>
+        <v>0.463</v>
       </c>
     </row>
     <row r="440">
@@ -19661,7 +19661,7 @@
         <v>0.789</v>
       </c>
       <c r="I440" t="n">
-        <v>0.919</v>
+        <v>1</v>
       </c>
     </row>
     <row r="441">
@@ -19698,7 +19698,7 @@
         <v>0.608</v>
       </c>
       <c r="I441" t="n">
-        <v>0.919</v>
+        <v>0.9419999999999999</v>
       </c>
     </row>
     <row r="442">
@@ -19735,7 +19735,7 @@
         <v>0.0459</v>
       </c>
       <c r="I442" t="n">
-        <v>0.33</v>
+        <v>0.147</v>
       </c>
     </row>
     <row r="443">
@@ -19772,7 +19772,7 @@
         <v>0.804</v>
       </c>
       <c r="I443" t="n">
-        <v>0.919</v>
+        <v>0.905</v>
       </c>
     </row>
     <row r="444">
@@ -19809,7 +19809,7 @@
         <v>0.238</v>
       </c>
       <c r="I444" t="n">
-        <v>0.634</v>
+        <v>0.8179999999999999</v>
       </c>
     </row>
     <row r="445">
@@ -19846,7 +19846,7 @@
         <v>0.788</v>
       </c>
       <c r="I445" t="n">
-        <v>0.919</v>
+        <v>0.788</v>
       </c>
     </row>
     <row r="446">
@@ -19883,7 +19883,7 @@
         <v>0.611</v>
       </c>
       <c r="I446" t="n">
-        <v>0.919</v>
+        <v>1</v>
       </c>
     </row>
     <row r="447">
@@ -19920,7 +19920,7 @@
         <v>0.6</v>
       </c>
       <c r="I447" t="n">
-        <v>0.919</v>
+        <v>1</v>
       </c>
     </row>
     <row r="448">
@@ -19957,7 +19957,7 @@
         <v>0.8</v>
       </c>
       <c r="I448" t="n">
-        <v>0.919</v>
+        <v>1</v>
       </c>
     </row>
     <row r="449">
@@ -19994,7 +19994,7 @@
         <v>0.804</v>
       </c>
       <c r="I449" t="n">
-        <v>0.919</v>
+        <v>0.905</v>
       </c>
     </row>
     <row r="450">
@@ -20068,7 +20068,7 @@
         <v>0.0575</v>
       </c>
       <c r="I451" t="n">
-        <v>0.306</v>
+        <v>0.173</v>
       </c>
     </row>
     <row r="452">
@@ -20105,7 +20105,7 @@
         <v>0.0575</v>
       </c>
       <c r="I452" t="n">
-        <v>0.306</v>
+        <v>0.259</v>
       </c>
     </row>
     <row r="453">
@@ -20142,7 +20142,7 @@
         <v>0.0522</v>
       </c>
       <c r="I453" t="n">
-        <v>0.306</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="454">
@@ -20586,7 +20586,7 @@
         <v>0.438</v>
       </c>
       <c r="I465" t="n">
-        <v>1</v>
+        <v>0.909</v>
       </c>
     </row>
     <row r="466">
@@ -20623,7 +20623,7 @@
         <v>0.736</v>
       </c>
       <c r="I466" t="n">
-        <v>1</v>
+        <v>0.946</v>
       </c>
     </row>
     <row r="467">
@@ -20660,7 +20660,7 @@
         <v>0.538</v>
       </c>
       <c r="I467" t="n">
-        <v>1</v>
+        <v>0.821</v>
       </c>
     </row>
     <row r="468">
@@ -20734,7 +20734,7 @@
         <v>0.103</v>
       </c>
       <c r="I469" t="n">
-        <v>1</v>
+        <v>0.927</v>
       </c>
     </row>
     <row r="470">
@@ -21178,7 +21178,7 @@
         <v>0.191</v>
       </c>
       <c r="I481" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="482">
@@ -21622,7 +21622,7 @@
         <v>0.743</v>
       </c>
       <c r="I493" t="n">
-        <v>1</v>
+        <v>0.955</v>
       </c>
     </row>
     <row r="494">
@@ -21733,7 +21733,7 @@
         <v>0.0824</v>
       </c>
       <c r="I496" t="n">
-        <v>1</v>
+        <v>0.371</v>
       </c>
     </row>
     <row r="497">
@@ -21770,7 +21770,7 @@
         <v>0.491</v>
       </c>
       <c r="I497" t="n">
-        <v>1</v>
+        <v>0.736</v>
       </c>
     </row>
     <row r="498">
@@ -21844,7 +21844,7 @@
         <v>0.65</v>
       </c>
       <c r="I499" t="n">
-        <v>1</v>
+        <v>0.838</v>
       </c>
     </row>
     <row r="500">
@@ -21881,7 +21881,7 @@
         <v>0.09329999999999999</v>
       </c>
       <c r="I500" t="n">
-        <v>0.746</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="501">
@@ -21918,7 +21918,7 @@
         <v>0.0482</v>
       </c>
       <c r="I501" t="n">
-        <v>0.746</v>
+        <v>0.215</v>
       </c>
     </row>
     <row r="502">
@@ -22140,7 +22140,7 @@
         <v>0.219</v>
       </c>
       <c r="I507" t="n">
-        <v>1</v>
+        <v>0.675</v>
       </c>
     </row>
     <row r="508">
@@ -22177,7 +22177,7 @@
         <v>0.8179999999999999</v>
       </c>
       <c r="I508" t="n">
-        <v>1</v>
+        <v>0.8179999999999999</v>
       </c>
     </row>
     <row r="509">
@@ -22214,7 +22214,7 @@
         <v>0.592</v>
       </c>
       <c r="I509" t="n">
-        <v>1</v>
+        <v>0.788</v>
       </c>
     </row>
     <row r="510">
@@ -22399,7 +22399,7 @@
         <v>0.209</v>
       </c>
       <c r="I514" t="n">
-        <v>0.5580000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="515">
@@ -22436,7 +22436,7 @@
         <v>0.104</v>
       </c>
       <c r="I515" t="n">
-        <v>0.501</v>
+        <v>0.234</v>
       </c>
     </row>
     <row r="516">
@@ -22584,7 +22584,7 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I519" t="n">
-        <v>0.501</v>
+        <v>0.756</v>
       </c>
     </row>
     <row r="520">
@@ -22621,7 +22621,7 @@
         <v>0.158</v>
       </c>
       <c r="I520" t="n">
-        <v>0.506</v>
+        <v>1</v>
       </c>
     </row>
     <row r="521">
@@ -22806,7 +22806,7 @@
         <v>0.0716</v>
       </c>
       <c r="I525" t="n">
-        <v>0.501</v>
+        <v>0.644</v>
       </c>
     </row>
     <row r="526">
@@ -22880,7 +22880,7 @@
         <v>0.125</v>
       </c>
       <c r="I527" t="n">
-        <v>0.501</v>
+        <v>1</v>
       </c>
     </row>
     <row r="528">
@@ -23028,7 +23028,7 @@
         <v>0.547</v>
       </c>
       <c r="I531" t="n">
-        <v>1</v>
+        <v>0.821</v>
       </c>
     </row>
     <row r="532">
@@ -23583,7 +23583,7 @@
         <v>0.0496</v>
       </c>
       <c r="I546" t="n">
-        <v>0.159</v>
+        <v>0.309</v>
       </c>
     </row>
     <row r="547">
@@ -23731,7 +23731,7 @@
         <v>0.385</v>
       </c>
       <c r="I550" t="n">
-        <v>0.872</v>
+        <v>1</v>
       </c>
     </row>
     <row r="551">
@@ -23768,7 +23768,7 @@
         <v>0.008840000000000001</v>
       </c>
       <c r="I551" t="n">
-        <v>0.0471</v>
+        <v>0.0796</v>
       </c>
     </row>
     <row r="552">
@@ -23805,7 +23805,7 @@
         <v>0.00304</v>
       </c>
       <c r="I552" t="n">
-        <v>0.0471</v>
+        <v>0.0274</v>
       </c>
     </row>
     <row r="553">
@@ -23916,7 +23916,7 @@
         <v>0.365</v>
       </c>
       <c r="I555" t="n">
-        <v>0.872</v>
+        <v>1</v>
       </c>
     </row>
     <row r="556">
@@ -23953,7 +23953,7 @@
         <v>0.572</v>
       </c>
       <c r="I556" t="n">
-        <v>0.915</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="557">
@@ -23990,7 +23990,7 @@
         <v>0.007820000000000001</v>
       </c>
       <c r="I557" t="n">
-        <v>0.0471</v>
+        <v>0.0704</v>
       </c>
     </row>
     <row r="558">
@@ -24064,7 +24064,7 @@
         <v>0.0436</v>
       </c>
       <c r="I559" t="n">
-        <v>0.159</v>
+        <v>0.392</v>
       </c>
     </row>
     <row r="560">
@@ -24101,7 +24101,7 @@
         <v>0.451</v>
       </c>
       <c r="I560" t="n">
-        <v>0.872</v>
+        <v>0.9409999999999999</v>
       </c>
     </row>
     <row r="561">
@@ -24138,7 +24138,7 @@
         <v>0.491</v>
       </c>
       <c r="I561" t="n">
-        <v>0.872</v>
+        <v>0.736</v>
       </c>
     </row>
     <row r="562">
@@ -24175,7 +24175,7 @@
         <v>0.136</v>
       </c>
       <c r="I562" t="n">
-        <v>0.435</v>
+        <v>0.612</v>
       </c>
     </row>
     <row r="563">
@@ -24212,7 +24212,7 @@
         <v>0.652</v>
       </c>
       <c r="I563" t="n">
-        <v>1</v>
+        <v>0.838</v>
       </c>
     </row>
     <row r="564">
@@ -24323,7 +24323,7 @@
         <v>0.245</v>
       </c>
       <c r="I566" t="n">
-        <v>0.653</v>
+        <v>1</v>
       </c>
     </row>
     <row r="567">
@@ -24360,7 +24360,7 @@
         <v>0.0106</v>
       </c>
       <c r="I567" t="n">
-        <v>0.136</v>
+        <v>0.0954</v>
       </c>
     </row>
     <row r="568">
@@ -24397,7 +24397,7 @@
         <v>0.0255</v>
       </c>
       <c r="I568" t="n">
-        <v>0.136</v>
+        <v>0.229</v>
       </c>
     </row>
     <row r="569">
@@ -24471,7 +24471,7 @@
         <v>0.819</v>
       </c>
       <c r="I570" t="n">
-        <v>1</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="571">
@@ -24508,7 +24508,7 @@
         <v>0.311</v>
       </c>
       <c r="I571" t="n">
-        <v>0.711</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="572">
@@ -24545,7 +24545,7 @@
         <v>0.647</v>
       </c>
       <c r="I572" t="n">
-        <v>1</v>
+        <v>0.8179999999999999</v>
       </c>
     </row>
     <row r="573">
@@ -24582,7 +24582,7 @@
         <v>0.0171</v>
       </c>
       <c r="I573" t="n">
-        <v>0.136</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="574">
@@ -24656,7 +24656,7 @@
         <v>0.0434</v>
       </c>
       <c r="I575" t="n">
-        <v>0.174</v>
+        <v>0.391</v>
       </c>
     </row>
     <row r="576">
@@ -24730,7 +24730,7 @@
         <v>0.609</v>
       </c>
       <c r="I577" t="n">
-        <v>1</v>
+        <v>0.905</v>
       </c>
     </row>
   </sheetData>
@@ -24835,7 +24835,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>85.7**</t>
+          <t>85.7**†</t>
         </is>
       </c>
     </row>
@@ -24925,7 +24925,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>94.7**</t>
+          <t>94.7**†</t>
         </is>
       </c>
     </row>

--- a/eval/results/statistical_tests_new30.xlsx
+++ b/eval/results/statistical_tests_new30.xlsx
@@ -24744,7 +24744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24801,131 +24801,41 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>85.7**†</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>81.8</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>90.9</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>78.3</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>47.4</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>94.7**</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>12</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>83.3</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>85.7</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>94.7**†</t>
+          <t>94.7*</t>
         </is>
       </c>
     </row>
